--- a/gstdatabase/GSTR-3B-2019-2020.xlsx
+++ b/gstdatabase/GSTR-3B-2019-2020.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\Feb-26\GST Statistics Downloads 28th Feb 26\Downloads\GSTR 3B\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\May-26\GST Statistics Downloads 31st May 26\Downloads\GSTR 3B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D9EF1E1-5EA5-4E06-81F8-23C45CFFC054}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F272B1B-ED77-47E6-BED5-0070BDDBFCAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -185,10 +185,10 @@
     <t>STATE WISE RETURN PERIOD WISE GSTR-3B FILING SUMMARY</t>
   </si>
   <si>
-    <t>Data Considered upto 28th Feb 2026</t>
+    <t>Data Considered upto 31st May 2026</t>
   </si>
   <si>
-    <t>Filing %age as on 28th Feb 2026</t>
+    <t>Filing %age as on 31st May 2026</t>
   </si>
 </sst>
 </file>
@@ -367,6 +367,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="17" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -375,18 +387,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -679,12 +679,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:62" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
     </row>
     <row r="2" spans="1:62" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -701,10 +701,10 @@
       <c r="L2" s="1"/>
     </row>
     <row r="3" spans="1:62" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="22" t="s">
+      <c r="A3" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="22"/>
+      <c r="B3" s="26"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
@@ -731,107 +731,107 @@
       <c r="L4" s="1"/>
     </row>
     <row r="5" spans="1:62" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="22" t="s">
+      <c r="A5" s="26" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="22"/>
-      <c r="C5" s="22"/>
+      <c r="B5" s="26"/>
+      <c r="C5" s="26"/>
     </row>
     <row r="8" spans="1:62" s="17" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="23" t="s">
+      <c r="A8" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="24" t="s">
+      <c r="B8" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="C8" s="25">
+      <c r="C8" s="22">
         <v>43556</v>
       </c>
-      <c r="D8" s="24"/>
-      <c r="E8" s="24"/>
-      <c r="F8" s="24"/>
-      <c r="G8" s="24"/>
-      <c r="H8" s="25">
+      <c r="D8" s="23"/>
+      <c r="E8" s="23"/>
+      <c r="F8" s="23"/>
+      <c r="G8" s="23"/>
+      <c r="H8" s="22">
         <v>43586</v>
       </c>
-      <c r="I8" s="24"/>
-      <c r="J8" s="24"/>
-      <c r="K8" s="24"/>
-      <c r="L8" s="24"/>
-      <c r="M8" s="25">
+      <c r="I8" s="23"/>
+      <c r="J8" s="23"/>
+      <c r="K8" s="23"/>
+      <c r="L8" s="23"/>
+      <c r="M8" s="22">
         <v>43617</v>
       </c>
-      <c r="N8" s="24"/>
-      <c r="O8" s="24"/>
-      <c r="P8" s="24"/>
-      <c r="Q8" s="24"/>
-      <c r="R8" s="25">
+      <c r="N8" s="23"/>
+      <c r="O8" s="23"/>
+      <c r="P8" s="23"/>
+      <c r="Q8" s="23"/>
+      <c r="R8" s="22">
         <v>43647</v>
       </c>
-      <c r="S8" s="24"/>
-      <c r="T8" s="24"/>
-      <c r="U8" s="24"/>
-      <c r="V8" s="24"/>
-      <c r="W8" s="25">
+      <c r="S8" s="23"/>
+      <c r="T8" s="23"/>
+      <c r="U8" s="23"/>
+      <c r="V8" s="23"/>
+      <c r="W8" s="22">
         <v>43678</v>
       </c>
-      <c r="X8" s="24"/>
-      <c r="Y8" s="24"/>
-      <c r="Z8" s="24"/>
-      <c r="AA8" s="24"/>
-      <c r="AB8" s="25">
+      <c r="X8" s="23"/>
+      <c r="Y8" s="23"/>
+      <c r="Z8" s="23"/>
+      <c r="AA8" s="23"/>
+      <c r="AB8" s="22">
         <v>43709</v>
       </c>
-      <c r="AC8" s="24"/>
-      <c r="AD8" s="24"/>
-      <c r="AE8" s="24"/>
-      <c r="AF8" s="24"/>
-      <c r="AG8" s="25">
+      <c r="AC8" s="23"/>
+      <c r="AD8" s="23"/>
+      <c r="AE8" s="23"/>
+      <c r="AF8" s="23"/>
+      <c r="AG8" s="22">
         <v>43739</v>
       </c>
-      <c r="AH8" s="24"/>
-      <c r="AI8" s="24"/>
-      <c r="AJ8" s="24"/>
-      <c r="AK8" s="24"/>
-      <c r="AL8" s="25">
+      <c r="AH8" s="23"/>
+      <c r="AI8" s="23"/>
+      <c r="AJ8" s="23"/>
+      <c r="AK8" s="23"/>
+      <c r="AL8" s="22">
         <v>43770</v>
       </c>
-      <c r="AM8" s="24"/>
-      <c r="AN8" s="24"/>
-      <c r="AO8" s="24"/>
-      <c r="AP8" s="24"/>
-      <c r="AQ8" s="25">
+      <c r="AM8" s="23"/>
+      <c r="AN8" s="23"/>
+      <c r="AO8" s="23"/>
+      <c r="AP8" s="23"/>
+      <c r="AQ8" s="22">
         <v>43800</v>
       </c>
-      <c r="AR8" s="24"/>
-      <c r="AS8" s="24"/>
-      <c r="AT8" s="24"/>
-      <c r="AU8" s="24"/>
-      <c r="AV8" s="25">
+      <c r="AR8" s="23"/>
+      <c r="AS8" s="23"/>
+      <c r="AT8" s="23"/>
+      <c r="AU8" s="23"/>
+      <c r="AV8" s="22">
         <v>43831</v>
       </c>
-      <c r="AW8" s="24"/>
-      <c r="AX8" s="24"/>
-      <c r="AY8" s="24"/>
-      <c r="AZ8" s="24"/>
-      <c r="BA8" s="25">
+      <c r="AW8" s="23"/>
+      <c r="AX8" s="23"/>
+      <c r="AY8" s="23"/>
+      <c r="AZ8" s="23"/>
+      <c r="BA8" s="22">
         <v>43862</v>
       </c>
-      <c r="BB8" s="24"/>
-      <c r="BC8" s="24"/>
-      <c r="BD8" s="24"/>
-      <c r="BE8" s="24"/>
-      <c r="BF8" s="25">
+      <c r="BB8" s="23"/>
+      <c r="BC8" s="23"/>
+      <c r="BD8" s="23"/>
+      <c r="BE8" s="23"/>
+      <c r="BF8" s="22">
         <v>43891</v>
       </c>
-      <c r="BG8" s="24"/>
-      <c r="BH8" s="24"/>
-      <c r="BI8" s="24"/>
-      <c r="BJ8" s="24"/>
+      <c r="BG8" s="23"/>
+      <c r="BH8" s="23"/>
+      <c r="BI8" s="23"/>
+      <c r="BJ8" s="23"/>
     </row>
     <row r="9" spans="1:62" s="17" customFormat="1" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="A9" s="23"/>
-      <c r="B9" s="24"/>
+      <c r="A9" s="27"/>
+      <c r="B9" s="23"/>
       <c r="C9" s="18" t="s">
         <v>3</v>
       </c>
@@ -1517,14 +1517,14 @@
       </c>
       <c r="Y12" s="11">
         <f t="shared" si="7"/>
-        <v>52167</v>
+        <v>52168</v>
       </c>
       <c r="Z12" s="3">
-        <v>284818</v>
+        <v>284819</v>
       </c>
       <c r="AA12" s="12">
         <f t="shared" si="8"/>
-        <v>0.91622595380557159</v>
+        <v>0.91622917068776943</v>
       </c>
       <c r="AB12" s="10">
         <v>311089</v>
@@ -1534,14 +1534,14 @@
       </c>
       <c r="AD12" s="11">
         <f t="shared" si="9"/>
-        <v>78533</v>
+        <v>78534</v>
       </c>
       <c r="AE12" s="3">
-        <v>286192</v>
+        <v>286193</v>
       </c>
       <c r="AF12" s="12">
         <f t="shared" si="10"/>
-        <v>0.91996824059995697</v>
+        <v>0.91997145511413136</v>
       </c>
       <c r="AG12" s="10">
         <v>309832</v>
@@ -1551,14 +1551,14 @@
       </c>
       <c r="AI12" s="11">
         <f t="shared" si="11"/>
-        <v>64628</v>
+        <v>64629</v>
       </c>
       <c r="AJ12" s="3">
-        <v>287455</v>
+        <v>287456</v>
       </c>
       <c r="AK12" s="12">
         <f t="shared" si="12"/>
-        <v>0.92777698881974746</v>
+        <v>0.92778021637532593</v>
       </c>
       <c r="AL12" s="10">
         <v>309106</v>
@@ -1568,14 +1568,14 @@
       </c>
       <c r="AN12" s="11">
         <f t="shared" si="13"/>
-        <v>31055</v>
+        <v>31056</v>
       </c>
       <c r="AO12" s="3">
-        <v>288426</v>
+        <v>288427</v>
       </c>
       <c r="AP12" s="12">
         <f t="shared" si="14"/>
-        <v>0.93309738406889542</v>
+        <v>0.93310061920506238</v>
       </c>
       <c r="AQ12" s="10">
         <v>308579</v>
@@ -1585,14 +1585,14 @@
       </c>
       <c r="AS12" s="11">
         <f t="shared" si="15"/>
-        <v>67337</v>
+        <v>67338</v>
       </c>
       <c r="AT12" s="3">
-        <v>290109</v>
+        <v>290110</v>
       </c>
       <c r="AU12" s="12">
         <f t="shared" si="16"/>
-        <v>0.94014498718318484</v>
+        <v>0.94014822784440932</v>
       </c>
       <c r="AV12" s="10">
         <v>309304</v>
@@ -1602,14 +1602,14 @@
       </c>
       <c r="AX12" s="11">
         <f t="shared" si="17"/>
-        <v>32676</v>
+        <v>32677</v>
       </c>
       <c r="AY12" s="3">
-        <v>291680</v>
+        <v>291681</v>
       </c>
       <c r="AZ12" s="12">
         <f t="shared" si="18"/>
-        <v>0.94302045883661378</v>
+        <v>0.94302369190181823</v>
       </c>
       <c r="BA12" s="10">
         <v>310694</v>
@@ -1619,14 +1619,14 @@
       </c>
       <c r="BC12" s="11">
         <f t="shared" si="19"/>
-        <v>59878</v>
+        <v>59879</v>
       </c>
       <c r="BD12" s="3">
-        <v>293021</v>
+        <v>293022</v>
       </c>
       <c r="BE12" s="12">
         <f t="shared" si="20"/>
-        <v>0.94311766561311128</v>
+        <v>0.94312088421404983</v>
       </c>
       <c r="BF12" s="10">
         <v>312194</v>
@@ -1636,14 +1636,14 @@
       </c>
       <c r="BH12" s="11">
         <f t="shared" si="21"/>
-        <v>281199</v>
+        <v>281200</v>
       </c>
       <c r="BI12" s="3">
-        <v>294507</v>
+        <v>294508</v>
       </c>
       <c r="BJ12" s="12">
         <f t="shared" si="22"/>
-        <v>0.943346124525135</v>
+        <v>0.94334932766164625</v>
       </c>
     </row>
     <row r="13" spans="1:62" x14ac:dyDescent="0.3">
@@ -1874,11 +1874,11 @@
         <v>111410</v>
       </c>
       <c r="F14" s="3">
-        <v>111522</v>
+        <v>111523</v>
       </c>
       <c r="G14" s="12">
         <f t="shared" si="0"/>
-        <v>0.86504809183990072</v>
+        <v>0.86505584858827178</v>
       </c>
       <c r="H14" s="10">
         <v>128392</v>
@@ -1888,14 +1888,14 @@
       </c>
       <c r="J14" s="11">
         <f t="shared" si="1"/>
-        <v>33400</v>
+        <v>33401</v>
       </c>
       <c r="K14" s="3">
-        <v>112557</v>
+        <v>112558</v>
       </c>
       <c r="L14" s="12">
         <f t="shared" si="2"/>
-        <v>0.87666677051529696</v>
+        <v>0.87667455916256465</v>
       </c>
       <c r="M14" s="10">
         <v>129422</v>
@@ -1905,14 +1905,14 @@
       </c>
       <c r="O14" s="11">
         <f t="shared" si="3"/>
-        <v>31902</v>
+        <v>31903</v>
       </c>
       <c r="P14" s="3">
-        <v>113281</v>
+        <v>113282</v>
       </c>
       <c r="Q14" s="12">
         <f t="shared" si="4"/>
-        <v>0.87528395481448285</v>
+        <v>0.87529168147610148</v>
       </c>
       <c r="R14" s="10">
         <v>131061</v>
@@ -1922,14 +1922,14 @@
       </c>
       <c r="T14" s="11">
         <f t="shared" si="5"/>
-        <v>28040</v>
+        <v>28042</v>
       </c>
       <c r="U14" s="3">
-        <v>114529</v>
+        <v>114531</v>
       </c>
       <c r="V14" s="12">
         <f t="shared" si="6"/>
-        <v>0.87386026354140434</v>
+        <v>0.87387552361114296</v>
       </c>
       <c r="W14" s="10">
         <v>131538</v>
@@ -1939,14 +1939,14 @@
       </c>
       <c r="Y14" s="11">
         <f t="shared" si="7"/>
-        <v>34535</v>
+        <v>34537</v>
       </c>
       <c r="Z14" s="3">
-        <v>115493</v>
+        <v>115495</v>
       </c>
       <c r="AA14" s="12">
         <f t="shared" si="8"/>
-        <v>0.87802003983639709</v>
+        <v>0.87803524456810955</v>
       </c>
       <c r="AB14" s="10">
         <v>131532</v>
@@ -1956,14 +1956,14 @@
       </c>
       <c r="AD14" s="11">
         <f t="shared" si="9"/>
-        <v>41988</v>
+        <v>41989</v>
       </c>
       <c r="AE14" s="3">
-        <v>116500</v>
+        <v>116501</v>
       </c>
       <c r="AF14" s="12">
         <f t="shared" si="10"/>
-        <v>0.88571602347717671</v>
+        <v>0.88572362618982448</v>
       </c>
       <c r="AG14" s="10">
         <v>131053</v>
@@ -1973,14 +1973,14 @@
       </c>
       <c r="AI14" s="11">
         <f t="shared" si="11"/>
-        <v>36698</v>
+        <v>36699</v>
       </c>
       <c r="AJ14" s="3">
-        <v>117326</v>
+        <v>117327</v>
       </c>
       <c r="AK14" s="12">
         <f t="shared" si="12"/>
-        <v>0.89525611775388581</v>
+        <v>0.89526374825452293</v>
       </c>
       <c r="AL14" s="10">
         <v>129677</v>
@@ -2007,14 +2007,14 @@
       </c>
       <c r="AS14" s="11">
         <f t="shared" si="15"/>
-        <v>37777</v>
+        <v>37778</v>
       </c>
       <c r="AT14" s="3">
-        <v>119508</v>
+        <v>119509</v>
       </c>
       <c r="AU14" s="12">
         <f t="shared" si="16"/>
-        <v>0.93032742219246756</v>
+        <v>0.93033520683803261</v>
       </c>
       <c r="AV14" s="10">
         <v>129146</v>
@@ -2024,14 +2024,14 @@
       </c>
       <c r="AX14" s="11">
         <f t="shared" si="17"/>
-        <v>22591</v>
+        <v>22592</v>
       </c>
       <c r="AY14" s="3">
-        <v>120575</v>
+        <v>120576</v>
       </c>
       <c r="AZ14" s="12">
         <f t="shared" si="18"/>
-        <v>0.93363325228810801</v>
+        <v>0.93364099546249979</v>
       </c>
       <c r="BA14" s="10">
         <v>130276</v>
@@ -2058,14 +2058,14 @@
       </c>
       <c r="BH14" s="11">
         <f t="shared" si="21"/>
-        <v>111833</v>
+        <v>111834</v>
       </c>
       <c r="BI14" s="3">
-        <v>122209</v>
+        <v>122210</v>
       </c>
       <c r="BJ14" s="12">
         <f t="shared" si="22"/>
-        <v>0.92742064004006886</v>
+        <v>0.92742822884809484</v>
       </c>
     </row>
     <row r="15" spans="1:62" x14ac:dyDescent="0.3">
@@ -2184,14 +2184,14 @@
       </c>
       <c r="AI15" s="11">
         <f t="shared" si="11"/>
-        <v>106881</v>
+        <v>106882</v>
       </c>
       <c r="AJ15" s="3">
-        <v>384874</v>
+        <v>384875</v>
       </c>
       <c r="AK15" s="12">
         <f t="shared" si="12"/>
-        <v>0.90589282015553507</v>
+        <v>0.90589517389421359</v>
       </c>
       <c r="AL15" s="10">
         <v>424839</v>
@@ -2201,14 +2201,14 @@
       </c>
       <c r="AN15" s="11">
         <f t="shared" si="13"/>
-        <v>60993</v>
+        <v>60994</v>
       </c>
       <c r="AO15" s="3">
-        <v>387669</v>
+        <v>387670</v>
       </c>
       <c r="AP15" s="12">
         <f t="shared" si="14"/>
-        <v>0.91250803245464751</v>
+        <v>0.91251038628751124</v>
       </c>
       <c r="AQ15" s="10">
         <v>424443</v>
@@ -2218,14 +2218,14 @@
       </c>
       <c r="AS15" s="11">
         <f t="shared" si="15"/>
-        <v>112476</v>
+        <v>112477</v>
       </c>
       <c r="AT15" s="3">
-        <v>390041</v>
+        <v>390042</v>
       </c>
       <c r="AU15" s="12">
         <f t="shared" si="16"/>
-        <v>0.91894789170748492</v>
+        <v>0.91895024773644518</v>
       </c>
       <c r="AV15" s="10">
         <v>424329</v>
@@ -2235,14 +2235,14 @@
       </c>
       <c r="AX15" s="11">
         <f t="shared" si="17"/>
-        <v>63093</v>
+        <v>63094</v>
       </c>
       <c r="AY15" s="3">
-        <v>391318</v>
+        <v>391319</v>
       </c>
       <c r="AZ15" s="12">
         <f t="shared" si="18"/>
-        <v>0.92220423303615828</v>
+        <v>0.922206589698088</v>
       </c>
       <c r="BA15" s="10">
         <v>421659</v>
@@ -2252,14 +2252,14 @@
       </c>
       <c r="BC15" s="11">
         <f t="shared" si="19"/>
-        <v>93165</v>
+        <v>93166</v>
       </c>
       <c r="BD15" s="3">
-        <v>393774</v>
+        <v>393775</v>
       </c>
       <c r="BE15" s="12">
         <f t="shared" si="20"/>
-        <v>0.93386836282398811</v>
+        <v>0.93387073440860979</v>
       </c>
       <c r="BF15" s="10">
         <v>423351</v>
@@ -2269,14 +2269,14 @@
       </c>
       <c r="BH15" s="11">
         <f t="shared" si="21"/>
-        <v>367412</v>
+        <v>367413</v>
       </c>
       <c r="BI15" s="3">
-        <v>394149</v>
+        <v>394150</v>
       </c>
       <c r="BJ15" s="12">
         <f t="shared" si="22"/>
-        <v>0.93102177625658145</v>
+        <v>0.93102413836272979</v>
       </c>
     </row>
     <row r="16" spans="1:62" x14ac:dyDescent="0.3">
@@ -2296,11 +2296,11 @@
         <v>615933</v>
       </c>
       <c r="F16" s="3">
-        <v>616114</v>
+        <v>616116</v>
       </c>
       <c r="G16" s="12">
         <f t="shared" si="0"/>
-        <v>0.83220299834805855</v>
+        <v>0.8322056998059002</v>
       </c>
       <c r="H16" s="10">
         <v>752005</v>
@@ -2310,14 +2310,14 @@
       </c>
       <c r="J16" s="11">
         <f t="shared" si="1"/>
-        <v>171520</v>
+        <v>171521</v>
       </c>
       <c r="K16" s="3">
-        <v>621838</v>
+        <v>621839</v>
       </c>
       <c r="L16" s="12">
         <f t="shared" si="2"/>
-        <v>0.82690673599244691</v>
+        <v>0.82690806577083931</v>
       </c>
       <c r="M16" s="10">
         <v>759157</v>
@@ -2327,14 +2327,14 @@
       </c>
       <c r="O16" s="11">
         <f t="shared" si="3"/>
-        <v>164541</v>
+        <v>164542</v>
       </c>
       <c r="P16" s="3">
-        <v>625644</v>
+        <v>625645</v>
       </c>
       <c r="Q16" s="12">
         <f t="shared" si="4"/>
-        <v>0.82412992305939348</v>
+        <v>0.82413124030997542</v>
       </c>
       <c r="R16" s="10">
         <v>765931</v>
@@ -2344,14 +2344,14 @@
       </c>
       <c r="T16" s="11">
         <f t="shared" si="5"/>
-        <v>140257</v>
+        <v>140259</v>
       </c>
       <c r="U16" s="3">
-        <v>630496</v>
+        <v>630498</v>
       </c>
       <c r="V16" s="12">
         <f t="shared" si="6"/>
-        <v>0.82317597799279574</v>
+        <v>0.82317858919406584</v>
       </c>
       <c r="W16" s="10">
         <v>767326</v>
@@ -2361,14 +2361,14 @@
       </c>
       <c r="Y16" s="11">
         <f t="shared" si="7"/>
-        <v>175746</v>
+        <v>175747</v>
       </c>
       <c r="Z16" s="3">
-        <v>634250</v>
+        <v>634251</v>
       </c>
       <c r="AA16" s="12">
         <f t="shared" si="8"/>
-        <v>0.82657175698464536</v>
+        <v>0.82657306021169619</v>
       </c>
       <c r="AB16" s="10">
         <v>766277</v>
@@ -2378,14 +2378,14 @@
       </c>
       <c r="AD16" s="11">
         <f t="shared" si="9"/>
-        <v>231750</v>
+        <v>231751</v>
       </c>
       <c r="AE16" s="3">
-        <v>638413</v>
+        <v>638414</v>
       </c>
       <c r="AF16" s="12">
         <f t="shared" si="10"/>
-        <v>0.83313605915354372</v>
+        <v>0.83313736416465589</v>
       </c>
       <c r="AG16" s="10">
         <v>757603</v>
@@ -2395,14 +2395,14 @@
       </c>
       <c r="AI16" s="11">
         <f t="shared" si="11"/>
-        <v>204326</v>
+        <v>204327</v>
       </c>
       <c r="AJ16" s="3">
-        <v>642293</v>
+        <v>642294</v>
       </c>
       <c r="AK16" s="12">
         <f t="shared" si="12"/>
-        <v>0.84779627324601403</v>
+        <v>0.84779759319854853</v>
       </c>
       <c r="AL16" s="10">
         <v>756133</v>
@@ -2412,14 +2412,14 @@
       </c>
       <c r="AN16" s="11">
         <f t="shared" si="13"/>
-        <v>124189</v>
+        <v>124190</v>
       </c>
       <c r="AO16" s="3">
-        <v>646446</v>
+        <v>646447</v>
       </c>
       <c r="AP16" s="12">
         <f t="shared" si="14"/>
-        <v>0.85493689602226064</v>
+        <v>0.85493821854091812</v>
       </c>
       <c r="AQ16" s="10">
         <v>746559</v>
@@ -2429,14 +2429,14 @@
       </c>
       <c r="AS16" s="11">
         <f t="shared" si="15"/>
-        <v>195658</v>
+        <v>195660</v>
       </c>
       <c r="AT16" s="3">
-        <v>651413</v>
+        <v>651415</v>
       </c>
       <c r="AU16" s="12">
         <f t="shared" si="16"/>
-        <v>0.87255394416248411</v>
+        <v>0.87255662312020887</v>
       </c>
       <c r="AV16" s="10">
         <v>745423</v>
@@ -2446,14 +2446,14 @@
       </c>
       <c r="AX16" s="11">
         <f t="shared" si="17"/>
-        <v>119187</v>
+        <v>119188</v>
       </c>
       <c r="AY16" s="3">
-        <v>654901</v>
+        <v>654902</v>
       </c>
       <c r="AZ16" s="12">
         <f t="shared" si="18"/>
-        <v>0.87856290991826114</v>
+        <v>0.87856425143844497</v>
       </c>
       <c r="BA16" s="10">
         <v>750648</v>
@@ -2463,14 +2463,14 @@
       </c>
       <c r="BC16" s="11">
         <f t="shared" si="19"/>
-        <v>183057</v>
+        <v>183058</v>
       </c>
       <c r="BD16" s="3">
-        <v>657657</v>
+        <v>657658</v>
       </c>
       <c r="BE16" s="12">
         <f t="shared" si="20"/>
-        <v>0.87611903315535378</v>
+        <v>0.87612036533768156</v>
       </c>
       <c r="BF16" s="10">
         <v>752110</v>
@@ -2480,14 +2480,14 @@
       </c>
       <c r="BH16" s="11">
         <f t="shared" si="21"/>
-        <v>610443</v>
+        <v>610444</v>
       </c>
       <c r="BI16" s="3">
-        <v>654252</v>
+        <v>654253</v>
       </c>
       <c r="BJ16" s="12">
         <f t="shared" si="22"/>
-        <v>0.86988871308718141</v>
+        <v>0.86989004267992709</v>
       </c>
     </row>
     <row r="17" spans="1:62" x14ac:dyDescent="0.3">
@@ -2507,11 +2507,11 @@
         <v>487170</v>
       </c>
       <c r="F17" s="3">
-        <v>487414</v>
+        <v>487417</v>
       </c>
       <c r="G17" s="12">
         <f t="shared" si="0"/>
-        <v>0.8802726346738714</v>
+        <v>0.88027805269203263</v>
       </c>
       <c r="H17" s="10">
         <v>557836</v>
@@ -2521,14 +2521,14 @@
       </c>
       <c r="J17" s="11">
         <f t="shared" si="1"/>
-        <v>119056</v>
+        <v>119060</v>
       </c>
       <c r="K17" s="3">
-        <v>491123</v>
+        <v>491127</v>
       </c>
       <c r="L17" s="12">
         <f t="shared" si="2"/>
-        <v>0.88040750328053408</v>
+        <v>0.88041467384679373</v>
       </c>
       <c r="M17" s="10">
         <v>560439</v>
@@ -2538,14 +2538,14 @@
       </c>
       <c r="O17" s="11">
         <f t="shared" si="3"/>
-        <v>114181</v>
+        <v>114183</v>
       </c>
       <c r="P17" s="3">
-        <v>494267</v>
+        <v>494269</v>
       </c>
       <c r="Q17" s="12">
         <f t="shared" si="4"/>
-        <v>0.88192827408513685</v>
+        <v>0.88193184271615643</v>
       </c>
       <c r="R17" s="10">
         <v>561513</v>
@@ -2555,14 +2555,14 @@
       </c>
       <c r="T17" s="11">
         <f t="shared" si="5"/>
-        <v>96201</v>
+        <v>96204</v>
       </c>
       <c r="U17" s="3">
-        <v>498342</v>
+        <v>498345</v>
       </c>
       <c r="V17" s="12">
         <f t="shared" si="6"/>
-        <v>0.88749859753914873</v>
+        <v>0.88750394024715362</v>
       </c>
       <c r="W17" s="10">
         <v>560642</v>
@@ -2572,14 +2572,14 @@
       </c>
       <c r="Y17" s="11">
         <f t="shared" si="7"/>
-        <v>126336</v>
+        <v>126338</v>
       </c>
       <c r="Z17" s="3">
-        <v>500734</v>
+        <v>500736</v>
       </c>
       <c r="AA17" s="12">
         <f t="shared" si="8"/>
-        <v>0.89314393142147752</v>
+        <v>0.89314749876034971</v>
       </c>
       <c r="AB17" s="10">
         <v>559918</v>
@@ -2589,14 +2589,14 @@
       </c>
       <c r="AD17" s="11">
         <f t="shared" si="9"/>
-        <v>167227</v>
+        <v>167229</v>
       </c>
       <c r="AE17" s="3">
-        <v>504381</v>
+        <v>504383</v>
       </c>
       <c r="AF17" s="12">
         <f t="shared" si="10"/>
-        <v>0.90081226179547724</v>
+        <v>0.9008158337470844</v>
       </c>
       <c r="AG17" s="10">
         <v>561583</v>
@@ -2606,14 +2606,14 @@
       </c>
       <c r="AI17" s="11">
         <f t="shared" si="11"/>
-        <v>143629</v>
+        <v>143632</v>
       </c>
       <c r="AJ17" s="3">
-        <v>508323</v>
+        <v>508326</v>
       </c>
       <c r="AK17" s="12">
         <f t="shared" si="12"/>
-        <v>0.90516094682353276</v>
+        <v>0.9051662888655817</v>
       </c>
       <c r="AL17" s="10">
         <v>559753</v>
@@ -2623,14 +2623,14 @@
       </c>
       <c r="AN17" s="11">
         <f t="shared" si="13"/>
-        <v>81138</v>
+        <v>81141</v>
       </c>
       <c r="AO17" s="3">
-        <v>511817</v>
+        <v>511820</v>
       </c>
       <c r="AP17" s="12">
         <f t="shared" si="14"/>
-        <v>0.91436222762539909</v>
+        <v>0.91436758713218147</v>
       </c>
       <c r="AQ17" s="10">
         <v>541872</v>
@@ -2640,14 +2640,14 @@
       </c>
       <c r="AS17" s="11">
         <f t="shared" si="15"/>
-        <v>151528</v>
+        <v>151530</v>
       </c>
       <c r="AT17" s="3">
-        <v>515481</v>
+        <v>515483</v>
       </c>
       <c r="AU17" s="12">
         <f t="shared" si="16"/>
-        <v>0.95129661617503769</v>
+        <v>0.9513003070835917</v>
       </c>
       <c r="AV17" s="10">
         <v>543495</v>
@@ -2657,14 +2657,14 @@
       </c>
       <c r="AX17" s="11">
         <f t="shared" si="17"/>
-        <v>80653</v>
+        <v>80657</v>
       </c>
       <c r="AY17" s="3">
-        <v>518289</v>
+        <v>518293</v>
       </c>
       <c r="AZ17" s="12">
         <f t="shared" si="18"/>
-        <v>0.95362238843043634</v>
+        <v>0.95362974820375535</v>
       </c>
       <c r="BA17" s="10">
         <v>547860</v>
@@ -2674,14 +2674,14 @@
       </c>
       <c r="BC17" s="11">
         <f t="shared" si="19"/>
-        <v>132517</v>
+        <v>132521</v>
       </c>
       <c r="BD17" s="3">
-        <v>522890</v>
+        <v>522894</v>
       </c>
       <c r="BE17" s="12">
         <f t="shared" si="20"/>
-        <v>0.95442266272405363</v>
+        <v>0.95442996385938017</v>
       </c>
       <c r="BF17" s="10">
         <v>552190</v>
@@ -2691,14 +2691,14 @@
       </c>
       <c r="BH17" s="11">
         <f t="shared" si="21"/>
-        <v>503399</v>
+        <v>503404</v>
       </c>
       <c r="BI17" s="3">
-        <v>526183</v>
+        <v>526188</v>
       </c>
       <c r="BJ17" s="12">
         <f t="shared" si="22"/>
-        <v>0.95290208080551986</v>
+        <v>0.95291113565982721</v>
       </c>
     </row>
     <row r="18" spans="1:62" x14ac:dyDescent="0.3">
@@ -2718,11 +2718,11 @@
         <v>977646</v>
       </c>
       <c r="F18" s="3">
-        <v>978113</v>
+        <v>978116</v>
       </c>
       <c r="G18" s="12">
         <f t="shared" si="0"/>
-        <v>0.87817414749286904</v>
+        <v>0.87817684096738835</v>
       </c>
       <c r="H18" s="10">
         <v>1112907</v>
@@ -2732,14 +2732,14 @@
       </c>
       <c r="J18" s="11">
         <f t="shared" si="1"/>
-        <v>228447</v>
+        <v>228450</v>
       </c>
       <c r="K18" s="3">
-        <v>985772</v>
+        <v>985775</v>
       </c>
       <c r="L18" s="12">
         <f t="shared" si="2"/>
-        <v>0.88576314103514486</v>
+        <v>0.8857658366781771</v>
       </c>
       <c r="M18" s="10">
         <v>1118687</v>
@@ -2749,14 +2749,14 @@
       </c>
       <c r="O18" s="11">
         <f t="shared" si="3"/>
-        <v>221694</v>
+        <v>221699</v>
       </c>
       <c r="P18" s="3">
-        <v>991274</v>
+        <v>991279</v>
       </c>
       <c r="Q18" s="12">
         <f t="shared" si="4"/>
-        <v>0.88610487115699033</v>
+        <v>0.88610934068242497</v>
       </c>
       <c r="R18" s="10">
         <v>1127309</v>
@@ -2766,14 +2766,14 @@
       </c>
       <c r="T18" s="11">
         <f t="shared" si="5"/>
-        <v>178377</v>
+        <v>178382</v>
       </c>
       <c r="U18" s="3">
-        <v>1000091</v>
+        <v>1000096</v>
       </c>
       <c r="V18" s="12">
         <f t="shared" si="6"/>
-        <v>0.88714895383608217</v>
+        <v>0.8871533891772353</v>
       </c>
       <c r="W18" s="10">
         <v>1128388</v>
@@ -2783,14 +2783,14 @@
       </c>
       <c r="Y18" s="11">
         <f t="shared" si="7"/>
-        <v>244979</v>
+        <v>244984</v>
       </c>
       <c r="Z18" s="3">
-        <v>1007713</v>
+        <v>1007718</v>
       </c>
       <c r="AA18" s="12">
         <f t="shared" si="8"/>
-        <v>0.89305540292877983</v>
+        <v>0.89305983402872058</v>
       </c>
       <c r="AB18" s="10">
         <v>1126122</v>
@@ -2800,14 +2800,14 @@
       </c>
       <c r="AD18" s="11">
         <f t="shared" si="9"/>
-        <v>308050</v>
+        <v>308055</v>
       </c>
       <c r="AE18" s="3">
-        <v>1016951</v>
+        <v>1016956</v>
       </c>
       <c r="AF18" s="12">
         <f t="shared" si="10"/>
-        <v>0.90305579679643944</v>
+        <v>0.90306023681270764</v>
       </c>
       <c r="AG18" s="10">
         <v>1126652</v>
@@ -2817,14 +2817,14 @@
       </c>
       <c r="AI18" s="11">
         <f t="shared" si="11"/>
-        <v>271496</v>
+        <v>271499</v>
       </c>
       <c r="AJ18" s="3">
-        <v>1026204</v>
+        <v>1026207</v>
       </c>
       <c r="AK18" s="12">
         <f t="shared" si="12"/>
-        <v>0.91084380980107438</v>
+        <v>0.91084647255763096</v>
       </c>
       <c r="AL18" s="10">
         <v>1124411</v>
@@ -2834,14 +2834,14 @@
       </c>
       <c r="AN18" s="11">
         <f t="shared" si="13"/>
-        <v>195014</v>
+        <v>195019</v>
       </c>
       <c r="AO18" s="3">
-        <v>1036122</v>
+        <v>1036127</v>
       </c>
       <c r="AP18" s="12">
         <f t="shared" si="14"/>
-        <v>0.92147977919106094</v>
+        <v>0.92148422596363788</v>
       </c>
       <c r="AQ18" s="10">
         <v>1127354</v>
@@ -2851,14 +2851,14 @@
       </c>
       <c r="AS18" s="11">
         <f t="shared" si="15"/>
-        <v>311775</v>
+        <v>311781</v>
       </c>
       <c r="AT18" s="3">
-        <v>1046788</v>
+        <v>1046794</v>
       </c>
       <c r="AU18" s="12">
         <f t="shared" si="16"/>
-        <v>0.92853531366367614</v>
+        <v>0.92854063586060809</v>
       </c>
       <c r="AV18" s="10">
         <v>1133999</v>
@@ -2868,14 +2868,14 @@
       </c>
       <c r="AX18" s="11">
         <f t="shared" si="17"/>
-        <v>165984</v>
+        <v>165989</v>
       </c>
       <c r="AY18" s="3">
-        <v>1059062</v>
+        <v>1059067</v>
       </c>
       <c r="AZ18" s="12">
         <f t="shared" si="18"/>
-        <v>0.93391793114456012</v>
+        <v>0.93392234031952404</v>
       </c>
       <c r="BA18" s="10">
         <v>1144874</v>
@@ -2885,14 +2885,14 @@
       </c>
       <c r="BC18" s="11">
         <f t="shared" si="19"/>
-        <v>239372</v>
+        <v>239377</v>
       </c>
       <c r="BD18" s="3">
-        <v>1070491</v>
+        <v>1070496</v>
       </c>
       <c r="BE18" s="12">
         <f t="shared" si="20"/>
-        <v>0.93502953163404878</v>
+        <v>0.93503389892686883</v>
       </c>
       <c r="BF18" s="10">
         <v>1155076</v>
@@ -2902,14 +2902,14 @@
       </c>
       <c r="BH18" s="11">
         <f t="shared" si="21"/>
-        <v>991954</v>
+        <v>991961</v>
       </c>
       <c r="BI18" s="3">
-        <v>1073224</v>
+        <v>1073231</v>
       </c>
       <c r="BJ18" s="12">
         <f t="shared" si="22"/>
-        <v>0.92913713037064227</v>
+        <v>0.92914319057793604</v>
       </c>
     </row>
     <row r="19" spans="1:62" x14ac:dyDescent="0.3">
@@ -2929,11 +2929,11 @@
         <v>256179</v>
       </c>
       <c r="F19" s="3">
-        <v>256468</v>
+        <v>256469</v>
       </c>
       <c r="G19" s="12">
         <f t="shared" si="0"/>
-        <v>0.8396618670647783</v>
+        <v>0.83966514100876766</v>
       </c>
       <c r="H19" s="10">
         <v>307632</v>
@@ -2943,14 +2943,14 @@
       </c>
       <c r="J19" s="11">
         <f t="shared" si="1"/>
-        <v>91609</v>
+        <v>91610</v>
       </c>
       <c r="K19" s="3">
-        <v>258787</v>
+        <v>258788</v>
       </c>
       <c r="L19" s="12">
         <f t="shared" si="2"/>
-        <v>0.8412226296354085</v>
+        <v>0.84122588027253342</v>
       </c>
       <c r="M19" s="10">
         <v>313451</v>
@@ -2960,14 +2960,14 @@
       </c>
       <c r="O19" s="11">
         <f t="shared" si="3"/>
-        <v>86409</v>
+        <v>86410</v>
       </c>
       <c r="P19" s="3">
-        <v>260668</v>
+        <v>260669</v>
       </c>
       <c r="Q19" s="12">
         <f t="shared" si="4"/>
-        <v>0.83160685402184076</v>
+        <v>0.83161004431314622</v>
       </c>
       <c r="R19" s="10">
         <v>317629</v>
@@ -2977,14 +2977,14 @@
       </c>
       <c r="T19" s="11">
         <f t="shared" si="5"/>
-        <v>74087</v>
+        <v>74088</v>
       </c>
       <c r="U19" s="3">
-        <v>264619</v>
+        <v>264620</v>
       </c>
       <c r="V19" s="12">
         <f t="shared" si="6"/>
-        <v>0.8331071785007037</v>
+        <v>0.83311032682784003</v>
       </c>
       <c r="W19" s="10">
         <v>320572</v>
@@ -2994,14 +2994,14 @@
       </c>
       <c r="Y19" s="11">
         <f t="shared" si="7"/>
-        <v>94193</v>
+        <v>94194</v>
       </c>
       <c r="Z19" s="3">
-        <v>267981</v>
+        <v>267982</v>
       </c>
       <c r="AA19" s="12">
         <f t="shared" si="8"/>
-        <v>0.83594637086208401</v>
+        <v>0.83594949028611354</v>
       </c>
       <c r="AB19" s="10">
         <v>325576</v>
@@ -3011,14 +3011,14 @@
       </c>
       <c r="AD19" s="11">
         <f t="shared" si="9"/>
-        <v>109232</v>
+        <v>109233</v>
       </c>
       <c r="AE19" s="3">
-        <v>272004</v>
+        <v>272005</v>
       </c>
       <c r="AF19" s="12">
         <f t="shared" si="10"/>
-        <v>0.83545470182077308</v>
+        <v>0.83545777330024329</v>
       </c>
       <c r="AG19" s="10">
         <v>330399</v>
@@ -3028,14 +3028,14 @@
       </c>
       <c r="AI19" s="11">
         <f t="shared" si="11"/>
-        <v>99184</v>
+        <v>99186</v>
       </c>
       <c r="AJ19" s="3">
-        <v>276219</v>
+        <v>276221</v>
       </c>
       <c r="AK19" s="12">
         <f t="shared" si="12"/>
-        <v>0.83601645283430037</v>
+        <v>0.83602250612138651</v>
       </c>
       <c r="AL19" s="10">
         <v>333051</v>
@@ -3045,14 +3045,14 @@
       </c>
       <c r="AN19" s="11">
         <f t="shared" si="13"/>
-        <v>64618</v>
+        <v>64620</v>
       </c>
       <c r="AO19" s="3">
-        <v>279782</v>
+        <v>279784</v>
       </c>
       <c r="AP19" s="12">
         <f t="shared" si="14"/>
-        <v>0.84005752872683159</v>
+        <v>0.8400635338131397</v>
       </c>
       <c r="AQ19" s="10">
         <v>332886</v>
@@ -3062,14 +3062,14 @@
       </c>
       <c r="AS19" s="11">
         <f t="shared" si="15"/>
-        <v>96091</v>
+        <v>96093</v>
       </c>
       <c r="AT19" s="3">
-        <v>284878</v>
+        <v>284880</v>
       </c>
       <c r="AU19" s="12">
         <f t="shared" si="16"/>
-        <v>0.85578246006140235</v>
+        <v>0.85578846812422271</v>
       </c>
       <c r="AV19" s="10">
         <v>332957</v>
@@ -3079,14 +3079,14 @@
       </c>
       <c r="AX19" s="11">
         <f t="shared" si="17"/>
-        <v>63422</v>
+        <v>63424</v>
       </c>
       <c r="AY19" s="3">
-        <v>289812</v>
+        <v>289814</v>
       </c>
       <c r="AZ19" s="12">
         <f t="shared" si="18"/>
-        <v>0.8704187027153657</v>
+        <v>0.87042470949702211</v>
       </c>
       <c r="BA19" s="10">
         <v>314833</v>
@@ -3096,14 +3096,14 @@
       </c>
       <c r="BC19" s="11">
         <f t="shared" si="19"/>
-        <v>87860</v>
+        <v>87862</v>
       </c>
       <c r="BD19" s="3">
-        <v>293376</v>
+        <v>293378</v>
       </c>
       <c r="BE19" s="12">
         <f t="shared" si="20"/>
-        <v>0.93184640746046321</v>
+        <v>0.93185276003468509</v>
       </c>
       <c r="BF19" s="10">
         <v>320339</v>
@@ -3113,14 +3113,14 @@
       </c>
       <c r="BH19" s="11">
         <f t="shared" si="21"/>
-        <v>273787</v>
+        <v>273791</v>
       </c>
       <c r="BI19" s="3">
-        <v>296535</v>
+        <v>296539</v>
       </c>
       <c r="BJ19" s="12">
         <f t="shared" si="22"/>
-        <v>0.92569122086289835</v>
+        <v>0.92570370763472443</v>
       </c>
     </row>
     <row r="20" spans="1:62" x14ac:dyDescent="0.3">
@@ -3399,14 +3399,14 @@
       </c>
       <c r="T21" s="11">
         <f t="shared" si="5"/>
-        <v>4331</v>
+        <v>4332</v>
       </c>
       <c r="U21" s="3">
-        <v>8564</v>
+        <v>8565</v>
       </c>
       <c r="V21" s="12">
         <f t="shared" si="6"/>
-        <v>0.75149175149175151</v>
+        <v>0.7515795015795016</v>
       </c>
       <c r="W21" s="10">
         <v>11658</v>
@@ -3416,14 +3416,14 @@
       </c>
       <c r="Y21" s="11">
         <f t="shared" si="7"/>
-        <v>4717</v>
+        <v>4718</v>
       </c>
       <c r="Z21" s="3">
-        <v>8747</v>
+        <v>8748</v>
       </c>
       <c r="AA21" s="12">
         <f t="shared" si="8"/>
-        <v>0.75030022302281696</v>
+        <v>0.75038600102933606</v>
       </c>
       <c r="AB21" s="10">
         <v>11960</v>
@@ -3433,14 +3433,14 @@
       </c>
       <c r="AD21" s="11">
         <f t="shared" si="9"/>
-        <v>5132</v>
+        <v>5133</v>
       </c>
       <c r="AE21" s="3">
-        <v>8953</v>
+        <v>8954</v>
       </c>
       <c r="AF21" s="12">
         <f t="shared" si="10"/>
-        <v>0.74857859531772575</v>
+        <v>0.74866220735785949</v>
       </c>
       <c r="AG21" s="10">
         <v>12126</v>
@@ -3450,14 +3450,14 @@
       </c>
       <c r="AI21" s="11">
         <f t="shared" si="11"/>
-        <v>4718</v>
+        <v>4719</v>
       </c>
       <c r="AJ21" s="3">
-        <v>9061</v>
+        <v>9062</v>
       </c>
       <c r="AK21" s="12">
         <f t="shared" si="12"/>
-        <v>0.74723734125020613</v>
+        <v>0.74731980867557313</v>
       </c>
       <c r="AL21" s="10">
         <v>12318</v>
@@ -3627,14 +3627,14 @@
       </c>
       <c r="Y22" s="11">
         <f t="shared" si="7"/>
-        <v>2522</v>
+        <v>2523</v>
       </c>
       <c r="Z22" s="3">
-        <v>5311</v>
+        <v>5312</v>
       </c>
       <c r="AA22" s="12">
         <f t="shared" si="8"/>
-        <v>0.79912729461330123</v>
+        <v>0.79927776105928383</v>
       </c>
       <c r="AB22" s="10">
         <v>6718</v>
@@ -3644,14 +3644,14 @@
       </c>
       <c r="AD22" s="11">
         <f t="shared" si="9"/>
-        <v>2803</v>
+        <v>2804</v>
       </c>
       <c r="AE22" s="3">
-        <v>5382</v>
+        <v>5383</v>
       </c>
       <c r="AF22" s="12">
         <f t="shared" si="10"/>
-        <v>0.80113128907412923</v>
+        <v>0.80128014289967253</v>
       </c>
       <c r="AG22" s="10">
         <v>6744</v>
@@ -3661,14 +3661,14 @@
       </c>
       <c r="AI22" s="11">
         <f t="shared" si="11"/>
-        <v>2600</v>
+        <v>2601</v>
       </c>
       <c r="AJ22" s="3">
-        <v>5453</v>
+        <v>5454</v>
       </c>
       <c r="AK22" s="12">
         <f t="shared" si="12"/>
-        <v>0.80857058125741399</v>
+        <v>0.80871886120996439</v>
       </c>
       <c r="AL22" s="10">
         <v>6735</v>
@@ -3678,14 +3678,14 @@
       </c>
       <c r="AN22" s="11">
         <f t="shared" si="13"/>
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="AO22" s="3">
-        <v>5506</v>
+        <v>5507</v>
       </c>
       <c r="AP22" s="12">
         <f t="shared" si="14"/>
-        <v>0.81752041573867851</v>
+        <v>0.81766889383815888</v>
       </c>
       <c r="AQ22" s="10">
         <v>6694</v>
@@ -3695,14 +3695,14 @@
       </c>
       <c r="AS22" s="11">
         <f t="shared" si="15"/>
-        <v>2716</v>
+        <v>2717</v>
       </c>
       <c r="AT22" s="3">
-        <v>5546</v>
+        <v>5547</v>
       </c>
       <c r="AU22" s="12">
         <f t="shared" si="16"/>
-        <v>0.82850313713773527</v>
+        <v>0.82865252464893935</v>
       </c>
       <c r="AV22" s="10">
         <v>6757</v>
@@ -3712,14 +3712,14 @@
       </c>
       <c r="AX22" s="11">
         <f t="shared" si="17"/>
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="AY22" s="3">
-        <v>5600</v>
+        <v>5601</v>
       </c>
       <c r="AZ22" s="12">
         <f t="shared" si="18"/>
-        <v>0.82877016427408612</v>
+        <v>0.82891815894627796</v>
       </c>
       <c r="BA22" s="10">
         <v>6695</v>
@@ -3729,14 +3729,14 @@
       </c>
       <c r="BC22" s="11">
         <f t="shared" si="19"/>
-        <v>2267</v>
+        <v>2268</v>
       </c>
       <c r="BD22" s="3">
-        <v>5631</v>
+        <v>5632</v>
       </c>
       <c r="BE22" s="12">
         <f t="shared" si="20"/>
-        <v>0.84107542942494395</v>
+        <v>0.84122479462285282</v>
       </c>
       <c r="BF22" s="10">
         <v>6784</v>
@@ -3746,14 +3746,14 @@
       </c>
       <c r="BH22" s="11">
         <f t="shared" si="21"/>
-        <v>5165</v>
+        <v>5166</v>
       </c>
       <c r="BI22" s="3">
-        <v>5672</v>
+        <v>5673</v>
       </c>
       <c r="BJ22" s="12">
         <f t="shared" si="22"/>
-        <v>0.83608490566037741</v>
+        <v>0.83623231132075471</v>
       </c>
     </row>
     <row r="23" spans="1:62" x14ac:dyDescent="0.3">
@@ -4617,11 +4617,11 @@
         <v>119095</v>
       </c>
       <c r="F27" s="3">
-        <v>119351</v>
+        <v>119353</v>
       </c>
       <c r="G27" s="12">
         <f t="shared" si="0"/>
-        <v>0.75604163103450461</v>
+        <v>0.75605430024768316</v>
       </c>
       <c r="H27" s="10">
         <v>159240</v>
@@ -4631,14 +4631,14 @@
       </c>
       <c r="J27" s="11">
         <f t="shared" si="1"/>
-        <v>52398</v>
+        <v>52400</v>
       </c>
       <c r="K27" s="3">
-        <v>120249</v>
+        <v>120251</v>
       </c>
       <c r="L27" s="12">
         <f t="shared" si="2"/>
-        <v>0.75514318010550108</v>
+        <v>0.7551557397638784</v>
       </c>
       <c r="M27" s="10">
         <v>161175</v>
@@ -4648,14 +4648,14 @@
       </c>
       <c r="O27" s="11">
         <f t="shared" si="3"/>
-        <v>51222</v>
+        <v>51224</v>
       </c>
       <c r="P27" s="3">
-        <v>121470</v>
+        <v>121472</v>
       </c>
       <c r="Q27" s="12">
         <f t="shared" si="4"/>
-        <v>0.75365286179618429</v>
+        <v>0.75366527066852795</v>
       </c>
       <c r="R27" s="10">
         <v>163738</v>
@@ -4665,14 +4665,14 @@
       </c>
       <c r="T27" s="11">
         <f t="shared" si="5"/>
-        <v>45702</v>
+        <v>45703</v>
       </c>
       <c r="U27" s="3">
-        <v>123209</v>
+        <v>123210</v>
       </c>
       <c r="V27" s="12">
         <f t="shared" si="6"/>
-        <v>0.7524765173631045</v>
+        <v>0.75248262468089266</v>
       </c>
       <c r="W27" s="10">
         <v>165285</v>
@@ -4682,14 +4682,14 @@
       </c>
       <c r="Y27" s="11">
         <f t="shared" si="7"/>
-        <v>54508</v>
+        <v>54509</v>
       </c>
       <c r="Z27" s="3">
-        <v>124679</v>
+        <v>124680</v>
       </c>
       <c r="AA27" s="12">
         <f t="shared" si="8"/>
-        <v>0.7543273739298787</v>
+        <v>0.75433342408567017</v>
       </c>
       <c r="AB27" s="10">
         <v>167059</v>
@@ -4699,14 +4699,14 @@
       </c>
       <c r="AD27" s="11">
         <f t="shared" si="9"/>
-        <v>63478</v>
+        <v>63479</v>
       </c>
       <c r="AE27" s="3">
-        <v>126161</v>
+        <v>126162</v>
       </c>
       <c r="AF27" s="12">
         <f t="shared" si="10"/>
-        <v>0.75518828677293648</v>
+        <v>0.75519427268210637</v>
       </c>
       <c r="AG27" s="10">
         <v>167755</v>
@@ -4716,14 +4716,14 @@
       </c>
       <c r="AI27" s="11">
         <f t="shared" si="11"/>
-        <v>54794</v>
+        <v>54795</v>
       </c>
       <c r="AJ27" s="3">
-        <v>127103</v>
+        <v>127104</v>
       </c>
       <c r="AK27" s="12">
         <f t="shared" si="12"/>
-        <v>0.75767041220827991</v>
+        <v>0.75767637328246551</v>
       </c>
       <c r="AL27" s="10">
         <v>166641</v>
@@ -4733,14 +4733,14 @@
       </c>
       <c r="AN27" s="11">
         <f t="shared" si="13"/>
-        <v>50760</v>
+        <v>50761</v>
       </c>
       <c r="AO27" s="3">
-        <v>128423</v>
+        <v>128424</v>
       </c>
       <c r="AP27" s="12">
         <f t="shared" si="14"/>
-        <v>0.77065668112889385</v>
+        <v>0.77066268205303612</v>
       </c>
       <c r="AQ27" s="10">
         <v>146205</v>
@@ -4750,14 +4750,14 @@
       </c>
       <c r="AS27" s="11">
         <f t="shared" si="15"/>
-        <v>56457</v>
+        <v>56458</v>
       </c>
       <c r="AT27" s="3">
-        <v>128844</v>
+        <v>128845</v>
       </c>
       <c r="AU27" s="12">
         <f t="shared" si="16"/>
-        <v>0.88125577100646357</v>
+        <v>0.88126261071782774</v>
       </c>
       <c r="AV27" s="10">
         <v>144136</v>
@@ -4767,14 +4767,14 @@
       </c>
       <c r="AX27" s="11">
         <f t="shared" si="17"/>
-        <v>38971</v>
+        <v>38972</v>
       </c>
       <c r="AY27" s="3">
-        <v>129611</v>
+        <v>129612</v>
       </c>
       <c r="AZ27" s="12">
         <f t="shared" si="18"/>
-        <v>0.89922711883221407</v>
+        <v>0.89923405672420487</v>
       </c>
       <c r="BA27" s="10">
         <v>144942</v>
@@ -4784,14 +4784,14 @@
       </c>
       <c r="BC27" s="11">
         <f t="shared" si="19"/>
-        <v>48734</v>
+        <v>48736</v>
       </c>
       <c r="BD27" s="3">
-        <v>130837</v>
+        <v>130839</v>
       </c>
       <c r="BE27" s="12">
         <f t="shared" si="20"/>
-        <v>0.90268521201584084</v>
+        <v>0.90269901063873825</v>
       </c>
       <c r="BF27" s="10">
         <v>145908</v>
@@ -4801,14 +4801,14 @@
       </c>
       <c r="BH27" s="11">
         <f t="shared" si="21"/>
-        <v>123823</v>
+        <v>123826</v>
       </c>
       <c r="BI27" s="3">
-        <v>131299</v>
+        <v>131302</v>
       </c>
       <c r="BJ27" s="12">
         <f t="shared" si="22"/>
-        <v>0.89987526386490113</v>
+        <v>0.89989582476629104</v>
       </c>
     </row>
     <row r="28" spans="1:62" x14ac:dyDescent="0.3">
@@ -4828,11 +4828,11 @@
         <v>516434</v>
       </c>
       <c r="F28" s="3">
-        <v>516701</v>
+        <v>516702</v>
       </c>
       <c r="G28" s="12">
         <f t="shared" si="0"/>
-        <v>0.88352444692194831</v>
+        <v>0.88352615685563718</v>
       </c>
       <c r="H28" s="10">
         <v>588402</v>
@@ -4842,14 +4842,14 @@
       </c>
       <c r="J28" s="11">
         <f t="shared" si="1"/>
-        <v>139563</v>
+        <v>139564</v>
       </c>
       <c r="K28" s="3">
-        <v>519360</v>
+        <v>519361</v>
       </c>
       <c r="L28" s="12">
         <f t="shared" si="2"/>
-        <v>0.88266185363068106</v>
+        <v>0.88266355314903755</v>
       </c>
       <c r="M28" s="10">
         <v>593424</v>
@@ -4859,14 +4859,14 @@
       </c>
       <c r="O28" s="11">
         <f t="shared" si="3"/>
-        <v>131522</v>
+        <v>131523</v>
       </c>
       <c r="P28" s="3">
-        <v>521974</v>
+        <v>521975</v>
       </c>
       <c r="Q28" s="12">
         <f t="shared" si="4"/>
-        <v>0.87959705033837521</v>
+        <v>0.87959873547412981</v>
       </c>
       <c r="R28" s="10">
         <v>598953</v>
@@ -4876,14 +4876,14 @@
       </c>
       <c r="T28" s="11">
         <f t="shared" si="5"/>
-        <v>115167</v>
+        <v>115168</v>
       </c>
       <c r="U28" s="3">
-        <v>526470</v>
+        <v>526471</v>
       </c>
       <c r="V28" s="12">
         <f t="shared" si="6"/>
-        <v>0.87898382677772713</v>
+        <v>0.87898549635781109</v>
       </c>
       <c r="W28" s="10">
         <v>603444</v>
@@ -4893,14 +4893,14 @@
       </c>
       <c r="Y28" s="11">
         <f t="shared" si="7"/>
-        <v>150608</v>
+        <v>150610</v>
       </c>
       <c r="Z28" s="3">
-        <v>530229</v>
+        <v>530231</v>
       </c>
       <c r="AA28" s="12">
         <f t="shared" si="8"/>
-        <v>0.87867142601467574</v>
+        <v>0.87867474032387427</v>
       </c>
       <c r="AB28" s="10">
         <v>607620</v>
@@ -4910,14 +4910,14 @@
       </c>
       <c r="AD28" s="11">
         <f t="shared" si="9"/>
-        <v>179455</v>
+        <v>179457</v>
       </c>
       <c r="AE28" s="3">
-        <v>533662</v>
+        <v>533664</v>
       </c>
       <c r="AF28" s="12">
         <f t="shared" si="10"/>
-        <v>0.87828247918106717</v>
+        <v>0.87828577071195812</v>
       </c>
       <c r="AG28" s="10">
         <v>610678</v>
@@ -4927,14 +4927,14 @@
       </c>
       <c r="AI28" s="11">
         <f t="shared" si="11"/>
-        <v>145985</v>
+        <v>145987</v>
       </c>
       <c r="AJ28" s="3">
-        <v>535616</v>
+        <v>535618</v>
       </c>
       <c r="AK28" s="12">
         <f t="shared" si="12"/>
-        <v>0.87708415891844804</v>
+        <v>0.87708743396683686</v>
       </c>
       <c r="AL28" s="10">
         <v>612549</v>
@@ -4944,14 +4944,14 @@
       </c>
       <c r="AN28" s="11">
         <f t="shared" si="13"/>
-        <v>100035</v>
+        <v>100037</v>
       </c>
       <c r="AO28" s="3">
-        <v>539203</v>
+        <v>539205</v>
       </c>
       <c r="AP28" s="12">
         <f t="shared" si="14"/>
-        <v>0.88026100769081328</v>
+        <v>0.88026427273573216</v>
       </c>
       <c r="AQ28" s="10">
         <v>611342</v>
@@ -4961,14 +4961,14 @@
       </c>
       <c r="AS28" s="11">
         <f t="shared" si="15"/>
-        <v>156268</v>
+        <v>156270</v>
       </c>
       <c r="AT28" s="3">
-        <v>543845</v>
+        <v>543847</v>
       </c>
       <c r="AU28" s="12">
         <f t="shared" si="16"/>
-        <v>0.88959207775680393</v>
+        <v>0.88959534924804773</v>
       </c>
       <c r="AV28" s="10">
         <v>612426</v>
@@ -4978,14 +4978,14 @@
       </c>
       <c r="AX28" s="11">
         <f t="shared" si="17"/>
-        <v>93827</v>
+        <v>93830</v>
       </c>
       <c r="AY28" s="3">
-        <v>546417</v>
+        <v>546420</v>
       </c>
       <c r="AZ28" s="12">
         <f t="shared" si="18"/>
-        <v>0.89221718215751777</v>
+        <v>0.89222208070852638</v>
       </c>
       <c r="BA28" s="10">
         <v>611319</v>
@@ -4995,14 +4995,14 @@
       </c>
       <c r="BC28" s="11">
         <f t="shared" si="19"/>
-        <v>134674</v>
+        <v>134677</v>
       </c>
       <c r="BD28" s="3">
-        <v>549764</v>
+        <v>549767</v>
       </c>
       <c r="BE28" s="12">
         <f t="shared" si="20"/>
-        <v>0.8993078899886966</v>
+        <v>0.8993127974101901</v>
       </c>
       <c r="BF28" s="10">
         <v>611625</v>
@@ -5012,14 +5012,14 @@
       </c>
       <c r="BH28" s="11">
         <f t="shared" si="21"/>
-        <v>507346</v>
+        <v>507349</v>
       </c>
       <c r="BI28" s="3">
-        <v>550971</v>
+        <v>550974</v>
       </c>
       <c r="BJ28" s="12">
         <f t="shared" si="22"/>
-        <v>0.90083139178418148</v>
+        <v>0.90083629675045984</v>
       </c>
     </row>
     <row r="29" spans="1:62" x14ac:dyDescent="0.3">
@@ -5250,11 +5250,11 @@
         <v>192952</v>
       </c>
       <c r="F30" s="3">
-        <v>193165</v>
+        <v>193169</v>
       </c>
       <c r="G30" s="12">
         <f t="shared" si="0"/>
-        <v>0.88193531302505657</v>
+        <v>0.88195357586383227</v>
       </c>
       <c r="H30" s="10">
         <v>219645</v>
@@ -5264,14 +5264,14 @@
       </c>
       <c r="J30" s="11">
         <f t="shared" si="1"/>
-        <v>67233</v>
+        <v>67235</v>
       </c>
       <c r="K30" s="3">
-        <v>194744</v>
+        <v>194746</v>
       </c>
       <c r="L30" s="12">
         <f t="shared" si="2"/>
-        <v>0.88663069953789064</v>
+        <v>0.88663980514011242</v>
       </c>
       <c r="M30" s="10">
         <v>219769</v>
@@ -5281,14 +5281,14 @@
       </c>
       <c r="O30" s="11">
         <f t="shared" si="3"/>
-        <v>62225</v>
+        <v>62227</v>
       </c>
       <c r="P30" s="3">
-        <v>195699</v>
+        <v>195701</v>
       </c>
       <c r="Q30" s="12">
         <f t="shared" si="4"/>
-        <v>0.89047590879514404</v>
+        <v>0.89048500925972274</v>
       </c>
       <c r="R30" s="10">
         <v>219972</v>
@@ -5298,14 +5298,14 @@
       </c>
       <c r="T30" s="11">
         <f t="shared" si="5"/>
-        <v>50586</v>
+        <v>50587</v>
       </c>
       <c r="U30" s="3">
-        <v>197861</v>
+        <v>197862</v>
       </c>
       <c r="V30" s="12">
         <f t="shared" si="6"/>
-        <v>0.89948266142963651</v>
+        <v>0.899487207462768</v>
       </c>
       <c r="W30" s="10">
         <v>220124</v>
@@ -5315,14 +5315,14 @@
       </c>
       <c r="Y30" s="11">
         <f t="shared" si="7"/>
-        <v>67686</v>
+        <v>67687</v>
       </c>
       <c r="Z30" s="3">
-        <v>199928</v>
+        <v>199929</v>
       </c>
       <c r="AA30" s="12">
         <f t="shared" si="8"/>
-        <v>0.90825171267103999</v>
+        <v>0.90825625556504519</v>
       </c>
       <c r="AB30" s="10">
         <v>220841</v>
@@ -5332,14 +5332,14 @@
       </c>
       <c r="AD30" s="11">
         <f t="shared" si="9"/>
-        <v>73358</v>
+        <v>73361</v>
       </c>
       <c r="AE30" s="3">
-        <v>202067</v>
+        <v>202070</v>
       </c>
       <c r="AF30" s="12">
         <f t="shared" si="10"/>
-        <v>0.91498861171612156</v>
+        <v>0.91500219615017142</v>
       </c>
       <c r="AG30" s="10">
         <v>221583</v>
@@ -5349,14 +5349,14 @@
       </c>
       <c r="AI30" s="11">
         <f t="shared" si="11"/>
-        <v>65142</v>
+        <v>65145</v>
       </c>
       <c r="AJ30" s="3">
-        <v>204329</v>
+        <v>204332</v>
       </c>
       <c r="AK30" s="12">
         <f t="shared" si="12"/>
-        <v>0.92213301561942929</v>
+        <v>0.92214655456420391</v>
       </c>
       <c r="AL30" s="10">
         <v>221270</v>
@@ -5366,14 +5366,14 @@
       </c>
       <c r="AN30" s="11">
         <f t="shared" si="13"/>
-        <v>41876</v>
+        <v>41877</v>
       </c>
       <c r="AO30" s="3">
-        <v>207164</v>
+        <v>207165</v>
       </c>
       <c r="AP30" s="12">
         <f t="shared" si="14"/>
-        <v>0.93624983052379451</v>
+        <v>0.93625434988927558</v>
       </c>
       <c r="AQ30" s="10">
         <v>222288</v>
@@ -5383,14 +5383,14 @@
       </c>
       <c r="AS30" s="11">
         <f t="shared" si="15"/>
-        <v>71377</v>
+        <v>71378</v>
       </c>
       <c r="AT30" s="3">
-        <v>210205</v>
+        <v>210206</v>
       </c>
       <c r="AU30" s="12">
         <f t="shared" si="16"/>
-        <v>0.9456425897934212</v>
+        <v>0.94564708846181533</v>
       </c>
       <c r="AV30" s="10">
         <v>223595</v>
@@ -5400,14 +5400,14 @@
       </c>
       <c r="AX30" s="11">
         <f t="shared" si="17"/>
-        <v>44967</v>
+        <v>44969</v>
       </c>
       <c r="AY30" s="3">
-        <v>212265</v>
+        <v>212267</v>
       </c>
       <c r="AZ30" s="12">
         <f t="shared" si="18"/>
-        <v>0.94932802611865208</v>
+        <v>0.94933697086249691</v>
       </c>
       <c r="BA30" s="10">
         <v>223670</v>
@@ -5417,14 +5417,14 @@
       </c>
       <c r="BC30" s="11">
         <f t="shared" si="19"/>
-        <v>55521</v>
+        <v>55525</v>
       </c>
       <c r="BD30" s="3">
-        <v>214160</v>
+        <v>214164</v>
       </c>
       <c r="BE30" s="12">
         <f t="shared" si="20"/>
-        <v>0.95748200473912459</v>
+        <v>0.95749988822819332</v>
       </c>
       <c r="BF30" s="10">
         <v>223069</v>
@@ -5434,14 +5434,14 @@
       </c>
       <c r="BH30" s="11">
         <f t="shared" si="21"/>
-        <v>194006</v>
+        <v>194010</v>
       </c>
       <c r="BI30" s="3">
-        <v>214653</v>
+        <v>214657</v>
       </c>
       <c r="BJ30" s="12">
         <f t="shared" si="22"/>
-        <v>0.96227176344539134</v>
+        <v>0.96228969511675755</v>
       </c>
     </row>
     <row r="31" spans="1:62" x14ac:dyDescent="0.3">
@@ -5461,11 +5461,11 @@
         <v>95037</v>
       </c>
       <c r="F31" s="3">
-        <v>95120</v>
+        <v>95122</v>
       </c>
       <c r="G31" s="12">
         <f t="shared" si="0"/>
-        <v>0.92397956210051868</v>
+        <v>0.92399898976162265</v>
       </c>
       <c r="H31" s="10">
         <v>103880</v>
@@ -5475,14 +5475,14 @@
       </c>
       <c r="J31" s="11">
         <f t="shared" si="1"/>
-        <v>38776</v>
+        <v>38779</v>
       </c>
       <c r="K31" s="3">
-        <v>95777</v>
+        <v>95780</v>
       </c>
       <c r="L31" s="12">
         <f t="shared" si="2"/>
-        <v>0.92199653446284169</v>
+        <v>0.9220254139391606</v>
       </c>
       <c r="M31" s="10">
         <v>104773</v>
@@ -5492,14 +5492,14 @@
       </c>
       <c r="O31" s="11">
         <f t="shared" si="3"/>
-        <v>37056</v>
+        <v>37058</v>
       </c>
       <c r="P31" s="3">
-        <v>96419</v>
+        <v>96421</v>
       </c>
       <c r="Q31" s="12">
         <f t="shared" si="4"/>
-        <v>0.92026571731266638</v>
+        <v>0.92028480620007058</v>
       </c>
       <c r="R31" s="10">
         <v>106003</v>
@@ -5509,14 +5509,14 @@
       </c>
       <c r="T31" s="11">
         <f t="shared" si="5"/>
-        <v>31794</v>
+        <v>31796</v>
       </c>
       <c r="U31" s="3">
-        <v>97293</v>
+        <v>97295</v>
       </c>
       <c r="V31" s="12">
         <f t="shared" si="6"/>
-        <v>0.91783251417412715</v>
+        <v>0.91785138156467272</v>
       </c>
       <c r="W31" s="10">
         <v>106926</v>
@@ -5526,14 +5526,14 @@
       </c>
       <c r="Y31" s="11">
         <f t="shared" si="7"/>
-        <v>38974</v>
+        <v>38976</v>
       </c>
       <c r="Z31" s="3">
-        <v>97989</v>
+        <v>97991</v>
       </c>
       <c r="AA31" s="12">
         <f t="shared" si="8"/>
-        <v>0.91641883171539196</v>
+        <v>0.91643753624001645</v>
       </c>
       <c r="AB31" s="10">
         <v>107458</v>
@@ -5543,14 +5543,14 @@
       </c>
       <c r="AD31" s="11">
         <f t="shared" si="9"/>
-        <v>45794</v>
+        <v>45796</v>
       </c>
       <c r="AE31" s="3">
-        <v>98714</v>
+        <v>98716</v>
       </c>
       <c r="AF31" s="12">
         <f t="shared" si="10"/>
-        <v>0.91862867352826216</v>
+        <v>0.91864728545106</v>
       </c>
       <c r="AG31" s="10">
         <v>107867</v>
@@ -5560,14 +5560,14 @@
       </c>
       <c r="AI31" s="11">
         <f t="shared" si="11"/>
-        <v>40919</v>
+        <v>40920</v>
       </c>
       <c r="AJ31" s="3">
-        <v>99571</v>
+        <v>99572</v>
       </c>
       <c r="AK31" s="12">
         <f t="shared" si="12"/>
-        <v>0.9230904725263519</v>
+        <v>0.92309974320227683</v>
       </c>
       <c r="AL31" s="10">
         <v>106953</v>
@@ -5577,14 +5577,14 @@
       </c>
       <c r="AN31" s="11">
         <f t="shared" si="13"/>
-        <v>26280</v>
+        <v>26281</v>
       </c>
       <c r="AO31" s="3">
-        <v>100300</v>
+        <v>100301</v>
       </c>
       <c r="AP31" s="12">
         <f t="shared" si="14"/>
-        <v>0.93779510626162899</v>
+        <v>0.93780445616298747</v>
       </c>
       <c r="AQ31" s="10">
         <v>105112</v>
@@ -5594,14 +5594,14 @@
       </c>
       <c r="AS31" s="11">
         <f t="shared" si="15"/>
-        <v>38477</v>
+        <v>38479</v>
       </c>
       <c r="AT31" s="3">
-        <v>101057</v>
+        <v>101059</v>
       </c>
       <c r="AU31" s="12">
         <f t="shared" si="16"/>
-        <v>0.96142210213867119</v>
+        <v>0.9614411294619073</v>
       </c>
       <c r="AV31" s="10">
         <v>104718</v>
@@ -5611,14 +5611,14 @@
       </c>
       <c r="AX31" s="11">
         <f t="shared" si="17"/>
-        <v>26650</v>
+        <v>26651</v>
       </c>
       <c r="AY31" s="3">
-        <v>101538</v>
+        <v>101539</v>
       </c>
       <c r="AZ31" s="12">
         <f t="shared" si="18"/>
-        <v>0.96963272789778265</v>
+        <v>0.96964227735441855</v>
       </c>
       <c r="BA31" s="10">
         <v>105608</v>
@@ -5628,14 +5628,14 @@
       </c>
       <c r="BC31" s="11">
         <f t="shared" si="19"/>
-        <v>34945</v>
+        <v>34947</v>
       </c>
       <c r="BD31" s="3">
-        <v>102143</v>
+        <v>102145</v>
       </c>
       <c r="BE31" s="12">
         <f t="shared" si="20"/>
-        <v>0.96718998560715097</v>
+        <v>0.96720892356639654</v>
       </c>
       <c r="BF31" s="10">
         <v>107069</v>
@@ -5645,14 +5645,14 @@
       </c>
       <c r="BH31" s="11">
         <f t="shared" si="21"/>
-        <v>97168</v>
+        <v>97171</v>
       </c>
       <c r="BI31" s="3">
-        <v>102792</v>
+        <v>102795</v>
       </c>
       <c r="BJ31" s="12">
         <f t="shared" si="22"/>
-        <v>0.96005379708412331</v>
+        <v>0.96008181639877088</v>
       </c>
     </row>
     <row r="32" spans="1:62" x14ac:dyDescent="0.3">
@@ -5672,11 +5672,11 @@
         <v>322477</v>
       </c>
       <c r="F32" s="3">
-        <v>322628</v>
+        <v>322629</v>
       </c>
       <c r="G32" s="12">
         <f t="shared" si="0"/>
-        <v>0.92544052136847754</v>
+        <v>0.92544338981300611</v>
       </c>
       <c r="H32" s="10">
         <v>351108</v>
@@ -5686,14 +5686,14 @@
       </c>
       <c r="J32" s="11">
         <f t="shared" si="1"/>
-        <v>101288</v>
+        <v>101289</v>
       </c>
       <c r="K32" s="3">
-        <v>324242</v>
+        <v>324243</v>
       </c>
       <c r="L32" s="12">
         <f t="shared" si="2"/>
-        <v>0.92348223338687807</v>
+        <v>0.92348508151338049</v>
       </c>
       <c r="M32" s="10">
         <v>353290</v>
@@ -5703,14 +5703,14 @@
       </c>
       <c r="O32" s="11">
         <f t="shared" si="3"/>
-        <v>96829</v>
+        <v>96830</v>
       </c>
       <c r="P32" s="3">
-        <v>326003</v>
+        <v>326004</v>
       </c>
       <c r="Q32" s="12">
         <f t="shared" si="4"/>
-        <v>0.92276316906790457</v>
+        <v>0.92276599960372496</v>
       </c>
       <c r="R32" s="10">
         <v>356965</v>
@@ -5720,14 +5720,14 @@
       </c>
       <c r="T32" s="11">
         <f t="shared" si="5"/>
-        <v>82599</v>
+        <v>82600</v>
       </c>
       <c r="U32" s="3">
-        <v>328433</v>
+        <v>328434</v>
       </c>
       <c r="V32" s="12">
         <f t="shared" si="6"/>
-        <v>0.92007059515638789</v>
+        <v>0.92007339655148268</v>
       </c>
       <c r="W32" s="10">
         <v>358593</v>
@@ -5737,14 +5737,14 @@
       </c>
       <c r="Y32" s="11">
         <f t="shared" si="7"/>
-        <v>104436</v>
+        <v>104438</v>
       </c>
       <c r="Z32" s="3">
-        <v>330361</v>
+        <v>330363</v>
       </c>
       <c r="AA32" s="12">
         <f t="shared" si="8"/>
-        <v>0.92127007498752067</v>
+        <v>0.92127565234123365</v>
       </c>
       <c r="AB32" s="10">
         <v>359995</v>
@@ -5754,14 +5754,14 @@
       </c>
       <c r="AD32" s="11">
         <f t="shared" si="9"/>
-        <v>133116</v>
+        <v>133117</v>
       </c>
       <c r="AE32" s="3">
-        <v>332562</v>
+        <v>332563</v>
       </c>
       <c r="AF32" s="12">
         <f t="shared" si="10"/>
-        <v>0.92379616383560881</v>
+        <v>0.92379894165196741</v>
       </c>
       <c r="AG32" s="10">
         <v>361943</v>
@@ -5771,14 +5771,14 @@
       </c>
       <c r="AI32" s="11">
         <f t="shared" si="11"/>
-        <v>115785</v>
+        <v>115786</v>
       </c>
       <c r="AJ32" s="3">
-        <v>335343</v>
+        <v>335344</v>
       </c>
       <c r="AK32" s="12">
         <f t="shared" si="12"/>
-        <v>0.9265077650348259</v>
+        <v>0.92651052790080202</v>
       </c>
       <c r="AL32" s="10">
         <v>362211</v>
@@ -5788,14 +5788,14 @@
       </c>
       <c r="AN32" s="11">
         <f t="shared" si="13"/>
-        <v>63066</v>
+        <v>63067</v>
       </c>
       <c r="AO32" s="3">
-        <v>337803</v>
+        <v>337804</v>
       </c>
       <c r="AP32" s="12">
         <f t="shared" si="14"/>
-        <v>0.93261386319023998</v>
+        <v>0.93261662401197087</v>
       </c>
       <c r="AQ32" s="10">
         <v>354752</v>
@@ -5805,14 +5805,14 @@
       </c>
       <c r="AS32" s="11">
         <f t="shared" si="15"/>
-        <v>107059</v>
+        <v>107060</v>
       </c>
       <c r="AT32" s="3">
-        <v>340056</v>
+        <v>340057</v>
       </c>
       <c r="AU32" s="12">
         <f t="shared" si="16"/>
-        <v>0.95857387696193397</v>
+        <v>0.95857669583258165</v>
       </c>
       <c r="AV32" s="10">
         <v>347413</v>
@@ -5822,14 +5822,14 @@
       </c>
       <c r="AX32" s="11">
         <f t="shared" si="17"/>
-        <v>63213</v>
+        <v>63214</v>
       </c>
       <c r="AY32" s="3">
-        <v>342092</v>
+        <v>342093</v>
       </c>
       <c r="AZ32" s="12">
         <f t="shared" si="18"/>
-        <v>0.98468393525861153</v>
+        <v>0.98468681367709321</v>
       </c>
       <c r="BA32" s="10">
         <v>348074</v>
@@ -5839,14 +5839,14 @@
       </c>
       <c r="BC32" s="11">
         <f t="shared" si="19"/>
-        <v>76526</v>
+        <v>76527</v>
       </c>
       <c r="BD32" s="3">
-        <v>344314</v>
+        <v>344315</v>
       </c>
       <c r="BE32" s="12">
         <f t="shared" si="20"/>
-        <v>0.98919769933979551</v>
+        <v>0.98920057229209879</v>
       </c>
       <c r="BF32" s="10">
         <v>351474</v>
@@ -5856,14 +5856,14 @@
       </c>
       <c r="BH32" s="11">
         <f t="shared" si="21"/>
-        <v>330988</v>
+        <v>330989</v>
       </c>
       <c r="BI32" s="3">
-        <v>346330</v>
+        <v>346331</v>
       </c>
       <c r="BJ32" s="12">
         <f t="shared" si="22"/>
-        <v>0.98536449353294986</v>
+        <v>0.98536733869361603</v>
       </c>
     </row>
     <row r="33" spans="1:62" x14ac:dyDescent="0.3">
@@ -5883,11 +5883,11 @@
         <v>798628</v>
       </c>
       <c r="F33" s="3">
-        <v>798871</v>
+        <v>798873</v>
       </c>
       <c r="G33" s="12">
         <f t="shared" si="0"/>
-        <v>0.91928650007134538</v>
+        <v>0.91928880153553694</v>
       </c>
       <c r="H33" s="10">
         <v>871303</v>
@@ -5897,14 +5897,14 @@
       </c>
       <c r="J33" s="11">
         <f t="shared" si="1"/>
-        <v>172515</v>
+        <v>172517</v>
       </c>
       <c r="K33" s="3">
-        <v>805150</v>
+        <v>805152</v>
       </c>
       <c r="L33" s="12">
         <f t="shared" si="2"/>
-        <v>0.92407578075594832</v>
+        <v>0.92407807616868065</v>
       </c>
       <c r="M33" s="10">
         <v>877062</v>
@@ -5914,14 +5914,14 @@
       </c>
       <c r="O33" s="11">
         <f t="shared" si="3"/>
-        <v>162000</v>
+        <v>162002</v>
       </c>
       <c r="P33" s="3">
-        <v>810228</v>
+        <v>810230</v>
       </c>
       <c r="Q33" s="12">
         <f t="shared" si="4"/>
-        <v>0.92379786149667864</v>
+        <v>0.92380014183717918</v>
       </c>
       <c r="R33" s="10">
         <v>881026</v>
@@ -5931,14 +5931,14 @@
       </c>
       <c r="T33" s="11">
         <f t="shared" si="5"/>
-        <v>137065</v>
+        <v>137067</v>
       </c>
       <c r="U33" s="3">
-        <v>816376</v>
+        <v>816378</v>
       </c>
       <c r="V33" s="12">
         <f t="shared" si="6"/>
-        <v>0.92661964573122702</v>
+        <v>0.92662191581179221</v>
       </c>
       <c r="W33" s="10">
         <v>884173</v>
@@ -5948,14 +5948,14 @@
       </c>
       <c r="Y33" s="11">
         <f t="shared" si="7"/>
-        <v>177128</v>
+        <v>177130</v>
       </c>
       <c r="Z33" s="3">
-        <v>820946</v>
+        <v>820948</v>
       </c>
       <c r="AA33" s="12">
         <f t="shared" si="8"/>
-        <v>0.92849023890121052</v>
+        <v>0.92849250090197277</v>
       </c>
       <c r="AB33" s="10">
         <v>884817</v>
@@ -5965,14 +5965,14 @@
       </c>
       <c r="AD33" s="11">
         <f t="shared" si="9"/>
-        <v>222668</v>
+        <v>222671</v>
       </c>
       <c r="AE33" s="3">
-        <v>826023</v>
+        <v>826026</v>
       </c>
       <c r="AF33" s="12">
         <f t="shared" si="10"/>
-        <v>0.93355236167478695</v>
+        <v>0.93355575220638842</v>
       </c>
       <c r="AG33" s="10">
         <v>888089</v>
@@ -5982,14 +5982,14 @@
       </c>
       <c r="AI33" s="11">
         <f t="shared" si="11"/>
-        <v>209151</v>
+        <v>209154</v>
       </c>
       <c r="AJ33" s="3">
-        <v>829765</v>
+        <v>829768</v>
       </c>
       <c r="AK33" s="12">
         <f t="shared" si="12"/>
-        <v>0.93432640197097361</v>
+        <v>0.93432978001078726</v>
       </c>
       <c r="AL33" s="10">
         <v>887648</v>
@@ -5999,14 +5999,14 @@
       </c>
       <c r="AN33" s="11">
         <f t="shared" si="13"/>
-        <v>110951</v>
+        <v>110955</v>
       </c>
       <c r="AO33" s="3">
-        <v>833650</v>
+        <v>833654</v>
       </c>
       <c r="AP33" s="12">
         <f t="shared" si="14"/>
-        <v>0.93916732758931465</v>
+        <v>0.93917183388009662</v>
       </c>
       <c r="AQ33" s="10">
         <v>877839</v>
@@ -6016,14 +6016,14 @@
       </c>
       <c r="AS33" s="11">
         <f t="shared" si="15"/>
-        <v>210334</v>
+        <v>210337</v>
       </c>
       <c r="AT33" s="3">
-        <v>841911</v>
+        <v>841914</v>
       </c>
       <c r="AU33" s="12">
         <f t="shared" si="16"/>
-        <v>0.95907222167162776</v>
+        <v>0.95907563915478811</v>
       </c>
       <c r="AV33" s="10">
         <v>881788</v>
@@ -6033,14 +6033,14 @@
       </c>
       <c r="AX33" s="11">
         <f t="shared" si="17"/>
-        <v>121429</v>
+        <v>121430</v>
       </c>
       <c r="AY33" s="3">
-        <v>847605</v>
+        <v>847606</v>
       </c>
       <c r="AZ33" s="12">
         <f t="shared" si="18"/>
-        <v>0.96123444637486566</v>
+        <v>0.96123558043429935</v>
       </c>
       <c r="BA33" s="10">
         <v>886741</v>
@@ -6050,14 +6050,14 @@
       </c>
       <c r="BC33" s="11">
         <f t="shared" si="19"/>
-        <v>139171</v>
+        <v>139172</v>
       </c>
       <c r="BD33" s="3">
-        <v>853497</v>
+        <v>853498</v>
       </c>
       <c r="BE33" s="12">
         <f t="shared" si="20"/>
-        <v>0.96250990988349472</v>
+        <v>0.96251103760850121</v>
       </c>
       <c r="BF33" s="10">
         <v>893063</v>
@@ -6067,14 +6067,14 @@
       </c>
       <c r="BH33" s="11">
         <f t="shared" si="21"/>
-        <v>834006</v>
+        <v>834008</v>
       </c>
       <c r="BI33" s="3">
-        <v>857129</v>
+        <v>857131</v>
       </c>
       <c r="BJ33" s="12">
         <f t="shared" si="22"/>
-        <v>0.95976319699730028</v>
+        <v>0.95976543648096491</v>
       </c>
     </row>
     <row r="34" spans="1:62" x14ac:dyDescent="0.3">
@@ -6305,11 +6305,11 @@
         <v>7383</v>
       </c>
       <c r="F35" s="3">
-        <v>7385</v>
+        <v>7386</v>
       </c>
       <c r="G35" s="12">
         <f t="shared" si="0"/>
-        <v>0.8965642831127838</v>
+        <v>0.89668568653636027</v>
       </c>
       <c r="H35" s="10">
         <v>8305</v>
@@ -6319,14 +6319,14 @@
       </c>
       <c r="J35" s="11">
         <f t="shared" si="1"/>
-        <v>2374</v>
+        <v>2375</v>
       </c>
       <c r="K35" s="3">
-        <v>7438</v>
+        <v>7439</v>
       </c>
       <c r="L35" s="12">
         <f t="shared" si="2"/>
-        <v>0.89560505719446115</v>
+        <v>0.89572546658639374</v>
       </c>
       <c r="M35" s="10">
         <v>8364</v>
@@ -6336,14 +6336,14 @@
       </c>
       <c r="O35" s="11">
         <f t="shared" si="3"/>
-        <v>2211</v>
+        <v>2212</v>
       </c>
       <c r="P35" s="3">
-        <v>7468</v>
+        <v>7469</v>
       </c>
       <c r="Q35" s="12">
         <f t="shared" si="4"/>
-        <v>0.89287422285987561</v>
+        <v>0.89299378287900522</v>
       </c>
       <c r="R35" s="10">
         <v>8417</v>
@@ -6353,14 +6353,14 @@
       </c>
       <c r="T35" s="11">
         <f t="shared" si="5"/>
-        <v>1952</v>
+        <v>1953</v>
       </c>
       <c r="U35" s="3">
-        <v>7510</v>
+        <v>7511</v>
       </c>
       <c r="V35" s="12">
         <f t="shared" si="6"/>
-        <v>0.89224189141024113</v>
+        <v>0.8923606985861946</v>
       </c>
       <c r="W35" s="10">
         <v>8451</v>
@@ -6370,14 +6370,14 @@
       </c>
       <c r="Y35" s="11">
         <f t="shared" si="7"/>
-        <v>2418</v>
+        <v>2419</v>
       </c>
       <c r="Z35" s="3">
-        <v>7569</v>
+        <v>7570</v>
       </c>
       <c r="AA35" s="12">
         <f t="shared" si="8"/>
-        <v>0.89563365282215124</v>
+        <v>0.89575198201396289</v>
       </c>
       <c r="AB35" s="10">
         <v>8395</v>
@@ -6387,14 +6387,14 @@
       </c>
       <c r="AD35" s="11">
         <f t="shared" si="9"/>
-        <v>2877</v>
+        <v>2878</v>
       </c>
       <c r="AE35" s="3">
-        <v>7588</v>
+        <v>7589</v>
       </c>
       <c r="AF35" s="12">
         <f t="shared" si="10"/>
-        <v>0.90387135199523527</v>
+        <v>0.90399047051816561</v>
       </c>
       <c r="AG35" s="10">
         <v>8265</v>
@@ -6404,14 +6404,14 @@
       </c>
       <c r="AI35" s="11">
         <f t="shared" si="11"/>
-        <v>2735</v>
+        <v>2736</v>
       </c>
       <c r="AJ35" s="3">
-        <v>7588</v>
+        <v>7589</v>
       </c>
       <c r="AK35" s="12">
         <f t="shared" si="12"/>
-        <v>0.91808832425892317</v>
+        <v>0.91820931639443437</v>
       </c>
       <c r="AL35" s="10">
         <v>8043</v>
@@ -6421,14 +6421,14 @@
       </c>
       <c r="AN35" s="11">
         <f t="shared" si="13"/>
-        <v>1712</v>
+        <v>1713</v>
       </c>
       <c r="AO35" s="3">
-        <v>7576</v>
+        <v>7577</v>
       </c>
       <c r="AP35" s="12">
         <f t="shared" si="14"/>
-        <v>0.94193708815118737</v>
+        <v>0.94206141986820835</v>
       </c>
       <c r="AQ35" s="10">
         <v>7976</v>
@@ -6516,11 +6516,11 @@
         <v>1213488</v>
       </c>
       <c r="F36" s="3">
-        <v>1214464</v>
+        <v>1214466</v>
       </c>
       <c r="G36" s="12">
         <f t="shared" si="0"/>
-        <v>0.87391189526850288</v>
+        <v>0.87391333444149655</v>
       </c>
       <c r="H36" s="10">
         <v>1398033</v>
@@ -6530,14 +6530,14 @@
       </c>
       <c r="J36" s="11">
         <f t="shared" si="1"/>
-        <v>374673</v>
+        <v>374677</v>
       </c>
       <c r="K36" s="3">
-        <v>1219838</v>
+        <v>1219842</v>
       </c>
       <c r="L36" s="12">
         <f t="shared" si="2"/>
-        <v>0.87253877412049641</v>
+        <v>0.87254163528328732</v>
       </c>
       <c r="M36" s="10">
         <v>1405014</v>
@@ -6547,14 +6547,14 @@
       </c>
       <c r="O36" s="11">
         <f t="shared" si="3"/>
-        <v>355852</v>
+        <v>355855</v>
       </c>
       <c r="P36" s="3">
-        <v>1224764</v>
+        <v>1224767</v>
       </c>
       <c r="Q36" s="12">
         <f t="shared" si="4"/>
-        <v>0.87170946339324729</v>
+        <v>0.87171159860328795</v>
       </c>
       <c r="R36" s="10">
         <v>1409335</v>
@@ -6564,14 +6564,14 @@
       </c>
       <c r="T36" s="11">
         <f t="shared" si="5"/>
-        <v>320694</v>
+        <v>320696</v>
       </c>
       <c r="U36" s="3">
-        <v>1232417</v>
+        <v>1232419</v>
       </c>
       <c r="V36" s="12">
         <f t="shared" si="6"/>
-        <v>0.87446703587152808</v>
+        <v>0.87446845498054049</v>
       </c>
       <c r="W36" s="10">
         <v>1413902</v>
@@ -6581,14 +6581,14 @@
       </c>
       <c r="Y36" s="11">
         <f t="shared" si="7"/>
-        <v>384041</v>
+        <v>384044</v>
       </c>
       <c r="Z36" s="3">
-        <v>1237576</v>
+        <v>1237579</v>
       </c>
       <c r="AA36" s="12">
         <f t="shared" si="8"/>
-        <v>0.87529121537419141</v>
+        <v>0.87529333716198154</v>
       </c>
       <c r="AB36" s="10">
         <v>1416919</v>
@@ -6598,14 +6598,14 @@
       </c>
       <c r="AD36" s="11">
         <f t="shared" si="9"/>
-        <v>476490</v>
+        <v>476493</v>
       </c>
       <c r="AE36" s="3">
-        <v>1244823</v>
+        <v>1244826</v>
       </c>
       <c r="AF36" s="12">
         <f t="shared" si="10"/>
-        <v>0.87854210438281932</v>
+        <v>0.87854422165275503</v>
       </c>
       <c r="AG36" s="10">
         <v>1419473</v>
@@ -6615,14 +6615,14 @@
       </c>
       <c r="AI36" s="11">
         <f t="shared" si="11"/>
-        <v>414500</v>
+        <v>414504</v>
       </c>
       <c r="AJ36" s="3">
-        <v>1251109</v>
+        <v>1251113</v>
       </c>
       <c r="AK36" s="12">
         <f t="shared" si="12"/>
-        <v>0.88138978339144181</v>
+        <v>0.88139260133866582</v>
       </c>
       <c r="AL36" s="10">
         <v>1415447</v>
@@ -6632,14 +6632,14 @@
       </c>
       <c r="AN36" s="11">
         <f t="shared" si="13"/>
-        <v>261113</v>
+        <v>261118</v>
       </c>
       <c r="AO36" s="3">
-        <v>1259378</v>
+        <v>1259383</v>
       </c>
       <c r="AP36" s="12">
         <f t="shared" si="14"/>
-        <v>0.8897387185814799</v>
+        <v>0.8897422510344789</v>
       </c>
       <c r="AQ36" s="10">
         <v>1379433</v>
@@ -6649,14 +6649,14 @@
       </c>
       <c r="AS36" s="11">
         <f t="shared" si="15"/>
-        <v>413097</v>
+        <v>413101</v>
       </c>
       <c r="AT36" s="3">
-        <v>1269270</v>
+        <v>1269274</v>
       </c>
       <c r="AU36" s="12">
         <f t="shared" si="16"/>
-        <v>0.92013892664594799</v>
+        <v>0.92014182638808839</v>
       </c>
       <c r="AV36" s="10">
         <v>1370415</v>
@@ -6666,14 +6666,14 @@
       </c>
       <c r="AX36" s="11">
         <f t="shared" si="17"/>
-        <v>275207</v>
+        <v>275210</v>
       </c>
       <c r="AY36" s="3">
-        <v>1275417</v>
+        <v>1275420</v>
       </c>
       <c r="AZ36" s="12">
         <f t="shared" si="18"/>
-        <v>0.93067939273869593</v>
+        <v>0.93068158185659089</v>
       </c>
       <c r="BA36" s="10">
         <v>1375391</v>
@@ -6683,14 +6683,14 @@
       </c>
       <c r="BC36" s="11">
         <f t="shared" si="19"/>
-        <v>338572</v>
+        <v>338576</v>
       </c>
       <c r="BD36" s="3">
-        <v>1281938</v>
+        <v>1281942</v>
       </c>
       <c r="BE36" s="12">
         <f t="shared" si="20"/>
-        <v>0.93205350333105275</v>
+        <v>0.93205641159495733</v>
       </c>
       <c r="BF36" s="10">
         <v>1380633</v>
@@ -6700,14 +6700,14 @@
       </c>
       <c r="BH36" s="11">
         <f t="shared" si="21"/>
-        <v>1217300</v>
+        <v>1217306</v>
       </c>
       <c r="BI36" s="3">
-        <v>1281455</v>
+        <v>1281461</v>
       </c>
       <c r="BJ36" s="12">
         <f t="shared" si="22"/>
-        <v>0.92816483453604248</v>
+        <v>0.92816918036871487</v>
       </c>
     </row>
     <row r="37" spans="1:62" x14ac:dyDescent="0.3">
@@ -6727,11 +6727,11 @@
         <v>627302</v>
       </c>
       <c r="F37" s="3">
-        <v>627966</v>
+        <v>627968</v>
       </c>
       <c r="G37" s="12">
         <f t="shared" si="0"/>
-        <v>0.88627664619275581</v>
+        <v>0.8862794688826664</v>
       </c>
       <c r="H37" s="10">
         <v>707340</v>
@@ -6741,14 +6741,14 @@
       </c>
       <c r="J37" s="11">
         <f t="shared" si="1"/>
-        <v>167230</v>
+        <v>167233</v>
       </c>
       <c r="K37" s="3">
-        <v>632193</v>
+        <v>632196</v>
       </c>
       <c r="L37" s="12">
         <f t="shared" si="2"/>
-        <v>0.89376113325981843</v>
+        <v>0.89376537450165405</v>
       </c>
       <c r="M37" s="10">
         <v>710827</v>
@@ -6758,14 +6758,14 @@
       </c>
       <c r="O37" s="11">
         <f t="shared" si="3"/>
-        <v>160110</v>
+        <v>160112</v>
       </c>
       <c r="P37" s="3">
-        <v>636967</v>
+        <v>636969</v>
       </c>
       <c r="Q37" s="12">
         <f t="shared" si="4"/>
-        <v>0.89609286085081175</v>
+        <v>0.89609567447494254</v>
       </c>
       <c r="R37" s="10">
         <v>713357</v>
@@ -6775,14 +6775,14 @@
       </c>
       <c r="T37" s="11">
         <f t="shared" si="5"/>
-        <v>137608</v>
+        <v>137613</v>
       </c>
       <c r="U37" s="3">
-        <v>644562</v>
+        <v>644567</v>
       </c>
       <c r="V37" s="12">
         <f t="shared" si="6"/>
-        <v>0.90356161080637043</v>
+        <v>0.90356861991961945</v>
       </c>
       <c r="W37" s="10">
         <v>709504</v>
@@ -6792,14 +6792,14 @@
       </c>
       <c r="Y37" s="11">
         <f t="shared" si="7"/>
-        <v>170676</v>
+        <v>170678</v>
       </c>
       <c r="Z37" s="3">
-        <v>650131</v>
+        <v>650133</v>
       </c>
       <c r="AA37" s="12">
         <f t="shared" si="8"/>
-        <v>0.91631759651813094</v>
+        <v>0.91632041538877862</v>
       </c>
       <c r="AB37" s="10">
         <v>709880</v>
@@ -6809,14 +6809,14 @@
       </c>
       <c r="AD37" s="11">
         <f t="shared" si="9"/>
-        <v>220782</v>
+        <v>220784</v>
       </c>
       <c r="AE37" s="3">
-        <v>655096</v>
+        <v>655098</v>
       </c>
       <c r="AF37" s="12">
         <f t="shared" si="10"/>
-        <v>0.9228263931932158</v>
+        <v>0.9228292105708007</v>
       </c>
       <c r="AG37" s="10">
         <v>716349</v>
@@ -6826,14 +6826,14 @@
       </c>
       <c r="AI37" s="11">
         <f t="shared" si="11"/>
-        <v>195308</v>
+        <v>195310</v>
       </c>
       <c r="AJ37" s="3">
-        <v>661854</v>
+        <v>661856</v>
       </c>
       <c r="AK37" s="12">
         <f t="shared" si="12"/>
-        <v>0.92392674520380424</v>
+        <v>0.92392953713902026</v>
       </c>
       <c r="AL37" s="10">
         <v>718037</v>
@@ -6843,14 +6843,14 @@
       </c>
       <c r="AN37" s="11">
         <f t="shared" si="13"/>
-        <v>115172</v>
+        <v>115176</v>
       </c>
       <c r="AO37" s="3">
-        <v>668142</v>
+        <v>668146</v>
       </c>
       <c r="AP37" s="12">
         <f t="shared" si="14"/>
-        <v>0.93051193740712523</v>
+        <v>0.93051750815069423</v>
       </c>
       <c r="AQ37" s="10">
         <v>723207</v>
@@ -6860,14 +6860,14 @@
       </c>
       <c r="AS37" s="11">
         <f t="shared" si="15"/>
-        <v>201321</v>
+        <v>201324</v>
       </c>
       <c r="AT37" s="3">
-        <v>675764</v>
+        <v>675767</v>
       </c>
       <c r="AU37" s="12">
         <f t="shared" si="16"/>
-        <v>0.93439914160122894</v>
+        <v>0.93440328979116627</v>
       </c>
       <c r="AV37" s="10">
         <v>726054</v>
@@ -6877,14 +6877,14 @@
       </c>
       <c r="AX37" s="11">
         <f t="shared" si="17"/>
-        <v>124576</v>
+        <v>124579</v>
       </c>
       <c r="AY37" s="3">
-        <v>681062</v>
+        <v>681065</v>
       </c>
       <c r="AZ37" s="12">
         <f t="shared" si="18"/>
-        <v>0.93803215738774248</v>
+        <v>0.93803628931181426</v>
       </c>
       <c r="BA37" s="10">
         <v>731853</v>
@@ -6911,14 +6911,14 @@
       </c>
       <c r="BH37" s="11">
         <f t="shared" si="21"/>
-        <v>630832</v>
+        <v>630833</v>
       </c>
       <c r="BI37" s="3">
-        <v>686238</v>
+        <v>686239</v>
       </c>
       <c r="BJ37" s="12">
         <f t="shared" si="22"/>
-        <v>0.93391126837234617</v>
+        <v>0.93391262928688079</v>
       </c>
     </row>
     <row r="38" spans="1:62" x14ac:dyDescent="0.3">
@@ -6938,11 +6938,11 @@
         <v>28561</v>
       </c>
       <c r="F38" s="3">
-        <v>28618</v>
+        <v>28619</v>
       </c>
       <c r="G38" s="12">
         <f t="shared" si="0"/>
-        <v>0.85803376008155186</v>
+        <v>0.85806374239198868</v>
       </c>
       <c r="H38" s="10">
         <v>33480</v>
@@ -6952,14 +6952,14 @@
       </c>
       <c r="J38" s="11">
         <f t="shared" si="1"/>
-        <v>10369</v>
+        <v>10370</v>
       </c>
       <c r="K38" s="3">
-        <v>28740</v>
+        <v>28741</v>
       </c>
       <c r="L38" s="12">
         <f t="shared" si="2"/>
-        <v>0.85842293906810041</v>
+        <v>0.85845280764635601</v>
       </c>
       <c r="M38" s="10">
         <v>33757</v>
@@ -6969,14 +6969,14 @@
       </c>
       <c r="O38" s="11">
         <f t="shared" si="3"/>
-        <v>10139</v>
+        <v>10140</v>
       </c>
       <c r="P38" s="3">
-        <v>28874</v>
+        <v>28875</v>
       </c>
       <c r="Q38" s="12">
         <f t="shared" si="4"/>
-        <v>0.85534852030689934</v>
+        <v>0.85537814379239863</v>
       </c>
       <c r="R38" s="10">
         <v>34090</v>
@@ -6986,14 +6986,14 @@
       </c>
       <c r="T38" s="11">
         <f t="shared" si="5"/>
-        <v>9320</v>
+        <v>9321</v>
       </c>
       <c r="U38" s="3">
-        <v>29090</v>
+        <v>29091</v>
       </c>
       <c r="V38" s="12">
         <f t="shared" si="6"/>
-        <v>0.85332942211792318</v>
+        <v>0.85335875623349955</v>
       </c>
       <c r="W38" s="10">
         <v>34201</v>
@@ -7003,14 +7003,14 @@
       </c>
       <c r="Y38" s="11">
         <f t="shared" si="7"/>
-        <v>10931</v>
+        <v>10932</v>
       </c>
       <c r="Z38" s="3">
-        <v>29218</v>
+        <v>29219</v>
       </c>
       <c r="AA38" s="12">
         <f t="shared" si="8"/>
-        <v>0.85430250577468492</v>
+        <v>0.85433174468582795</v>
       </c>
       <c r="AB38" s="10">
         <v>34397</v>
@@ -7020,14 +7020,14 @@
       </c>
       <c r="AD38" s="11">
         <f t="shared" si="9"/>
-        <v>12619</v>
+        <v>12621</v>
       </c>
       <c r="AE38" s="3">
-        <v>29383</v>
+        <v>29385</v>
       </c>
       <c r="AF38" s="12">
         <f t="shared" si="10"/>
-        <v>0.85423147367502983</v>
+        <v>0.85428961828066396</v>
       </c>
       <c r="AG38" s="10">
         <v>34642</v>
@@ -7037,14 +7037,14 @@
       </c>
       <c r="AI38" s="11">
         <f t="shared" si="11"/>
-        <v>11338</v>
+        <v>11340</v>
       </c>
       <c r="AJ38" s="3">
-        <v>29634</v>
+        <v>29636</v>
       </c>
       <c r="AK38" s="12">
         <f t="shared" si="12"/>
-        <v>0.85543559840655847</v>
+        <v>0.85549333179377629</v>
       </c>
       <c r="AL38" s="10">
         <v>34765</v>
@@ -7054,14 +7054,14 @@
       </c>
       <c r="AN38" s="11">
         <f t="shared" si="13"/>
-        <v>8565</v>
+        <v>8566</v>
       </c>
       <c r="AO38" s="3">
-        <v>29814</v>
+        <v>29815</v>
       </c>
       <c r="AP38" s="12">
         <f t="shared" si="14"/>
-        <v>0.85758665324320438</v>
+        <v>0.85761541780526396</v>
       </c>
       <c r="AQ38" s="10">
         <v>35044</v>
@@ -7071,14 +7071,14 @@
       </c>
       <c r="AS38" s="11">
         <f t="shared" si="15"/>
-        <v>11637</v>
+        <v>11638</v>
       </c>
       <c r="AT38" s="3">
-        <v>30109</v>
+        <v>30110</v>
       </c>
       <c r="AU38" s="12">
         <f t="shared" si="16"/>
-        <v>0.85917703458509298</v>
+        <v>0.85920557014039489</v>
       </c>
       <c r="AV38" s="10">
         <v>35365</v>
@@ -7088,14 +7088,14 @@
       </c>
       <c r="AX38" s="11">
         <f t="shared" si="17"/>
-        <v>8443</v>
+        <v>8444</v>
       </c>
       <c r="AY38" s="3">
-        <v>30348</v>
+        <v>30349</v>
       </c>
       <c r="AZ38" s="12">
         <f t="shared" si="18"/>
-        <v>0.85813657571044821</v>
+        <v>0.85816485225505446</v>
       </c>
       <c r="BA38" s="10">
         <v>35756</v>
@@ -7105,14 +7105,14 @@
       </c>
       <c r="BC38" s="11">
         <f t="shared" si="19"/>
-        <v>9277</v>
+        <v>9278</v>
       </c>
       <c r="BD38" s="3">
-        <v>30590</v>
+        <v>30591</v>
       </c>
       <c r="BE38" s="12">
         <f t="shared" si="20"/>
-        <v>0.85552075176194209</v>
+        <v>0.85554871909609576</v>
       </c>
       <c r="BF38" s="10">
         <v>36052</v>
@@ -7122,14 +7122,14 @@
       </c>
       <c r="BH38" s="11">
         <f t="shared" si="21"/>
-        <v>28625</v>
+        <v>28626</v>
       </c>
       <c r="BI38" s="3">
-        <v>30643</v>
+        <v>30644</v>
       </c>
       <c r="BJ38" s="12">
         <f t="shared" si="22"/>
-        <v>0.84996671474536778</v>
+        <v>0.84999445245756133</v>
       </c>
     </row>
     <row r="39" spans="1:62" x14ac:dyDescent="0.3">
@@ -7360,11 +7360,11 @@
         <v>263483</v>
       </c>
       <c r="F40" s="3">
-        <v>263634</v>
+        <v>263637</v>
       </c>
       <c r="G40" s="12">
         <f t="shared" si="0"/>
-        <v>0.9019418671483701</v>
+        <v>0.90195213071680758</v>
       </c>
       <c r="H40" s="10">
         <v>292465</v>
@@ -7374,14 +7374,14 @@
       </c>
       <c r="J40" s="11">
         <f t="shared" si="1"/>
-        <v>94526</v>
+        <v>94528</v>
       </c>
       <c r="K40" s="3">
-        <v>265353</v>
+        <v>265355</v>
       </c>
       <c r="L40" s="12">
         <f t="shared" si="2"/>
-        <v>0.90729830919939136</v>
+        <v>0.9073051476245021</v>
       </c>
       <c r="M40" s="10">
         <v>295913</v>
@@ -7391,14 +7391,14 @@
       </c>
       <c r="O40" s="11">
         <f t="shared" si="3"/>
-        <v>89907</v>
+        <v>89908</v>
       </c>
       <c r="P40" s="3">
-        <v>266987</v>
+        <v>266988</v>
       </c>
       <c r="Q40" s="12">
         <f t="shared" si="4"/>
-        <v>0.90224829595185074</v>
+        <v>0.90225167532349038</v>
       </c>
       <c r="R40" s="10">
         <v>298709</v>
@@ -7408,14 +7408,14 @@
       </c>
       <c r="T40" s="11">
         <f t="shared" si="5"/>
-        <v>81293</v>
+        <v>81294</v>
       </c>
       <c r="U40" s="3">
-        <v>269536</v>
+        <v>269537</v>
       </c>
       <c r="V40" s="12">
         <f t="shared" si="6"/>
-        <v>0.90233638758792001</v>
+        <v>0.90233973532769352</v>
       </c>
       <c r="W40" s="10">
         <v>300746</v>
@@ -7425,14 +7425,14 @@
       </c>
       <c r="Y40" s="11">
         <f t="shared" si="7"/>
-        <v>112187</v>
+        <v>112188</v>
       </c>
       <c r="Z40" s="3">
-        <v>271710</v>
+        <v>271711</v>
       </c>
       <c r="AA40" s="12">
         <f t="shared" si="8"/>
-        <v>0.90345341251421463</v>
+        <v>0.90345673757921963</v>
       </c>
       <c r="AB40" s="10">
         <v>301836</v>
@@ -7442,14 +7442,14 @@
       </c>
       <c r="AD40" s="11">
         <f t="shared" si="9"/>
-        <v>123080</v>
+        <v>123081</v>
       </c>
       <c r="AE40" s="3">
-        <v>273068</v>
+        <v>273069</v>
       </c>
       <c r="AF40" s="12">
         <f t="shared" si="10"/>
-        <v>0.90468996408645752</v>
+        <v>0.90469327714387948</v>
       </c>
       <c r="AG40" s="10">
         <v>303421</v>
@@ -7459,14 +7459,14 @@
       </c>
       <c r="AI40" s="11">
         <f t="shared" si="11"/>
-        <v>104565</v>
+        <v>104566</v>
       </c>
       <c r="AJ40" s="3">
-        <v>275256</v>
+        <v>275257</v>
       </c>
       <c r="AK40" s="12">
         <f t="shared" si="12"/>
-        <v>0.90717517904166156</v>
+        <v>0.90717847479245006</v>
       </c>
       <c r="AL40" s="10">
         <v>303850</v>
@@ -7476,14 +7476,14 @@
       </c>
       <c r="AN40" s="11">
         <f t="shared" si="13"/>
-        <v>62706</v>
+        <v>62707</v>
       </c>
       <c r="AO40" s="3">
-        <v>277519</v>
+        <v>277520</v>
       </c>
       <c r="AP40" s="12">
         <f t="shared" si="14"/>
-        <v>0.91334210959354944</v>
+        <v>0.91334540069113046</v>
       </c>
       <c r="AQ40" s="10">
         <v>302709</v>
@@ -7493,14 +7493,14 @@
       </c>
       <c r="AS40" s="11">
         <f t="shared" si="15"/>
-        <v>107025</v>
+        <v>107026</v>
       </c>
       <c r="AT40" s="3">
-        <v>279345</v>
+        <v>279346</v>
       </c>
       <c r="AU40" s="12">
         <f t="shared" si="16"/>
-        <v>0.92281696282568404</v>
+        <v>0.92282026632838798</v>
       </c>
       <c r="AV40" s="10">
         <v>301724</v>
@@ -7510,14 +7510,14 @@
       </c>
       <c r="AX40" s="11">
         <f t="shared" si="17"/>
-        <v>70557</v>
+        <v>70558</v>
       </c>
       <c r="AY40" s="3">
-        <v>280797</v>
+        <v>280798</v>
       </c>
       <c r="AZ40" s="12">
         <f t="shared" si="18"/>
-        <v>0.93064191115058792</v>
+        <v>0.93064522543781736</v>
       </c>
       <c r="BA40" s="10">
         <v>302553</v>
@@ -7527,14 +7527,14 @@
       </c>
       <c r="BC40" s="11">
         <f t="shared" si="19"/>
-        <v>83696</v>
+        <v>83697</v>
       </c>
       <c r="BD40" s="3">
-        <v>282391</v>
+        <v>282392</v>
       </c>
       <c r="BE40" s="12">
         <f t="shared" si="20"/>
-        <v>0.93336043602277952</v>
+        <v>0.9333637412288095</v>
       </c>
       <c r="BF40" s="10">
         <v>304085</v>
@@ -7544,14 +7544,14 @@
       </c>
       <c r="BH40" s="11">
         <f t="shared" si="21"/>
-        <v>272360</v>
+        <v>272364</v>
       </c>
       <c r="BI40" s="3">
-        <v>283645</v>
+        <v>283649</v>
       </c>
       <c r="BJ40" s="12">
         <f t="shared" si="22"/>
-        <v>0.93278195241462092</v>
+        <v>0.93279510663136955</v>
       </c>
     </row>
     <row r="41" spans="1:62" x14ac:dyDescent="0.3">
@@ -7571,11 +7571,11 @@
         <v>762739</v>
       </c>
       <c r="F41" s="3">
-        <v>763658</v>
+        <v>763701</v>
       </c>
       <c r="G41" s="12">
         <f t="shared" si="0"/>
-        <v>0.87096229690304949</v>
+        <v>0.87101133898571848</v>
       </c>
       <c r="H41" s="10">
         <v>885438</v>
@@ -7585,14 +7585,14 @@
       </c>
       <c r="J41" s="11">
         <f t="shared" si="1"/>
-        <v>217369</v>
+        <v>217417</v>
       </c>
       <c r="K41" s="3">
-        <v>768903</v>
+        <v>768951</v>
       </c>
       <c r="L41" s="12">
         <f t="shared" si="2"/>
-        <v>0.86838717109498353</v>
+        <v>0.86844138155353623</v>
       </c>
       <c r="M41" s="10">
         <v>894344</v>
@@ -7602,14 +7602,14 @@
       </c>
       <c r="O41" s="11">
         <f t="shared" si="3"/>
-        <v>206424</v>
+        <v>206473</v>
       </c>
       <c r="P41" s="3">
-        <v>773368</v>
+        <v>773417</v>
       </c>
       <c r="Q41" s="12">
         <f t="shared" si="4"/>
-        <v>0.86473213886379285</v>
+        <v>0.8647869276251644</v>
       </c>
       <c r="R41" s="10">
         <v>899235</v>
@@ -7619,14 +7619,14 @@
       </c>
       <c r="T41" s="11">
         <f t="shared" si="5"/>
-        <v>170746</v>
+        <v>170800</v>
       </c>
       <c r="U41" s="3">
-        <v>780203</v>
+        <v>780257</v>
       </c>
       <c r="V41" s="12">
         <f t="shared" si="6"/>
-        <v>0.86762970747357471</v>
+        <v>0.86768975851696162</v>
       </c>
       <c r="W41" s="10">
         <v>900188</v>
@@ -7636,14 +7636,14 @@
       </c>
       <c r="Y41" s="11">
         <f t="shared" si="7"/>
-        <v>227406</v>
+        <v>227456</v>
       </c>
       <c r="Z41" s="3">
-        <v>786202</v>
+        <v>786252</v>
       </c>
       <c r="AA41" s="12">
         <f t="shared" si="8"/>
-        <v>0.87337533937355305</v>
+        <v>0.87343088332659402</v>
       </c>
       <c r="AB41" s="10">
         <v>900385</v>
@@ -7653,14 +7653,14 @@
       </c>
       <c r="AD41" s="11">
         <f t="shared" si="9"/>
-        <v>278249</v>
+        <v>278300</v>
       </c>
       <c r="AE41" s="3">
-        <v>790767</v>
+        <v>790818</v>
       </c>
       <c r="AF41" s="12">
         <f t="shared" si="10"/>
-        <v>0.87825430232622714</v>
+        <v>0.87831094476251825</v>
       </c>
       <c r="AG41" s="10">
         <v>896586</v>
@@ -7670,14 +7670,14 @@
       </c>
       <c r="AI41" s="11">
         <f t="shared" si="11"/>
-        <v>232806</v>
+        <v>232852</v>
       </c>
       <c r="AJ41" s="3">
-        <v>796616</v>
+        <v>796662</v>
       </c>
       <c r="AK41" s="12">
         <f t="shared" si="12"/>
-        <v>0.88849926275895452</v>
+        <v>0.88855056848980463</v>
       </c>
       <c r="AL41" s="10">
         <v>888836</v>
@@ -7687,14 +7687,14 @@
       </c>
       <c r="AN41" s="11">
         <f t="shared" si="13"/>
-        <v>136927</v>
+        <v>136975</v>
       </c>
       <c r="AO41" s="3">
-        <v>802452</v>
+        <v>802500</v>
       </c>
       <c r="AP41" s="12">
         <f t="shared" si="14"/>
-        <v>0.90281221732693095</v>
+        <v>0.90286622054012211</v>
       </c>
       <c r="AQ41" s="10">
         <v>877850</v>
@@ -7704,14 +7704,14 @@
       </c>
       <c r="AS41" s="11">
         <f t="shared" si="15"/>
-        <v>256399</v>
+        <v>256439</v>
       </c>
       <c r="AT41" s="3">
-        <v>809937</v>
+        <v>809977</v>
       </c>
       <c r="AU41" s="12">
         <f t="shared" si="16"/>
-        <v>0.92263712479352966</v>
+        <v>0.92268269066469211</v>
       </c>
       <c r="AV41" s="10">
         <v>870770</v>
@@ -7721,14 +7721,14 @@
       </c>
       <c r="AX41" s="11">
         <f t="shared" si="17"/>
-        <v>141854</v>
+        <v>141878</v>
       </c>
       <c r="AY41" s="3">
-        <v>814212</v>
+        <v>814236</v>
       </c>
       <c r="AZ41" s="12">
         <f t="shared" si="18"/>
-        <v>0.9350482905933829</v>
+        <v>0.93507585240649083</v>
       </c>
       <c r="BA41" s="10">
         <v>867846</v>
@@ -7738,14 +7738,14 @@
       </c>
       <c r="BC41" s="11">
         <f t="shared" si="19"/>
-        <v>163663</v>
+        <v>163691</v>
       </c>
       <c r="BD41" s="3">
-        <v>820719</v>
+        <v>820747</v>
       </c>
       <c r="BE41" s="12">
         <f t="shared" si="20"/>
-        <v>0.94569658672160728</v>
+        <v>0.94572885051034405</v>
       </c>
       <c r="BF41" s="10">
         <v>876639</v>
@@ -7755,14 +7755,14 @@
       </c>
       <c r="BH41" s="11">
         <f t="shared" si="21"/>
-        <v>773468</v>
+        <v>773500</v>
       </c>
       <c r="BI41" s="3">
-        <v>823791</v>
+        <v>823823</v>
       </c>
       <c r="BJ41" s="12">
         <f t="shared" si="22"/>
-        <v>0.93971520774229755</v>
+        <v>0.93975171079543574</v>
       </c>
     </row>
     <row r="42" spans="1:62" x14ac:dyDescent="0.3">
@@ -7847,14 +7847,14 @@
       </c>
       <c r="Y42" s="11">
         <f t="shared" si="7"/>
-        <v>5566</v>
+        <v>5567</v>
       </c>
       <c r="Z42" s="3">
-        <v>17587</v>
+        <v>17588</v>
       </c>
       <c r="AA42" s="12">
         <f t="shared" si="8"/>
-        <v>0.83473349470786462</v>
+        <v>0.83478095780530637</v>
       </c>
       <c r="AB42" s="10">
         <v>21025</v>
@@ -7864,14 +7864,14 @@
       </c>
       <c r="AD42" s="11">
         <f t="shared" si="9"/>
-        <v>6690</v>
+        <v>6691</v>
       </c>
       <c r="AE42" s="3">
-        <v>17733</v>
+        <v>17734</v>
       </c>
       <c r="AF42" s="12">
         <f t="shared" si="10"/>
-        <v>0.84342449464922709</v>
+        <v>0.8434720570749108</v>
       </c>
       <c r="AG42" s="10">
         <v>20898</v>
@@ -7881,14 +7881,14 @@
       </c>
       <c r="AI42" s="11">
         <f t="shared" si="11"/>
-        <v>5905</v>
+        <v>5906</v>
       </c>
       <c r="AJ42" s="3">
-        <v>17869</v>
+        <v>17870</v>
       </c>
       <c r="AK42" s="12">
         <f t="shared" si="12"/>
-        <v>0.85505790027753847</v>
+        <v>0.85510575174657866</v>
       </c>
       <c r="AL42" s="10">
         <v>20773</v>
@@ -7898,14 +7898,14 @@
       </c>
       <c r="AN42" s="11">
         <f t="shared" si="13"/>
-        <v>3443</v>
+        <v>3444</v>
       </c>
       <c r="AO42" s="3">
-        <v>17889</v>
+        <v>17890</v>
       </c>
       <c r="AP42" s="12">
         <f t="shared" si="14"/>
-        <v>0.86116593655225537</v>
+        <v>0.86121407596399169</v>
       </c>
       <c r="AQ42" s="10">
         <v>20391</v>
@@ -7915,14 +7915,14 @@
       </c>
       <c r="AS42" s="11">
         <f t="shared" si="15"/>
-        <v>6411</v>
+        <v>6412</v>
       </c>
       <c r="AT42" s="3">
-        <v>17963</v>
+        <v>17964</v>
       </c>
       <c r="AU42" s="12">
         <f t="shared" si="16"/>
-        <v>0.88092786033053794</v>
+        <v>0.88097690157422393</v>
       </c>
       <c r="AV42" s="10">
         <v>19656</v>
@@ -7932,14 +7932,14 @@
       </c>
       <c r="AX42" s="11">
         <f t="shared" si="17"/>
-        <v>3554</v>
+        <v>3555</v>
       </c>
       <c r="AY42" s="3">
-        <v>18002</v>
+        <v>18003</v>
       </c>
       <c r="AZ42" s="12">
         <f t="shared" si="18"/>
-        <v>0.91585266585266589</v>
+        <v>0.91590354090354087</v>
       </c>
       <c r="BA42" s="10">
         <v>19500</v>
@@ -7949,14 +7949,14 @@
       </c>
       <c r="BC42" s="11">
         <f t="shared" si="19"/>
-        <v>4014</v>
+        <v>4015</v>
       </c>
       <c r="BD42" s="3">
-        <v>18075</v>
+        <v>18076</v>
       </c>
       <c r="BE42" s="12">
         <f t="shared" si="20"/>
-        <v>0.92692307692307696</v>
+        <v>0.92697435897435898</v>
       </c>
       <c r="BF42" s="10">
         <v>19681</v>
@@ -7966,14 +7966,14 @@
       </c>
       <c r="BH42" s="11">
         <f t="shared" si="21"/>
-        <v>16671</v>
+        <v>16672</v>
       </c>
       <c r="BI42" s="3">
-        <v>18114</v>
+        <v>18115</v>
       </c>
       <c r="BJ42" s="12">
         <f t="shared" si="22"/>
-        <v>0.92038006198872013</v>
+        <v>0.92043087241501953</v>
       </c>
     </row>
     <row r="43" spans="1:62" x14ac:dyDescent="0.3">
@@ -8204,11 +8204,11 @@
         <v>275094</v>
       </c>
       <c r="F44" s="3">
-        <v>275294</v>
+        <v>275297</v>
       </c>
       <c r="G44" s="12">
         <f t="shared" si="0"/>
-        <v>0.85477776225296132</v>
+        <v>0.85478707714281277</v>
       </c>
       <c r="H44" s="10">
         <v>324349</v>
@@ -8218,14 +8218,14 @@
       </c>
       <c r="J44" s="11">
         <f t="shared" si="1"/>
-        <v>97770</v>
+        <v>97772</v>
       </c>
       <c r="K44" s="3">
-        <v>277801</v>
+        <v>277803</v>
       </c>
       <c r="L44" s="12">
         <f t="shared" si="2"/>
-        <v>0.85648791887750542</v>
+        <v>0.85649408507502722</v>
       </c>
       <c r="M44" s="10">
         <v>327844</v>
@@ -8235,14 +8235,14 @@
       </c>
       <c r="O44" s="11">
         <f t="shared" si="3"/>
-        <v>92274</v>
+        <v>92276</v>
       </c>
       <c r="P44" s="3">
-        <v>279389</v>
+        <v>279391</v>
       </c>
       <c r="Q44" s="12">
         <f t="shared" si="4"/>
-        <v>0.85220104683935038</v>
+        <v>0.8522071473017655</v>
       </c>
       <c r="R44" s="10">
         <v>331330</v>
@@ -8252,14 +8252,14 @@
       </c>
       <c r="T44" s="11">
         <f t="shared" si="5"/>
-        <v>80234</v>
+        <v>80236</v>
       </c>
       <c r="U44" s="3">
-        <v>283333</v>
+        <v>283335</v>
       </c>
       <c r="V44" s="12">
         <f t="shared" si="6"/>
-        <v>0.85513838167385992</v>
+        <v>0.85514441795189089</v>
       </c>
       <c r="W44" s="10">
         <v>334631</v>
@@ -8269,14 +8269,14 @@
       </c>
       <c r="Y44" s="11">
         <f t="shared" si="7"/>
-        <v>99414</v>
+        <v>99416</v>
       </c>
       <c r="Z44" s="3">
-        <v>286148</v>
+        <v>286150</v>
       </c>
       <c r="AA44" s="12">
         <f t="shared" si="8"/>
-        <v>0.85511503716033477</v>
+        <v>0.85512101389291484</v>
       </c>
       <c r="AB44" s="10">
         <v>337626</v>
@@ -8286,14 +8286,14 @@
       </c>
       <c r="AD44" s="11">
         <f t="shared" si="9"/>
-        <v>124388</v>
+        <v>124390</v>
       </c>
       <c r="AE44" s="3">
-        <v>289059</v>
+        <v>289061</v>
       </c>
       <c r="AF44" s="12">
         <f t="shared" si="10"/>
-        <v>0.85615148122478724</v>
+        <v>0.85615740493919312</v>
       </c>
       <c r="AG44" s="10">
         <v>342262</v>
@@ -8303,14 +8303,14 @@
       </c>
       <c r="AI44" s="11">
         <f t="shared" si="11"/>
-        <v>109857</v>
+        <v>109859</v>
       </c>
       <c r="AJ44" s="3">
-        <v>292509</v>
+        <v>292511</v>
       </c>
       <c r="AK44" s="12">
         <f t="shared" si="12"/>
-        <v>0.85463475349293816</v>
+        <v>0.85464059696957306</v>
       </c>
       <c r="AL44" s="10">
         <v>346374</v>
@@ -8320,14 +8320,14 @@
       </c>
       <c r="AN44" s="11">
         <f t="shared" si="13"/>
-        <v>72048</v>
+        <v>72050</v>
       </c>
       <c r="AO44" s="3">
-        <v>296160</v>
+        <v>296162</v>
       </c>
       <c r="AP44" s="12">
         <f t="shared" si="14"/>
-        <v>0.85502953454935993</v>
+        <v>0.8550353086548067</v>
       </c>
       <c r="AQ44" s="10">
         <v>350234</v>
@@ -8337,14 +8337,14 @@
       </c>
       <c r="AS44" s="11">
         <f t="shared" si="15"/>
-        <v>113560</v>
+        <v>113562</v>
       </c>
       <c r="AT44" s="3">
-        <v>300509</v>
+        <v>300511</v>
       </c>
       <c r="AU44" s="12">
         <f t="shared" si="16"/>
-        <v>0.85802349286477042</v>
+        <v>0.858029203332629</v>
       </c>
       <c r="AV44" s="10">
         <v>351952</v>
@@ -8354,14 +8354,14 @@
       </c>
       <c r="AX44" s="11">
         <f t="shared" si="17"/>
-        <v>77766</v>
+        <v>77768</v>
       </c>
       <c r="AY44" s="3">
-        <v>303219</v>
+        <v>303221</v>
       </c>
       <c r="AZ44" s="12">
         <f t="shared" si="18"/>
-        <v>0.86153509569486753</v>
+        <v>0.86154077828794839</v>
       </c>
       <c r="BA44" s="10">
         <v>353580</v>
@@ -8371,14 +8371,14 @@
       </c>
       <c r="BC44" s="11">
         <f t="shared" si="19"/>
-        <v>84506</v>
+        <v>84508</v>
       </c>
       <c r="BD44" s="3">
-        <v>306112</v>
+        <v>306114</v>
       </c>
       <c r="BE44" s="12">
         <f t="shared" si="20"/>
-        <v>0.86575032524464057</v>
+        <v>0.86575598167317158</v>
       </c>
       <c r="BF44" s="10">
         <v>357819</v>
@@ -8388,14 +8388,14 @@
       </c>
       <c r="BH44" s="11">
         <f t="shared" si="21"/>
-        <v>278260</v>
+        <v>278262</v>
       </c>
       <c r="BI44" s="3">
-        <v>306787</v>
+        <v>306789</v>
       </c>
       <c r="BJ44" s="12">
         <f t="shared" si="22"/>
-        <v>0.85738040741268629</v>
+        <v>0.85738599683079997</v>
       </c>
     </row>
     <row r="45" spans="1:62" x14ac:dyDescent="0.3">
@@ -8415,11 +8415,11 @@
         <v>241970</v>
       </c>
       <c r="F45" s="3">
-        <v>242208</v>
+        <v>242215</v>
       </c>
       <c r="G45" s="12">
         <f t="shared" si="0"/>
-        <v>0.86446049738743114</v>
+        <v>0.8644854809696485</v>
       </c>
       <c r="H45" s="10">
         <v>279810</v>
@@ -8429,14 +8429,14 @@
       </c>
       <c r="J45" s="11">
         <f t="shared" si="1"/>
-        <v>73560</v>
+        <v>73565</v>
       </c>
       <c r="K45" s="3">
-        <v>243489</v>
+        <v>243494</v>
       </c>
       <c r="L45" s="12">
         <f t="shared" si="2"/>
-        <v>0.87019406025517321</v>
+        <v>0.87021192952360527</v>
       </c>
       <c r="M45" s="10">
         <v>281946</v>
@@ -8446,14 +8446,14 @@
       </c>
       <c r="O45" s="11">
         <f t="shared" si="3"/>
-        <v>68008</v>
+        <v>68013</v>
       </c>
       <c r="P45" s="3">
-        <v>245099</v>
+        <v>245104</v>
       </c>
       <c r="Q45" s="12">
         <f t="shared" si="4"/>
-        <v>0.86931185404297273</v>
+        <v>0.86932958793527837</v>
       </c>
       <c r="R45" s="10">
         <v>285278</v>
@@ -8463,14 +8463,14 @@
       </c>
       <c r="T45" s="11">
         <f t="shared" si="5"/>
-        <v>56327</v>
+        <v>56332</v>
       </c>
       <c r="U45" s="3">
-        <v>247501</v>
+        <v>247506</v>
       </c>
       <c r="V45" s="12">
         <f t="shared" si="6"/>
-        <v>0.86757829205196335</v>
+        <v>0.86759581881533099</v>
       </c>
       <c r="W45" s="10">
         <v>286753</v>
@@ -8480,14 +8480,14 @@
       </c>
       <c r="Y45" s="11">
         <f t="shared" si="7"/>
-        <v>74233</v>
+        <v>74236</v>
       </c>
       <c r="Z45" s="3">
-        <v>248928</v>
+        <v>248931</v>
       </c>
       <c r="AA45" s="12">
         <f t="shared" si="8"/>
-        <v>0.86809205134732681</v>
+        <v>0.86810251331285115</v>
       </c>
       <c r="AB45" s="10">
         <v>287263</v>
@@ -8497,14 +8497,14 @@
       </c>
       <c r="AD45" s="11">
         <f t="shared" si="9"/>
-        <v>98461</v>
+        <v>98464</v>
       </c>
       <c r="AE45" s="3">
-        <v>249898</v>
+        <v>249901</v>
       </c>
       <c r="AF45" s="12">
         <f t="shared" si="10"/>
-        <v>0.86992755767363006</v>
+        <v>0.8699380010652259</v>
       </c>
       <c r="AG45" s="10">
         <v>287909</v>
@@ -8514,14 +8514,14 @@
       </c>
       <c r="AI45" s="11">
         <f t="shared" si="11"/>
-        <v>80950</v>
+        <v>80953</v>
       </c>
       <c r="AJ45" s="3">
-        <v>251715</v>
+        <v>251718</v>
       </c>
       <c r="AK45" s="12">
         <f t="shared" si="12"/>
-        <v>0.87428666696768775</v>
+        <v>0.87429708692677199</v>
       </c>
       <c r="AL45" s="10">
         <v>286336</v>
@@ -8531,14 +8531,14 @@
       </c>
       <c r="AN45" s="11">
         <f t="shared" si="13"/>
-        <v>46920</v>
+        <v>46923</v>
       </c>
       <c r="AO45" s="3">
-        <v>253959</v>
+        <v>253962</v>
       </c>
       <c r="AP45" s="12">
         <f t="shared" si="14"/>
-        <v>0.88692654783191771</v>
+        <v>0.886937025033527</v>
       </c>
       <c r="AQ45" s="10">
         <v>286760</v>
@@ -8548,14 +8548,14 @@
       </c>
       <c r="AS45" s="11">
         <f t="shared" si="15"/>
-        <v>82132</v>
+        <v>82135</v>
       </c>
       <c r="AT45" s="3">
-        <v>256148</v>
+        <v>256151</v>
       </c>
       <c r="AU45" s="12">
         <f t="shared" si="16"/>
-        <v>0.89324870972241599</v>
+        <v>0.89325917143255684</v>
       </c>
       <c r="AV45" s="10">
         <v>287132</v>
@@ -8565,14 +8565,14 @@
       </c>
       <c r="AX45" s="11">
         <f t="shared" si="17"/>
-        <v>51837</v>
+        <v>51840</v>
       </c>
       <c r="AY45" s="3">
-        <v>256808</v>
+        <v>256811</v>
       </c>
       <c r="AZ45" s="12">
         <f t="shared" si="18"/>
-        <v>0.89439003663820127</v>
+        <v>0.89440048479444989</v>
       </c>
       <c r="BA45" s="10">
         <v>284734</v>
@@ -8582,14 +8582,14 @@
       </c>
       <c r="BC45" s="11">
         <f t="shared" si="19"/>
-        <v>56053</v>
+        <v>56055</v>
       </c>
       <c r="BD45" s="3">
-        <v>257745</v>
+        <v>257747</v>
       </c>
       <c r="BE45" s="12">
         <f t="shared" si="20"/>
-        <v>0.90521328678696611</v>
+        <v>0.90522031088665211</v>
       </c>
       <c r="BF45" s="10">
         <v>283250</v>
@@ -8599,14 +8599,14 @@
       </c>
       <c r="BH45" s="11">
         <f t="shared" si="21"/>
-        <v>233671</v>
+        <v>233674</v>
       </c>
       <c r="BI45" s="3">
-        <v>257127</v>
+        <v>257130</v>
       </c>
       <c r="BJ45" s="12">
         <f t="shared" si="22"/>
-        <v>0.90777405119152688</v>
+        <v>0.90778464254192415</v>
       </c>
     </row>
     <row r="46" spans="1:62" x14ac:dyDescent="0.3">
@@ -8774,10 +8774,10 @@
       </c>
       <c r="BC46" s="11">
         <f t="shared" si="19"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BD46" s="3">
-        <v>2788</v>
+        <v>2789</v>
       </c>
       <c r="BE46" s="13">
         <v>0</v>
@@ -8790,10 +8790,10 @@
       </c>
       <c r="BH46" s="11">
         <f t="shared" si="21"/>
-        <v>2910</v>
+        <v>2911</v>
       </c>
       <c r="BI46" s="3">
-        <v>2910</v>
+        <v>2911</v>
       </c>
       <c r="BJ46" s="13">
         <v>0</v>
@@ -9011,10 +9011,10 @@
       </c>
     </row>
     <row r="48" spans="1:62" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A48" s="27" t="s">
+      <c r="A48" s="24" t="s">
         <v>44</v>
       </c>
-      <c r="B48" s="27"/>
+      <c r="B48" s="24"/>
       <c r="C48" s="6">
         <f>SUM(C10:C47)</f>
         <v>10233313</v>
@@ -9025,15 +9025,15 @@
       </c>
       <c r="E48" s="7">
         <f t="shared" ref="E48" si="23">F48-D48</f>
-        <v>2915024</v>
+        <v>2915108</v>
       </c>
       <c r="F48" s="8">
         <f>SUM(F10:F47)</f>
-        <v>8977002</v>
+        <v>8977086</v>
       </c>
       <c r="G48" s="5">
         <f>F48/C48</f>
-        <v>0.87723320883471467</v>
+        <v>0.87724141732007999</v>
       </c>
       <c r="H48" s="6">
         <f>SUM(H10:H47)</f>
@@ -9045,15 +9045,15 @@
       </c>
       <c r="J48" s="7">
         <f>K48-I48</f>
-        <v>2519967</v>
+        <v>2520054</v>
       </c>
       <c r="K48" s="8">
         <f>SUM(K10:K47)</f>
-        <v>9038375</v>
+        <v>9038462</v>
       </c>
       <c r="L48" s="5">
         <f>K48/H48</f>
-        <v>0.87870111236923198</v>
+        <v>0.8787095704158141</v>
       </c>
       <c r="M48" s="6">
         <f>SUM(M10:M47)</f>
@@ -9065,15 +9065,15 @@
       </c>
       <c r="O48" s="7">
         <f>P48-N48</f>
-        <v>2400776</v>
+        <v>2400860</v>
       </c>
       <c r="P48" s="8">
         <f>SUM(P10:P47)</f>
-        <v>9089440</v>
+        <v>9089524</v>
       </c>
       <c r="Q48" s="5">
         <f>P48/M48</f>
-        <v>0.87749467847299567</v>
+        <v>0.87750278783429758</v>
       </c>
       <c r="R48" s="6">
         <f>SUM(R10:R47)</f>
@@ -9085,15 +9085,15 @@
       </c>
       <c r="T48" s="7">
         <f>U48-S48</f>
-        <v>2087775</v>
+        <v>2087868</v>
       </c>
       <c r="U48" s="8">
         <f>SUM(U10:U47)</f>
-        <v>9168250</v>
+        <v>9168343</v>
       </c>
       <c r="V48" s="5">
         <f>U48/R48</f>
-        <v>0.87929982481617974</v>
+        <v>0.87930874417196825</v>
       </c>
       <c r="W48" s="6">
         <f>SUM(W10:W47)</f>
@@ -9105,15 +9105,15 @@
       </c>
       <c r="Y48" s="7">
         <f>Z48-X48</f>
-        <v>2662272</v>
+        <v>2662360</v>
       </c>
       <c r="Z48" s="8">
         <f>SUM(Z10:Z47)</f>
-        <v>9229491</v>
+        <v>9229579</v>
       </c>
       <c r="AA48" s="5">
         <f>Z48/W48</f>
-        <v>0.88270726999736326</v>
+        <v>0.88271568630545216</v>
       </c>
       <c r="AB48" s="6">
         <f>SUM(AB10:AB47)</f>
@@ -9125,15 +9125,15 @@
       </c>
       <c r="AD48" s="7">
         <f>AE48-AC48</f>
-        <v>3305487</v>
+        <v>3305578</v>
       </c>
       <c r="AE48" s="8">
         <f>SUM(AE10:AE47)</f>
-        <v>9295840</v>
+        <v>9295931</v>
       </c>
       <c r="AF48" s="5">
         <f>AE48/AB48</f>
-        <v>0.88753151430796839</v>
+        <v>0.88754020264251399</v>
       </c>
       <c r="AG48" s="6">
         <f>SUM(AG10:AG47)</f>
@@ -9145,15 +9145,15 @@
       </c>
       <c r="AI48" s="7">
         <f>AJ48-AH48</f>
-        <v>2880701</v>
+        <v>2880788</v>
       </c>
       <c r="AJ48" s="8">
         <f>SUM(AJ10:AJ47)</f>
-        <v>9363509</v>
+        <v>9363596</v>
       </c>
       <c r="AK48" s="5">
         <f>AJ48/AG48</f>
-        <v>0.89218217249556553</v>
+        <v>0.89219046210675801</v>
       </c>
       <c r="AL48" s="6">
         <f>SUM(AL10:AL47)</f>
@@ -9165,15 +9165,15 @@
       </c>
       <c r="AN48" s="7">
         <f>AO48-AM48</f>
-        <v>1785140</v>
+        <v>1785230</v>
       </c>
       <c r="AO48" s="8">
         <f>SUM(AO10:AO47)</f>
-        <v>9434929</v>
+        <v>9435019</v>
       </c>
       <c r="AP48" s="5">
         <f>AO48/AL48</f>
-        <v>0.90041351575234485</v>
+        <v>0.90042210481712925</v>
       </c>
       <c r="AQ48" s="6">
         <f>SUM(AQ10:AQ47)</f>
@@ -9185,15 +9185,15 @@
       </c>
       <c r="AS48" s="7">
         <f>AT48-AR48</f>
-        <v>2955143</v>
+        <v>2955224</v>
       </c>
       <c r="AT48" s="8">
         <f>SUM(AT10:AT47)</f>
-        <v>9520014</v>
+        <v>9520095</v>
       </c>
       <c r="AU48" s="5">
         <f>AT48/AQ48</f>
-        <v>0.91796809988403916</v>
+        <v>0.91797591031541992</v>
       </c>
       <c r="AV48" s="6">
         <f>SUM(AV10:AV47)</f>
@@ -9205,15 +9205,15 @@
       </c>
       <c r="AX48" s="7">
         <f>AY48-AW48</f>
-        <v>1784435</v>
+        <v>1784498</v>
       </c>
       <c r="AY48" s="8">
         <f>SUM(AY10:AY47)</f>
-        <v>9585281</v>
+        <v>9585344</v>
       </c>
       <c r="AZ48" s="5">
         <f>AY48/AV48</f>
-        <v>0.92542267695064162</v>
+        <v>0.92542875936269064</v>
       </c>
       <c r="BA48" s="6">
         <f>SUM(BA10:BA47)</f>
@@ -9225,15 +9225,15 @@
       </c>
       <c r="BC48" s="7">
         <f>BD48-BB48</f>
-        <v>2313668</v>
+        <v>2313736</v>
       </c>
       <c r="BD48" s="8">
         <f>SUM(BD10:BD47)</f>
-        <v>9653666</v>
+        <v>9653734</v>
       </c>
       <c r="BE48" s="5">
         <f>BD48/BA48</f>
-        <v>0.93072519440913104</v>
+        <v>0.93073175039658906</v>
       </c>
       <c r="BF48" s="6">
         <f>SUM(BF10:BF47)</f>
@@ -9245,29 +9245,35 @@
       </c>
       <c r="BH48" s="7">
         <f>BI48-BG48</f>
-        <v>9066564</v>
+        <v>9066652</v>
       </c>
       <c r="BI48" s="8">
         <f>SUM(BI10:BI47)</f>
-        <v>9675937</v>
+        <v>9676025</v>
       </c>
       <c r="BJ48" s="5">
         <f>BI48/BF48</f>
-        <v>0.92789910422054911</v>
+        <v>0.92790754320905966</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A59" s="26" t="s">
+      <c r="A59" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="B59" s="26"/>
-      <c r="C59" s="26"/>
-      <c r="D59" s="26"/>
-      <c r="E59" s="26"/>
+      <c r="B59" s="21"/>
+      <c r="C59" s="21"/>
+      <c r="D59" s="21"/>
+      <c r="E59" s="21"/>
       <c r="F59" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C8:G8"/>
     <mergeCell ref="A59:E59"/>
     <mergeCell ref="AQ8:AU8"/>
     <mergeCell ref="AV8:AZ8"/>
@@ -9281,12 +9287,6 @@
     <mergeCell ref="AG8:AK8"/>
     <mergeCell ref="AL8:AP8"/>
     <mergeCell ref="H8:L8"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="C8:G8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/gstdatabase/GSTR-3B-2019-2020.xlsx
+++ b/gstdatabase/GSTR-3B-2019-2020.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\May-26\GST Statistics Downloads 31st May 26\Downloads\GSTR 3B\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\Jun-26\GST Statistics Downloads 31st May 26\Downloads\GSTR 3B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F272B1B-ED77-47E6-BED5-0070BDDBFCAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91F9D3A5-31E1-4001-A701-6471A6043E81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -185,10 +185,10 @@
     <t>STATE WISE RETURN PERIOD WISE GSTR-3B FILING SUMMARY</t>
   </si>
   <si>
-    <t>Data Considered upto 31st May 2026</t>
+    <t>Data Considered upto 30th Jun 2026</t>
   </si>
   <si>
-    <t>Filing %age as on 31st May 2026</t>
+    <t>Filing %age as on 30th Jun 2026</t>
   </si>
 </sst>
 </file>
@@ -367,18 +367,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="17" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -387,6 +375,18 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -679,12 +679,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:62" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
     </row>
     <row r="2" spans="1:62" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -701,10 +701,10 @@
       <c r="L2" s="1"/>
     </row>
     <row r="3" spans="1:62" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="26" t="s">
+      <c r="A3" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="26"/>
+      <c r="B3" s="22"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
@@ -731,107 +731,107 @@
       <c r="L4" s="1"/>
     </row>
     <row r="5" spans="1:62" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="26" t="s">
+      <c r="A5" s="22" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="26"/>
-      <c r="C5" s="26"/>
+      <c r="B5" s="22"/>
+      <c r="C5" s="22"/>
     </row>
     <row r="8" spans="1:62" s="17" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="27" t="s">
+      <c r="A8" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="23" t="s">
+      <c r="B8" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="C8" s="22">
+      <c r="C8" s="25">
         <v>43556</v>
       </c>
-      <c r="D8" s="23"/>
-      <c r="E8" s="23"/>
-      <c r="F8" s="23"/>
-      <c r="G8" s="23"/>
-      <c r="H8" s="22">
+      <c r="D8" s="24"/>
+      <c r="E8" s="24"/>
+      <c r="F8" s="24"/>
+      <c r="G8" s="24"/>
+      <c r="H8" s="25">
         <v>43586</v>
       </c>
-      <c r="I8" s="23"/>
-      <c r="J8" s="23"/>
-      <c r="K8" s="23"/>
-      <c r="L8" s="23"/>
-      <c r="M8" s="22">
+      <c r="I8" s="24"/>
+      <c r="J8" s="24"/>
+      <c r="K8" s="24"/>
+      <c r="L8" s="24"/>
+      <c r="M8" s="25">
         <v>43617</v>
       </c>
-      <c r="N8" s="23"/>
-      <c r="O8" s="23"/>
-      <c r="P8" s="23"/>
-      <c r="Q8" s="23"/>
-      <c r="R8" s="22">
+      <c r="N8" s="24"/>
+      <c r="O8" s="24"/>
+      <c r="P8" s="24"/>
+      <c r="Q8" s="24"/>
+      <c r="R8" s="25">
         <v>43647</v>
       </c>
-      <c r="S8" s="23"/>
-      <c r="T8" s="23"/>
-      <c r="U8" s="23"/>
-      <c r="V8" s="23"/>
-      <c r="W8" s="22">
+      <c r="S8" s="24"/>
+      <c r="T8" s="24"/>
+      <c r="U8" s="24"/>
+      <c r="V8" s="24"/>
+      <c r="W8" s="25">
         <v>43678</v>
       </c>
-      <c r="X8" s="23"/>
-      <c r="Y8" s="23"/>
-      <c r="Z8" s="23"/>
-      <c r="AA8" s="23"/>
-      <c r="AB8" s="22">
+      <c r="X8" s="24"/>
+      <c r="Y8" s="24"/>
+      <c r="Z8" s="24"/>
+      <c r="AA8" s="24"/>
+      <c r="AB8" s="25">
         <v>43709</v>
       </c>
-      <c r="AC8" s="23"/>
-      <c r="AD8" s="23"/>
-      <c r="AE8" s="23"/>
-      <c r="AF8" s="23"/>
-      <c r="AG8" s="22">
+      <c r="AC8" s="24"/>
+      <c r="AD8" s="24"/>
+      <c r="AE8" s="24"/>
+      <c r="AF8" s="24"/>
+      <c r="AG8" s="25">
         <v>43739</v>
       </c>
-      <c r="AH8" s="23"/>
-      <c r="AI8" s="23"/>
-      <c r="AJ8" s="23"/>
-      <c r="AK8" s="23"/>
-      <c r="AL8" s="22">
+      <c r="AH8" s="24"/>
+      <c r="AI8" s="24"/>
+      <c r="AJ8" s="24"/>
+      <c r="AK8" s="24"/>
+      <c r="AL8" s="25">
         <v>43770</v>
       </c>
-      <c r="AM8" s="23"/>
-      <c r="AN8" s="23"/>
-      <c r="AO8" s="23"/>
-      <c r="AP8" s="23"/>
-      <c r="AQ8" s="22">
+      <c r="AM8" s="24"/>
+      <c r="AN8" s="24"/>
+      <c r="AO8" s="24"/>
+      <c r="AP8" s="24"/>
+      <c r="AQ8" s="25">
         <v>43800</v>
       </c>
-      <c r="AR8" s="23"/>
-      <c r="AS8" s="23"/>
-      <c r="AT8" s="23"/>
-      <c r="AU8" s="23"/>
-      <c r="AV8" s="22">
+      <c r="AR8" s="24"/>
+      <c r="AS8" s="24"/>
+      <c r="AT8" s="24"/>
+      <c r="AU8" s="24"/>
+      <c r="AV8" s="25">
         <v>43831</v>
       </c>
-      <c r="AW8" s="23"/>
-      <c r="AX8" s="23"/>
-      <c r="AY8" s="23"/>
-      <c r="AZ8" s="23"/>
-      <c r="BA8" s="22">
+      <c r="AW8" s="24"/>
+      <c r="AX8" s="24"/>
+      <c r="AY8" s="24"/>
+      <c r="AZ8" s="24"/>
+      <c r="BA8" s="25">
         <v>43862</v>
       </c>
-      <c r="BB8" s="23"/>
-      <c r="BC8" s="23"/>
-      <c r="BD8" s="23"/>
-      <c r="BE8" s="23"/>
-      <c r="BF8" s="22">
+      <c r="BB8" s="24"/>
+      <c r="BC8" s="24"/>
+      <c r="BD8" s="24"/>
+      <c r="BE8" s="24"/>
+      <c r="BF8" s="25">
         <v>43891</v>
       </c>
-      <c r="BG8" s="23"/>
-      <c r="BH8" s="23"/>
-      <c r="BI8" s="23"/>
-      <c r="BJ8" s="23"/>
+      <c r="BG8" s="24"/>
+      <c r="BH8" s="24"/>
+      <c r="BI8" s="24"/>
+      <c r="BJ8" s="24"/>
     </row>
     <row r="9" spans="1:62" s="17" customFormat="1" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="A9" s="27"/>
-      <c r="B9" s="23"/>
+      <c r="A9" s="23"/>
+      <c r="B9" s="24"/>
       <c r="C9" s="18" t="s">
         <v>3</v>
       </c>
@@ -1030,11 +1030,11 @@
         <v>78332</v>
       </c>
       <c r="F10" s="3">
-        <v>78387</v>
+        <v>78388</v>
       </c>
       <c r="G10" s="12">
         <f>F10/C10</f>
-        <v>0.87890611860472934</v>
+        <v>0.87891733100115488</v>
       </c>
       <c r="H10" s="10">
         <v>90152</v>
@@ -1044,14 +1044,14 @@
       </c>
       <c r="J10" s="11">
         <f>K10-I10</f>
-        <v>23345</v>
+        <v>23346</v>
       </c>
       <c r="K10" s="3">
-        <v>79146</v>
+        <v>79147</v>
       </c>
       <c r="L10" s="12">
         <f>K10/H10</f>
-        <v>0.87791729523471473</v>
+        <v>0.87792838761203296</v>
       </c>
       <c r="M10" s="10">
         <v>90874</v>
@@ -1061,14 +1061,14 @@
       </c>
       <c r="O10" s="11">
         <f>P10-N10</f>
-        <v>21637</v>
+        <v>21638</v>
       </c>
       <c r="P10" s="3">
-        <v>79648</v>
+        <v>79649</v>
       </c>
       <c r="Q10" s="12">
         <f>P10/M10</f>
-        <v>0.8764663159979752</v>
+        <v>0.87647732024561475</v>
       </c>
       <c r="R10" s="10">
         <v>91798</v>
@@ -1078,14 +1078,14 @@
       </c>
       <c r="T10" s="11">
         <f>U10-S10</f>
-        <v>55436</v>
+        <v>55437</v>
       </c>
       <c r="U10" s="3">
-        <v>79481</v>
+        <v>79482</v>
       </c>
       <c r="V10" s="12">
         <f>U10/R10</f>
-        <v>0.86582496350683025</v>
+        <v>0.86583585699034837</v>
       </c>
       <c r="W10" s="10">
         <v>92245</v>
@@ -1095,14 +1095,14 @@
       </c>
       <c r="Y10" s="11">
         <f>Z10-X10</f>
-        <v>57246</v>
+        <v>57247</v>
       </c>
       <c r="Z10" s="3">
-        <v>79493</v>
+        <v>79494</v>
       </c>
       <c r="AA10" s="12">
         <f>Z10/W10</f>
-        <v>0.86175944495636625</v>
+        <v>0.86177028565233893</v>
       </c>
       <c r="AB10" s="10">
         <v>92462</v>
@@ -1112,14 +1112,14 @@
       </c>
       <c r="AD10" s="11">
         <f>AE10-AC10</f>
-        <v>59419</v>
+        <v>59420</v>
       </c>
       <c r="AE10" s="3">
-        <v>79655</v>
+        <v>79656</v>
       </c>
       <c r="AF10" s="12">
         <f>AE10/AB10</f>
-        <v>0.8614890441478662</v>
+        <v>0.86149985940170015</v>
       </c>
       <c r="AG10" s="3">
         <v>92639</v>
@@ -1129,14 +1129,14 @@
       </c>
       <c r="AI10" s="11">
         <f>AJ10-AH10</f>
-        <v>57491</v>
+        <v>57492</v>
       </c>
       <c r="AJ10" s="3">
-        <v>80000</v>
+        <v>80001</v>
       </c>
       <c r="AK10" s="12">
         <f>AJ10/AG10</f>
-        <v>0.86356718012931921</v>
+        <v>0.86357797471907083</v>
       </c>
       <c r="AL10" s="10">
         <v>92563</v>
@@ -1146,14 +1146,14 @@
       </c>
       <c r="AN10" s="11">
         <f>AO10-AM10</f>
-        <v>32310</v>
+        <v>32311</v>
       </c>
       <c r="AO10" s="3">
-        <v>80346</v>
+        <v>80347</v>
       </c>
       <c r="AP10" s="12">
         <f>AO10/AL10</f>
-        <v>0.86801421734386308</v>
+        <v>0.86802502079664656</v>
       </c>
       <c r="AQ10" s="16">
         <v>92194</v>
@@ -1163,14 +1163,14 @@
       </c>
       <c r="AS10" s="11">
         <f>AT10-AR10</f>
-        <v>39186</v>
+        <v>39187</v>
       </c>
       <c r="AT10" s="3">
-        <v>80890</v>
+        <v>80891</v>
       </c>
       <c r="AU10" s="12">
         <f>AT10/AQ10</f>
-        <v>0.87738898409874833</v>
+        <v>0.87739983079159167</v>
       </c>
       <c r="AV10" s="10">
         <v>91657</v>
@@ -2507,11 +2507,11 @@
         <v>487170</v>
       </c>
       <c r="F17" s="3">
-        <v>487417</v>
+        <v>487418</v>
       </c>
       <c r="G17" s="12">
         <f t="shared" si="0"/>
-        <v>0.88027805269203263</v>
+        <v>0.88027985869808634</v>
       </c>
       <c r="H17" s="10">
         <v>557836</v>
@@ -2640,14 +2640,14 @@
       </c>
       <c r="AS17" s="11">
         <f t="shared" si="15"/>
-        <v>151530</v>
+        <v>151531</v>
       </c>
       <c r="AT17" s="3">
-        <v>515483</v>
+        <v>515484</v>
       </c>
       <c r="AU17" s="12">
         <f t="shared" si="16"/>
-        <v>0.9513003070835917</v>
+        <v>0.95130215253786876</v>
       </c>
       <c r="AV17" s="10">
         <v>543495</v>
@@ -2674,14 +2674,14 @@
       </c>
       <c r="BC17" s="11">
         <f t="shared" si="19"/>
-        <v>132521</v>
+        <v>132522</v>
       </c>
       <c r="BD17" s="3">
-        <v>522894</v>
+        <v>522895</v>
       </c>
       <c r="BE17" s="12">
         <f t="shared" si="20"/>
-        <v>0.95442996385938017</v>
+        <v>0.95443178914321181</v>
       </c>
       <c r="BF17" s="10">
         <v>552190</v>
@@ -2718,11 +2718,11 @@
         <v>977646</v>
       </c>
       <c r="F18" s="3">
-        <v>978116</v>
+        <v>978118</v>
       </c>
       <c r="G18" s="12">
         <f t="shared" si="0"/>
-        <v>0.87817684096738835</v>
+        <v>0.87817863661706785</v>
       </c>
       <c r="H18" s="10">
         <v>1112907</v>
@@ -2732,14 +2732,14 @@
       </c>
       <c r="J18" s="11">
         <f t="shared" si="1"/>
-        <v>228450</v>
+        <v>228451</v>
       </c>
       <c r="K18" s="3">
-        <v>985775</v>
+        <v>985776</v>
       </c>
       <c r="L18" s="12">
         <f t="shared" si="2"/>
-        <v>0.8857658366781771</v>
+        <v>0.88576673522585447</v>
       </c>
       <c r="M18" s="10">
         <v>1118687</v>
@@ -2749,14 +2749,14 @@
       </c>
       <c r="O18" s="11">
         <f t="shared" si="3"/>
-        <v>221699</v>
+        <v>221700</v>
       </c>
       <c r="P18" s="3">
-        <v>991279</v>
+        <v>991280</v>
       </c>
       <c r="Q18" s="12">
         <f t="shared" si="4"/>
-        <v>0.88610934068242497</v>
+        <v>0.88611023458751192</v>
       </c>
       <c r="R18" s="10">
         <v>1127309</v>
@@ -2766,14 +2766,14 @@
       </c>
       <c r="T18" s="11">
         <f t="shared" si="5"/>
-        <v>178382</v>
+        <v>178383</v>
       </c>
       <c r="U18" s="3">
-        <v>1000096</v>
+        <v>1000097</v>
       </c>
       <c r="V18" s="12">
         <f t="shared" si="6"/>
-        <v>0.8871533891772353</v>
+        <v>0.88715427624546594</v>
       </c>
       <c r="W18" s="10">
         <v>1128388</v>
@@ -2783,14 +2783,14 @@
       </c>
       <c r="Y18" s="11">
         <f t="shared" si="7"/>
-        <v>244984</v>
+        <v>244987</v>
       </c>
       <c r="Z18" s="3">
-        <v>1007718</v>
+        <v>1007721</v>
       </c>
       <c r="AA18" s="12">
         <f t="shared" si="8"/>
-        <v>0.89305983402872058</v>
+        <v>0.89306249268868509</v>
       </c>
       <c r="AB18" s="10">
         <v>1126122</v>
@@ -2800,14 +2800,14 @@
       </c>
       <c r="AD18" s="11">
         <f t="shared" si="9"/>
-        <v>308055</v>
+        <v>308058</v>
       </c>
       <c r="AE18" s="3">
-        <v>1016956</v>
+        <v>1016959</v>
       </c>
       <c r="AF18" s="12">
         <f t="shared" si="10"/>
-        <v>0.90306023681270764</v>
+        <v>0.90306290082246865</v>
       </c>
       <c r="AG18" s="10">
         <v>1126652</v>
@@ -2817,14 +2817,14 @@
       </c>
       <c r="AI18" s="11">
         <f t="shared" si="11"/>
-        <v>271499</v>
+        <v>271501</v>
       </c>
       <c r="AJ18" s="3">
-        <v>1026207</v>
+        <v>1026209</v>
       </c>
       <c r="AK18" s="12">
         <f t="shared" si="12"/>
-        <v>0.91084647255763096</v>
+        <v>0.91084824772866868</v>
       </c>
       <c r="AL18" s="10">
         <v>1124411</v>
@@ -2834,14 +2834,14 @@
       </c>
       <c r="AN18" s="11">
         <f t="shared" si="13"/>
-        <v>195019</v>
+        <v>195021</v>
       </c>
       <c r="AO18" s="3">
-        <v>1036127</v>
+        <v>1036129</v>
       </c>
       <c r="AP18" s="12">
         <f t="shared" si="14"/>
-        <v>0.92148422596363788</v>
+        <v>0.92148600467266861</v>
       </c>
       <c r="AQ18" s="10">
         <v>1127354</v>
@@ -2851,14 +2851,14 @@
       </c>
       <c r="AS18" s="11">
         <f t="shared" si="15"/>
-        <v>311781</v>
+        <v>311783</v>
       </c>
       <c r="AT18" s="3">
-        <v>1046794</v>
+        <v>1046796</v>
       </c>
       <c r="AU18" s="12">
         <f t="shared" si="16"/>
-        <v>0.92854063586060809</v>
+        <v>0.92854240992625214</v>
       </c>
       <c r="AV18" s="10">
         <v>1133999</v>
@@ -2868,14 +2868,14 @@
       </c>
       <c r="AX18" s="11">
         <f t="shared" si="17"/>
-        <v>165989</v>
+        <v>165991</v>
       </c>
       <c r="AY18" s="3">
-        <v>1059067</v>
+        <v>1059069</v>
       </c>
       <c r="AZ18" s="12">
         <f t="shared" si="18"/>
-        <v>0.93392234031952404</v>
+        <v>0.93392410398950965</v>
       </c>
       <c r="BA18" s="10">
         <v>1144874</v>
@@ -2885,14 +2885,14 @@
       </c>
       <c r="BC18" s="11">
         <f t="shared" si="19"/>
-        <v>239377</v>
+        <v>239380</v>
       </c>
       <c r="BD18" s="3">
-        <v>1070496</v>
+        <v>1070499</v>
       </c>
       <c r="BE18" s="12">
         <f t="shared" si="20"/>
-        <v>0.93503389892686883</v>
+        <v>0.93503651930256082</v>
       </c>
       <c r="BF18" s="10">
         <v>1155076</v>
@@ -2902,14 +2902,14 @@
       </c>
       <c r="BH18" s="11">
         <f t="shared" si="21"/>
-        <v>991961</v>
+        <v>991965</v>
       </c>
       <c r="BI18" s="3">
-        <v>1073231</v>
+        <v>1073235</v>
       </c>
       <c r="BJ18" s="12">
         <f t="shared" si="22"/>
-        <v>0.92914319057793604</v>
+        <v>0.92914665355353243</v>
       </c>
     </row>
     <row r="19" spans="1:62" x14ac:dyDescent="0.3">
@@ -3113,14 +3113,14 @@
       </c>
       <c r="BH19" s="11">
         <f t="shared" si="21"/>
-        <v>273791</v>
+        <v>273792</v>
       </c>
       <c r="BI19" s="3">
-        <v>296539</v>
+        <v>296540</v>
       </c>
       <c r="BJ19" s="12">
         <f t="shared" si="22"/>
-        <v>0.92570370763472443</v>
+        <v>0.925706829327681</v>
       </c>
     </row>
     <row r="20" spans="1:62" x14ac:dyDescent="0.3">
@@ -4406,11 +4406,11 @@
         <v>19070</v>
       </c>
       <c r="F26" s="3">
-        <v>19118</v>
+        <v>19119</v>
       </c>
       <c r="G26" s="12">
         <f t="shared" si="0"/>
-        <v>0.80452804780541176</v>
+        <v>0.80457013003408662</v>
       </c>
       <c r="H26" s="10">
         <v>24195</v>
@@ -4420,14 +4420,14 @@
       </c>
       <c r="J26" s="11">
         <f t="shared" si="1"/>
-        <v>6130</v>
+        <v>6131</v>
       </c>
       <c r="K26" s="3">
-        <v>19480</v>
+        <v>19481</v>
       </c>
       <c r="L26" s="12">
         <f t="shared" si="2"/>
-        <v>0.80512502583178347</v>
+        <v>0.80516635668526559</v>
       </c>
       <c r="M26" s="10">
         <v>24878</v>
@@ -4437,14 +4437,14 @@
       </c>
       <c r="O26" s="11">
         <f t="shared" si="3"/>
-        <v>6346</v>
+        <v>6347</v>
       </c>
       <c r="P26" s="3">
-        <v>20084</v>
+        <v>20085</v>
       </c>
       <c r="Q26" s="12">
         <f t="shared" si="4"/>
-        <v>0.80729962215612183</v>
+        <v>0.80733981831336921</v>
       </c>
       <c r="R26" s="10">
         <v>25640</v>
@@ -4454,14 +4454,14 @@
       </c>
       <c r="T26" s="11">
         <f t="shared" si="5"/>
-        <v>5649</v>
+        <v>5650</v>
       </c>
       <c r="U26" s="3">
-        <v>20651</v>
+        <v>20652</v>
       </c>
       <c r="V26" s="12">
         <f t="shared" si="6"/>
-        <v>0.80542121684867396</v>
+        <v>0.80546021840873638</v>
       </c>
       <c r="W26" s="10">
         <v>25884</v>
@@ -4471,14 +4471,14 @@
       </c>
       <c r="Y26" s="11">
         <f t="shared" si="7"/>
-        <v>6418</v>
+        <v>6419</v>
       </c>
       <c r="Z26" s="3">
-        <v>20816</v>
+        <v>20817</v>
       </c>
       <c r="AA26" s="12">
         <f t="shared" si="8"/>
-        <v>0.80420336887652599</v>
+        <v>0.80424200278164115</v>
       </c>
       <c r="AB26" s="10">
         <v>26140</v>
@@ -4488,14 +4488,14 @@
       </c>
       <c r="AD26" s="11">
         <f t="shared" si="9"/>
-        <v>7477</v>
+        <v>7478</v>
       </c>
       <c r="AE26" s="3">
-        <v>20976</v>
+        <v>20977</v>
       </c>
       <c r="AF26" s="12">
         <f t="shared" si="10"/>
-        <v>0.80244835501147671</v>
+        <v>0.80248661055853099</v>
       </c>
       <c r="AG26" s="10">
         <v>26255</v>
@@ -4505,14 +4505,14 @@
       </c>
       <c r="AI26" s="11">
         <f t="shared" si="11"/>
-        <v>6655</v>
+        <v>6656</v>
       </c>
       <c r="AJ26" s="3">
-        <v>21057</v>
+        <v>21058</v>
       </c>
       <c r="AK26" s="12">
         <f t="shared" si="12"/>
-        <v>0.80201866311178827</v>
+        <v>0.8020567510950295</v>
       </c>
       <c r="AL26" s="10">
         <v>26357</v>
@@ -4522,14 +4522,14 @@
       </c>
       <c r="AN26" s="11">
         <f t="shared" si="13"/>
-        <v>6661</v>
+        <v>6662</v>
       </c>
       <c r="AO26" s="3">
-        <v>21053</v>
+        <v>21054</v>
       </c>
       <c r="AP26" s="12">
         <f t="shared" si="14"/>
-        <v>0.79876313692757139</v>
+        <v>0.7988010775126152</v>
       </c>
       <c r="AQ26" s="10">
         <v>26428</v>
@@ -4539,14 +4539,14 @@
       </c>
       <c r="AS26" s="11">
         <f t="shared" si="15"/>
-        <v>8146</v>
+        <v>8147</v>
       </c>
       <c r="AT26" s="3">
-        <v>21059</v>
+        <v>21060</v>
       </c>
       <c r="AU26" s="12">
         <f t="shared" si="16"/>
-        <v>0.79684425609202358</v>
+        <v>0.79688209474799454</v>
       </c>
       <c r="AV26" s="10">
         <v>26536</v>
@@ -4556,14 +4556,14 @@
       </c>
       <c r="AX26" s="11">
         <f t="shared" si="17"/>
-        <v>5323</v>
+        <v>5324</v>
       </c>
       <c r="AY26" s="3">
-        <v>21111</v>
+        <v>21112</v>
       </c>
       <c r="AZ26" s="12">
         <f t="shared" si="18"/>
-        <v>0.79556074766355145</v>
+        <v>0.79559843231835992</v>
       </c>
       <c r="BA26" s="10">
         <v>26675</v>
@@ -4573,14 +4573,14 @@
       </c>
       <c r="BC26" s="11">
         <f t="shared" si="19"/>
-        <v>6157</v>
+        <v>6158</v>
       </c>
       <c r="BD26" s="3">
-        <v>21114</v>
+        <v>21115</v>
       </c>
       <c r="BE26" s="12">
         <f t="shared" si="20"/>
-        <v>0.79152764761012184</v>
+        <v>0.79156513589503286</v>
       </c>
       <c r="BF26" s="10">
         <v>26706</v>
@@ -4590,14 +4590,14 @@
       </c>
       <c r="BH26" s="11">
         <f t="shared" si="21"/>
-        <v>17830</v>
+        <v>17831</v>
       </c>
       <c r="BI26" s="3">
-        <v>21026</v>
+        <v>21027</v>
       </c>
       <c r="BJ26" s="12">
         <f t="shared" si="22"/>
-        <v>0.78731371227439528</v>
+        <v>0.78735115704336101</v>
       </c>
     </row>
     <row r="27" spans="1:62" x14ac:dyDescent="0.3">
@@ -4665,14 +4665,14 @@
       </c>
       <c r="T27" s="11">
         <f t="shared" si="5"/>
-        <v>45703</v>
+        <v>45704</v>
       </c>
       <c r="U27" s="3">
-        <v>123210</v>
+        <v>123211</v>
       </c>
       <c r="V27" s="12">
         <f t="shared" si="6"/>
-        <v>0.75248262468089266</v>
+        <v>0.75248873199868083</v>
       </c>
       <c r="W27" s="10">
         <v>165285</v>
@@ -4682,14 +4682,14 @@
       </c>
       <c r="Y27" s="11">
         <f t="shared" si="7"/>
-        <v>54509</v>
+        <v>54510</v>
       </c>
       <c r="Z27" s="3">
-        <v>124680</v>
+        <v>124681</v>
       </c>
       <c r="AA27" s="12">
         <f t="shared" si="8"/>
-        <v>0.75433342408567017</v>
+        <v>0.75433947424146175</v>
       </c>
       <c r="AB27" s="10">
         <v>167059</v>
@@ -4699,14 +4699,14 @@
       </c>
       <c r="AD27" s="11">
         <f t="shared" si="9"/>
-        <v>63479</v>
+        <v>63480</v>
       </c>
       <c r="AE27" s="3">
-        <v>126162</v>
+        <v>126163</v>
       </c>
       <c r="AF27" s="12">
         <f t="shared" si="10"/>
-        <v>0.75519427268210637</v>
+        <v>0.75520025859127615</v>
       </c>
       <c r="AG27" s="10">
         <v>167755</v>
@@ -4716,14 +4716,14 @@
       </c>
       <c r="AI27" s="11">
         <f t="shared" si="11"/>
-        <v>54795</v>
+        <v>54796</v>
       </c>
       <c r="AJ27" s="3">
-        <v>127104</v>
+        <v>127105</v>
       </c>
       <c r="AK27" s="12">
         <f t="shared" si="12"/>
-        <v>0.75767637328246551</v>
+        <v>0.75768233435665111</v>
       </c>
       <c r="AL27" s="10">
         <v>166641</v>
@@ -4733,14 +4733,14 @@
       </c>
       <c r="AN27" s="11">
         <f t="shared" si="13"/>
-        <v>50761</v>
+        <v>50762</v>
       </c>
       <c r="AO27" s="3">
-        <v>128424</v>
+        <v>128425</v>
       </c>
       <c r="AP27" s="12">
         <f t="shared" si="14"/>
-        <v>0.77066268205303612</v>
+        <v>0.7706686829771785</v>
       </c>
       <c r="AQ27" s="10">
         <v>146205</v>
@@ -4750,14 +4750,14 @@
       </c>
       <c r="AS27" s="11">
         <f t="shared" si="15"/>
-        <v>56458</v>
+        <v>56459</v>
       </c>
       <c r="AT27" s="3">
-        <v>128845</v>
+        <v>128846</v>
       </c>
       <c r="AU27" s="12">
         <f t="shared" si="16"/>
-        <v>0.88126261071782774</v>
+        <v>0.88126945042919191</v>
       </c>
       <c r="AV27" s="10">
         <v>144136</v>
@@ -4767,14 +4767,14 @@
       </c>
       <c r="AX27" s="11">
         <f t="shared" si="17"/>
-        <v>38972</v>
+        <v>38973</v>
       </c>
       <c r="AY27" s="3">
-        <v>129612</v>
+        <v>129613</v>
       </c>
       <c r="AZ27" s="12">
         <f t="shared" si="18"/>
-        <v>0.89923405672420487</v>
+        <v>0.89924099461619578</v>
       </c>
       <c r="BA27" s="10">
         <v>144942</v>
@@ -4784,14 +4784,14 @@
       </c>
       <c r="BC27" s="11">
         <f t="shared" si="19"/>
-        <v>48736</v>
+        <v>48737</v>
       </c>
       <c r="BD27" s="3">
-        <v>130839</v>
+        <v>130840</v>
       </c>
       <c r="BE27" s="12">
         <f t="shared" si="20"/>
-        <v>0.90269901063873825</v>
+        <v>0.90270590995018696</v>
       </c>
       <c r="BF27" s="10">
         <v>145908</v>
@@ -4801,14 +4801,14 @@
       </c>
       <c r="BH27" s="11">
         <f t="shared" si="21"/>
-        <v>123826</v>
+        <v>123827</v>
       </c>
       <c r="BI27" s="3">
-        <v>131302</v>
+        <v>131303</v>
       </c>
       <c r="BJ27" s="12">
         <f t="shared" si="22"/>
-        <v>0.89989582476629104</v>
+        <v>0.89990267840008775</v>
       </c>
     </row>
     <row r="28" spans="1:62" x14ac:dyDescent="0.3">
@@ -4828,11 +4828,11 @@
         <v>516434</v>
       </c>
       <c r="F28" s="3">
-        <v>516702</v>
+        <v>516704</v>
       </c>
       <c r="G28" s="12">
         <f t="shared" si="0"/>
-        <v>0.88352615685563718</v>
+        <v>0.88352957672301469</v>
       </c>
       <c r="H28" s="10">
         <v>588402</v>
@@ -4842,14 +4842,14 @@
       </c>
       <c r="J28" s="11">
         <f t="shared" si="1"/>
-        <v>139564</v>
+        <v>139566</v>
       </c>
       <c r="K28" s="3">
-        <v>519361</v>
+        <v>519363</v>
       </c>
       <c r="L28" s="12">
         <f t="shared" si="2"/>
-        <v>0.88266355314903755</v>
+        <v>0.88266695218575053</v>
       </c>
       <c r="M28" s="10">
         <v>593424</v>
@@ -4859,14 +4859,14 @@
       </c>
       <c r="O28" s="11">
         <f t="shared" si="3"/>
-        <v>131523</v>
+        <v>131525</v>
       </c>
       <c r="P28" s="3">
-        <v>521975</v>
+        <v>521977</v>
       </c>
       <c r="Q28" s="12">
         <f t="shared" si="4"/>
-        <v>0.87959873547412981</v>
+        <v>0.87960210574563891</v>
       </c>
       <c r="R28" s="10">
         <v>598953</v>
@@ -4876,14 +4876,14 @@
       </c>
       <c r="T28" s="11">
         <f t="shared" si="5"/>
-        <v>115168</v>
+        <v>115170</v>
       </c>
       <c r="U28" s="3">
-        <v>526471</v>
+        <v>526473</v>
       </c>
       <c r="V28" s="12">
         <f t="shared" si="6"/>
-        <v>0.87898549635781109</v>
+        <v>0.87898883551797891</v>
       </c>
       <c r="W28" s="10">
         <v>603444</v>
@@ -4893,14 +4893,14 @@
       </c>
       <c r="Y28" s="11">
         <f t="shared" si="7"/>
-        <v>150610</v>
+        <v>150612</v>
       </c>
       <c r="Z28" s="3">
-        <v>530231</v>
+        <v>530233</v>
       </c>
       <c r="AA28" s="12">
         <f t="shared" si="8"/>
-        <v>0.87867474032387427</v>
+        <v>0.8786780546330728</v>
       </c>
       <c r="AB28" s="10">
         <v>607620</v>
@@ -4910,14 +4910,14 @@
       </c>
       <c r="AD28" s="11">
         <f t="shared" si="9"/>
-        <v>179457</v>
+        <v>179459</v>
       </c>
       <c r="AE28" s="3">
-        <v>533664</v>
+        <v>533666</v>
       </c>
       <c r="AF28" s="12">
         <f t="shared" si="10"/>
-        <v>0.87828577071195812</v>
+        <v>0.87828906224284919</v>
       </c>
       <c r="AG28" s="10">
         <v>610678</v>
@@ -4927,14 +4927,14 @@
       </c>
       <c r="AI28" s="11">
         <f t="shared" si="11"/>
-        <v>145987</v>
+        <v>145989</v>
       </c>
       <c r="AJ28" s="3">
-        <v>535618</v>
+        <v>535620</v>
       </c>
       <c r="AK28" s="12">
         <f t="shared" si="12"/>
-        <v>0.87708743396683686</v>
+        <v>0.87709070901522568</v>
       </c>
       <c r="AL28" s="10">
         <v>612549</v>
@@ -4944,14 +4944,14 @@
       </c>
       <c r="AN28" s="11">
         <f t="shared" si="13"/>
-        <v>100037</v>
+        <v>100038</v>
       </c>
       <c r="AO28" s="3">
-        <v>539205</v>
+        <v>539206</v>
       </c>
       <c r="AP28" s="12">
         <f t="shared" si="14"/>
-        <v>0.88026427273573216</v>
+        <v>0.88026590525819159</v>
       </c>
       <c r="AQ28" s="10">
         <v>611342</v>
@@ -5417,14 +5417,14 @@
       </c>
       <c r="BC30" s="11">
         <f t="shared" si="19"/>
-        <v>55525</v>
+        <v>55526</v>
       </c>
       <c r="BD30" s="3">
-        <v>214164</v>
+        <v>214165</v>
       </c>
       <c r="BE30" s="12">
         <f t="shared" si="20"/>
-        <v>0.95749988822819332</v>
+        <v>0.9575043591004605</v>
       </c>
       <c r="BF30" s="10">
         <v>223069</v>
@@ -5434,14 +5434,14 @@
       </c>
       <c r="BH30" s="11">
         <f t="shared" si="21"/>
-        <v>194010</v>
+        <v>194011</v>
       </c>
       <c r="BI30" s="3">
-        <v>214657</v>
+        <v>214658</v>
       </c>
       <c r="BJ30" s="12">
         <f t="shared" si="22"/>
-        <v>0.96228969511675755</v>
+        <v>0.96229417803459916</v>
       </c>
     </row>
     <row r="31" spans="1:62" x14ac:dyDescent="0.3">
@@ -5754,14 +5754,14 @@
       </c>
       <c r="AD32" s="11">
         <f t="shared" si="9"/>
-        <v>133117</v>
+        <v>133118</v>
       </c>
       <c r="AE32" s="3">
-        <v>332563</v>
+        <v>332564</v>
       </c>
       <c r="AF32" s="12">
         <f t="shared" si="10"/>
-        <v>0.92379894165196741</v>
+        <v>0.9238017194683259</v>
       </c>
       <c r="AG32" s="10">
         <v>361943</v>
@@ -5771,14 +5771,14 @@
       </c>
       <c r="AI32" s="11">
         <f t="shared" si="11"/>
-        <v>115786</v>
+        <v>115787</v>
       </c>
       <c r="AJ32" s="3">
-        <v>335344</v>
+        <v>335345</v>
       </c>
       <c r="AK32" s="12">
         <f t="shared" si="12"/>
-        <v>0.92651052790080202</v>
+        <v>0.92651329076677824</v>
       </c>
       <c r="AL32" s="10">
         <v>362211</v>
@@ -5788,14 +5788,14 @@
       </c>
       <c r="AN32" s="11">
         <f t="shared" si="13"/>
-        <v>63067</v>
+        <v>63068</v>
       </c>
       <c r="AO32" s="3">
-        <v>337804</v>
+        <v>337805</v>
       </c>
       <c r="AP32" s="12">
         <f t="shared" si="14"/>
-        <v>0.93261662401197087</v>
+        <v>0.93261938483370188</v>
       </c>
       <c r="AQ32" s="10">
         <v>354752</v>
@@ -5805,14 +5805,14 @@
       </c>
       <c r="AS32" s="11">
         <f t="shared" si="15"/>
-        <v>107060</v>
+        <v>107061</v>
       </c>
       <c r="AT32" s="3">
-        <v>340057</v>
+        <v>340058</v>
       </c>
       <c r="AU32" s="12">
         <f t="shared" si="16"/>
-        <v>0.95857669583258165</v>
+        <v>0.95857951470322933</v>
       </c>
       <c r="AV32" s="10">
         <v>347413</v>
@@ -5822,14 +5822,14 @@
       </c>
       <c r="AX32" s="11">
         <f t="shared" si="17"/>
-        <v>63214</v>
+        <v>63215</v>
       </c>
       <c r="AY32" s="3">
-        <v>342093</v>
+        <v>342094</v>
       </c>
       <c r="AZ32" s="12">
         <f t="shared" si="18"/>
-        <v>0.98468681367709321</v>
+        <v>0.984689692095575</v>
       </c>
       <c r="BA32" s="10">
         <v>348074</v>
@@ -5839,14 +5839,14 @@
       </c>
       <c r="BC32" s="11">
         <f t="shared" si="19"/>
-        <v>76527</v>
+        <v>76528</v>
       </c>
       <c r="BD32" s="3">
-        <v>344315</v>
+        <v>344316</v>
       </c>
       <c r="BE32" s="12">
         <f t="shared" si="20"/>
-        <v>0.98920057229209879</v>
+        <v>0.98920344524440207</v>
       </c>
       <c r="BF32" s="10">
         <v>351474</v>
@@ -5856,14 +5856,14 @@
       </c>
       <c r="BH32" s="11">
         <f t="shared" si="21"/>
-        <v>330989</v>
+        <v>330990</v>
       </c>
       <c r="BI32" s="3">
-        <v>346331</v>
+        <v>346332</v>
       </c>
       <c r="BJ32" s="12">
         <f t="shared" si="22"/>
-        <v>0.98536733869361603</v>
+        <v>0.98537018385428221</v>
       </c>
     </row>
     <row r="33" spans="1:62" x14ac:dyDescent="0.3">
@@ -5883,11 +5883,11 @@
         <v>798628</v>
       </c>
       <c r="F33" s="3">
-        <v>798873</v>
+        <v>798875</v>
       </c>
       <c r="G33" s="12">
         <f t="shared" si="0"/>
-        <v>0.91928880153553694</v>
+        <v>0.91929110299972838</v>
       </c>
       <c r="H33" s="10">
         <v>871303</v>
@@ -5897,14 +5897,14 @@
       </c>
       <c r="J33" s="11">
         <f t="shared" si="1"/>
-        <v>172517</v>
+        <v>172519</v>
       </c>
       <c r="K33" s="3">
-        <v>805152</v>
+        <v>805154</v>
       </c>
       <c r="L33" s="12">
         <f t="shared" si="2"/>
-        <v>0.92407807616868065</v>
+        <v>0.9240803715814131</v>
       </c>
       <c r="M33" s="10">
         <v>877062</v>
@@ -5914,14 +5914,14 @@
       </c>
       <c r="O33" s="11">
         <f t="shared" si="3"/>
-        <v>162002</v>
+        <v>162004</v>
       </c>
       <c r="P33" s="3">
-        <v>810230</v>
+        <v>810232</v>
       </c>
       <c r="Q33" s="12">
         <f t="shared" si="4"/>
-        <v>0.92380014183717918</v>
+        <v>0.92380242217767961</v>
       </c>
       <c r="R33" s="10">
         <v>881026</v>
@@ -5931,14 +5931,14 @@
       </c>
       <c r="T33" s="11">
         <f t="shared" si="5"/>
-        <v>137067</v>
+        <v>137069</v>
       </c>
       <c r="U33" s="3">
-        <v>816378</v>
+        <v>816380</v>
       </c>
       <c r="V33" s="12">
         <f t="shared" si="6"/>
-        <v>0.92662191581179221</v>
+        <v>0.92662418589235729</v>
       </c>
       <c r="W33" s="10">
         <v>884173</v>
@@ -5948,14 +5948,14 @@
       </c>
       <c r="Y33" s="11">
         <f t="shared" si="7"/>
-        <v>177130</v>
+        <v>177132</v>
       </c>
       <c r="Z33" s="3">
-        <v>820948</v>
+        <v>820950</v>
       </c>
       <c r="AA33" s="12">
         <f t="shared" si="8"/>
-        <v>0.92849250090197277</v>
+        <v>0.92849476290273514</v>
       </c>
       <c r="AB33" s="10">
         <v>884817</v>
@@ -5965,14 +5965,14 @@
       </c>
       <c r="AD33" s="11">
         <f t="shared" si="9"/>
-        <v>222671</v>
+        <v>222673</v>
       </c>
       <c r="AE33" s="3">
-        <v>826026</v>
+        <v>826028</v>
       </c>
       <c r="AF33" s="12">
         <f t="shared" si="10"/>
-        <v>0.93355575220638842</v>
+        <v>0.93355801256078941</v>
       </c>
       <c r="AG33" s="10">
         <v>888089</v>
@@ -5982,14 +5982,14 @@
       </c>
       <c r="AI33" s="11">
         <f t="shared" si="11"/>
-        <v>209154</v>
+        <v>209157</v>
       </c>
       <c r="AJ33" s="3">
-        <v>829768</v>
+        <v>829771</v>
       </c>
       <c r="AK33" s="12">
         <f t="shared" si="12"/>
-        <v>0.93432978001078726</v>
+        <v>0.9343331580506008</v>
       </c>
       <c r="AL33" s="10">
         <v>887648</v>
@@ -6516,11 +6516,11 @@
         <v>1213488</v>
       </c>
       <c r="F36" s="3">
-        <v>1214466</v>
+        <v>1214467</v>
       </c>
       <c r="G36" s="12">
         <f t="shared" si="0"/>
-        <v>0.87391333444149655</v>
+        <v>0.87391405402799338</v>
       </c>
       <c r="H36" s="10">
         <v>1398033</v>
@@ -6530,14 +6530,14 @@
       </c>
       <c r="J36" s="11">
         <f t="shared" si="1"/>
-        <v>374677</v>
+        <v>374679</v>
       </c>
       <c r="K36" s="3">
-        <v>1219842</v>
+        <v>1219844</v>
       </c>
       <c r="L36" s="12">
         <f t="shared" si="2"/>
-        <v>0.87254163528328732</v>
+        <v>0.87254306586468278</v>
       </c>
       <c r="M36" s="10">
         <v>1405014</v>
@@ -6547,14 +6547,14 @@
       </c>
       <c r="O36" s="11">
         <f t="shared" si="3"/>
-        <v>355855</v>
+        <v>355857</v>
       </c>
       <c r="P36" s="3">
-        <v>1224767</v>
+        <v>1224769</v>
       </c>
       <c r="Q36" s="12">
         <f t="shared" si="4"/>
-        <v>0.87171159860328795</v>
+        <v>0.87171302207664836</v>
       </c>
       <c r="R36" s="10">
         <v>1409335</v>
@@ -6564,14 +6564,14 @@
       </c>
       <c r="T36" s="11">
         <f t="shared" si="5"/>
-        <v>320696</v>
+        <v>320698</v>
       </c>
       <c r="U36" s="3">
-        <v>1232419</v>
+        <v>1232421</v>
       </c>
       <c r="V36" s="12">
         <f t="shared" si="6"/>
-        <v>0.87446845498054049</v>
+        <v>0.8744698740895529</v>
       </c>
       <c r="W36" s="10">
         <v>1413902</v>
@@ -6581,14 +6581,14 @@
       </c>
       <c r="Y36" s="11">
         <f t="shared" si="7"/>
-        <v>384044</v>
+        <v>384046</v>
       </c>
       <c r="Z36" s="3">
-        <v>1237579</v>
+        <v>1237581</v>
       </c>
       <c r="AA36" s="12">
         <f t="shared" si="8"/>
-        <v>0.87529333716198154</v>
+        <v>0.87529475168717497</v>
       </c>
       <c r="AB36" s="10">
         <v>1416919</v>
@@ -6598,14 +6598,14 @@
       </c>
       <c r="AD36" s="11">
         <f t="shared" si="9"/>
-        <v>476493</v>
+        <v>476495</v>
       </c>
       <c r="AE36" s="3">
-        <v>1244826</v>
+        <v>1244828</v>
       </c>
       <c r="AF36" s="12">
         <f t="shared" si="10"/>
-        <v>0.87854422165275503</v>
+        <v>0.8785456331660455</v>
       </c>
       <c r="AG36" s="10">
         <v>1419473</v>
@@ -6615,14 +6615,14 @@
       </c>
       <c r="AI36" s="11">
         <f t="shared" si="11"/>
-        <v>414504</v>
+        <v>414506</v>
       </c>
       <c r="AJ36" s="3">
-        <v>1251113</v>
+        <v>1251115</v>
       </c>
       <c r="AK36" s="12">
         <f t="shared" si="12"/>
-        <v>0.88139260133866582</v>
+        <v>0.88139401031227782</v>
       </c>
       <c r="AL36" s="10">
         <v>1415447</v>
@@ -6632,14 +6632,14 @@
       </c>
       <c r="AN36" s="11">
         <f t="shared" si="13"/>
-        <v>261118</v>
+        <v>261120</v>
       </c>
       <c r="AO36" s="3">
-        <v>1259383</v>
+        <v>1259385</v>
       </c>
       <c r="AP36" s="12">
         <f t="shared" si="14"/>
-        <v>0.8897422510344789</v>
+        <v>0.88974366401567839</v>
       </c>
       <c r="AQ36" s="10">
         <v>1379433</v>
@@ -6649,14 +6649,14 @@
       </c>
       <c r="AS36" s="11">
         <f t="shared" si="15"/>
-        <v>413101</v>
+        <v>413104</v>
       </c>
       <c r="AT36" s="3">
-        <v>1269274</v>
+        <v>1269277</v>
       </c>
       <c r="AU36" s="12">
         <f t="shared" si="16"/>
-        <v>0.92014182638808839</v>
+        <v>0.92014400119469375</v>
       </c>
       <c r="AV36" s="10">
         <v>1370415</v>
@@ -6666,14 +6666,14 @@
       </c>
       <c r="AX36" s="11">
         <f t="shared" si="17"/>
-        <v>275210</v>
+        <v>275212</v>
       </c>
       <c r="AY36" s="3">
-        <v>1275420</v>
+        <v>1275422</v>
       </c>
       <c r="AZ36" s="12">
         <f t="shared" si="18"/>
-        <v>0.93068158185659089</v>
+        <v>0.93068304126852086</v>
       </c>
       <c r="BA36" s="10">
         <v>1375391</v>
@@ -6683,14 +6683,14 @@
       </c>
       <c r="BC36" s="11">
         <f t="shared" si="19"/>
-        <v>338576</v>
+        <v>338579</v>
       </c>
       <c r="BD36" s="3">
-        <v>1281942</v>
+        <v>1281945</v>
       </c>
       <c r="BE36" s="12">
         <f t="shared" si="20"/>
-        <v>0.93205641159495733</v>
+        <v>0.93205859279288583</v>
       </c>
       <c r="BF36" s="10">
         <v>1380633</v>
@@ -6700,14 +6700,14 @@
       </c>
       <c r="BH36" s="11">
         <f t="shared" si="21"/>
-        <v>1217306</v>
+        <v>1217309</v>
       </c>
       <c r="BI36" s="3">
-        <v>1281461</v>
+        <v>1281464</v>
       </c>
       <c r="BJ36" s="12">
         <f t="shared" si="22"/>
-        <v>0.92816918036871487</v>
+        <v>0.92817135328505118</v>
       </c>
     </row>
     <row r="37" spans="1:62" x14ac:dyDescent="0.3">
@@ -6727,11 +6727,11 @@
         <v>627302</v>
       </c>
       <c r="F37" s="3">
-        <v>627968</v>
+        <v>627970</v>
       </c>
       <c r="G37" s="12">
         <f t="shared" si="0"/>
-        <v>0.8862794688826664</v>
+        <v>0.88628229157257699</v>
       </c>
       <c r="H37" s="10">
         <v>707340</v>
@@ -6741,14 +6741,14 @@
       </c>
       <c r="J37" s="11">
         <f t="shared" si="1"/>
-        <v>167233</v>
+        <v>167234</v>
       </c>
       <c r="K37" s="3">
-        <v>632196</v>
+        <v>632197</v>
       </c>
       <c r="L37" s="12">
         <f t="shared" si="2"/>
-        <v>0.89376537450165405</v>
+        <v>0.89376678824893263</v>
       </c>
       <c r="M37" s="10">
         <v>710827</v>
@@ -6758,14 +6758,14 @@
       </c>
       <c r="O37" s="11">
         <f t="shared" si="3"/>
-        <v>160112</v>
+        <v>160113</v>
       </c>
       <c r="P37" s="3">
-        <v>636969</v>
+        <v>636970</v>
       </c>
       <c r="Q37" s="12">
         <f t="shared" si="4"/>
-        <v>0.89609567447494254</v>
+        <v>0.89609708128700793</v>
       </c>
       <c r="R37" s="10">
         <v>713357</v>
@@ -6775,14 +6775,14 @@
       </c>
       <c r="T37" s="11">
         <f t="shared" si="5"/>
-        <v>137613</v>
+        <v>137614</v>
       </c>
       <c r="U37" s="3">
-        <v>644567</v>
+        <v>644568</v>
       </c>
       <c r="V37" s="12">
         <f t="shared" si="6"/>
-        <v>0.90356861991961945</v>
+        <v>0.9035700217422693</v>
       </c>
       <c r="W37" s="10">
         <v>709504</v>
@@ -6792,14 +6792,14 @@
       </c>
       <c r="Y37" s="11">
         <f t="shared" si="7"/>
-        <v>170678</v>
+        <v>170679</v>
       </c>
       <c r="Z37" s="3">
-        <v>650133</v>
+        <v>650134</v>
       </c>
       <c r="AA37" s="12">
         <f t="shared" si="8"/>
-        <v>0.91632041538877862</v>
+        <v>0.91632182482410252</v>
       </c>
       <c r="AB37" s="10">
         <v>709880</v>
@@ -6809,14 +6809,14 @@
       </c>
       <c r="AD37" s="11">
         <f t="shared" si="9"/>
-        <v>220784</v>
+        <v>220785</v>
       </c>
       <c r="AE37" s="3">
-        <v>655098</v>
+        <v>655099</v>
       </c>
       <c r="AF37" s="12">
         <f t="shared" si="10"/>
-        <v>0.9228292105708007</v>
+        <v>0.9228306192595932</v>
       </c>
       <c r="AG37" s="10">
         <v>716349</v>
@@ -6826,14 +6826,14 @@
       </c>
       <c r="AI37" s="11">
         <f t="shared" si="11"/>
-        <v>195310</v>
+        <v>195311</v>
       </c>
       <c r="AJ37" s="3">
-        <v>661856</v>
+        <v>661857</v>
       </c>
       <c r="AK37" s="12">
         <f t="shared" si="12"/>
-        <v>0.92392953713902026</v>
+        <v>0.92393093310662822</v>
       </c>
       <c r="AL37" s="10">
         <v>718037</v>
@@ -6843,14 +6843,14 @@
       </c>
       <c r="AN37" s="11">
         <f t="shared" si="13"/>
-        <v>115176</v>
+        <v>115177</v>
       </c>
       <c r="AO37" s="3">
-        <v>668146</v>
+        <v>668147</v>
       </c>
       <c r="AP37" s="12">
         <f t="shared" si="14"/>
-        <v>0.93051750815069423</v>
+        <v>0.93051890083658639</v>
       </c>
       <c r="AQ37" s="10">
         <v>723207</v>
@@ -6860,14 +6860,14 @@
       </c>
       <c r="AS37" s="11">
         <f t="shared" si="15"/>
-        <v>201324</v>
+        <v>201325</v>
       </c>
       <c r="AT37" s="3">
-        <v>675767</v>
+        <v>675768</v>
       </c>
       <c r="AU37" s="12">
         <f t="shared" si="16"/>
-        <v>0.93440328979116627</v>
+        <v>0.93440467252114545</v>
       </c>
       <c r="AV37" s="10">
         <v>726054</v>
@@ -6877,14 +6877,14 @@
       </c>
       <c r="AX37" s="11">
         <f t="shared" si="17"/>
-        <v>124579</v>
+        <v>124580</v>
       </c>
       <c r="AY37" s="3">
-        <v>681065</v>
+        <v>681066</v>
       </c>
       <c r="AZ37" s="12">
         <f t="shared" si="18"/>
-        <v>0.93803628931181426</v>
+        <v>0.93803766661983823</v>
       </c>
       <c r="BA37" s="10">
         <v>731853</v>
@@ -6894,14 +6894,14 @@
       </c>
       <c r="BC37" s="11">
         <f t="shared" si="19"/>
-        <v>136741</v>
+        <v>136742</v>
       </c>
       <c r="BD37" s="3">
-        <v>686376</v>
+        <v>686377</v>
       </c>
       <c r="BE37" s="12">
         <f t="shared" si="20"/>
-        <v>0.93786047198002875</v>
+        <v>0.93786183837464632</v>
       </c>
       <c r="BF37" s="10">
         <v>734800</v>
@@ -6911,14 +6911,14 @@
       </c>
       <c r="BH37" s="11">
         <f t="shared" si="21"/>
-        <v>630833</v>
+        <v>630834</v>
       </c>
       <c r="BI37" s="3">
-        <v>686239</v>
+        <v>686240</v>
       </c>
       <c r="BJ37" s="12">
         <f t="shared" si="22"/>
-        <v>0.93391262928688079</v>
+        <v>0.9339139902014153</v>
       </c>
     </row>
     <row r="38" spans="1:62" x14ac:dyDescent="0.3">
@@ -7391,14 +7391,14 @@
       </c>
       <c r="O40" s="11">
         <f t="shared" si="3"/>
-        <v>89908</v>
+        <v>89909</v>
       </c>
       <c r="P40" s="3">
-        <v>266988</v>
+        <v>266989</v>
       </c>
       <c r="Q40" s="12">
         <f t="shared" si="4"/>
-        <v>0.90225167532349038</v>
+        <v>0.90225505469513001</v>
       </c>
       <c r="R40" s="10">
         <v>298709</v>
@@ -7408,14 +7408,14 @@
       </c>
       <c r="T40" s="11">
         <f t="shared" si="5"/>
-        <v>81294</v>
+        <v>81295</v>
       </c>
       <c r="U40" s="3">
-        <v>269537</v>
+        <v>269538</v>
       </c>
       <c r="V40" s="12">
         <f t="shared" si="6"/>
-        <v>0.90233973532769352</v>
+        <v>0.90234308306746702</v>
       </c>
       <c r="W40" s="10">
         <v>300746</v>
@@ -7425,14 +7425,14 @@
       </c>
       <c r="Y40" s="11">
         <f t="shared" si="7"/>
-        <v>112188</v>
+        <v>112190</v>
       </c>
       <c r="Z40" s="3">
-        <v>271711</v>
+        <v>271713</v>
       </c>
       <c r="AA40" s="12">
         <f t="shared" si="8"/>
-        <v>0.90345673757921963</v>
+        <v>0.90346338770922974</v>
       </c>
       <c r="AB40" s="10">
         <v>301836</v>
@@ -7442,14 +7442,14 @@
       </c>
       <c r="AD40" s="11">
         <f t="shared" si="9"/>
-        <v>123081</v>
+        <v>123082</v>
       </c>
       <c r="AE40" s="3">
-        <v>273069</v>
+        <v>273070</v>
       </c>
       <c r="AF40" s="12">
         <f t="shared" si="10"/>
-        <v>0.90469327714387948</v>
+        <v>0.90469659020130133</v>
       </c>
       <c r="AG40" s="10">
         <v>303421</v>
@@ -7459,14 +7459,14 @@
       </c>
       <c r="AI40" s="11">
         <f t="shared" si="11"/>
-        <v>104566</v>
+        <v>104567</v>
       </c>
       <c r="AJ40" s="3">
-        <v>275257</v>
+        <v>275258</v>
       </c>
       <c r="AK40" s="12">
         <f t="shared" si="12"/>
-        <v>0.90717847479245006</v>
+        <v>0.90718177054323856</v>
       </c>
       <c r="AL40" s="10">
         <v>303850</v>
@@ -7476,14 +7476,14 @@
       </c>
       <c r="AN40" s="11">
         <f t="shared" si="13"/>
-        <v>62707</v>
+        <v>62708</v>
       </c>
       <c r="AO40" s="3">
-        <v>277520</v>
+        <v>277521</v>
       </c>
       <c r="AP40" s="12">
         <f t="shared" si="14"/>
-        <v>0.91334540069113046</v>
+        <v>0.91334869178871159</v>
       </c>
       <c r="AQ40" s="10">
         <v>302709</v>
@@ -7493,14 +7493,14 @@
       </c>
       <c r="AS40" s="11">
         <f t="shared" si="15"/>
-        <v>107026</v>
+        <v>107028</v>
       </c>
       <c r="AT40" s="3">
-        <v>279346</v>
+        <v>279348</v>
       </c>
       <c r="AU40" s="12">
         <f t="shared" si="16"/>
-        <v>0.92282026632838798</v>
+        <v>0.92282687333379587</v>
       </c>
       <c r="AV40" s="10">
         <v>301724</v>
@@ -7510,14 +7510,14 @@
       </c>
       <c r="AX40" s="11">
         <f t="shared" si="17"/>
-        <v>70558</v>
+        <v>70559</v>
       </c>
       <c r="AY40" s="3">
-        <v>280798</v>
+        <v>280799</v>
       </c>
       <c r="AZ40" s="12">
         <f t="shared" si="18"/>
-        <v>0.93064522543781736</v>
+        <v>0.93064853972504669</v>
       </c>
       <c r="BA40" s="10">
         <v>302553</v>
@@ -7527,14 +7527,14 @@
       </c>
       <c r="BC40" s="11">
         <f t="shared" si="19"/>
-        <v>83697</v>
+        <v>83698</v>
       </c>
       <c r="BD40" s="3">
-        <v>282392</v>
+        <v>282393</v>
       </c>
       <c r="BE40" s="12">
         <f t="shared" si="20"/>
-        <v>0.9333637412288095</v>
+        <v>0.93336704643483948</v>
       </c>
       <c r="BF40" s="10">
         <v>304085</v>
@@ -7544,14 +7544,14 @@
       </c>
       <c r="BH40" s="11">
         <f t="shared" si="21"/>
-        <v>272364</v>
+        <v>272365</v>
       </c>
       <c r="BI40" s="3">
-        <v>283649</v>
+        <v>283650</v>
       </c>
       <c r="BJ40" s="12">
         <f t="shared" si="22"/>
-        <v>0.93279510663136955</v>
+        <v>0.93279839518555663</v>
       </c>
     </row>
     <row r="41" spans="1:62" x14ac:dyDescent="0.3">
@@ -7571,11 +7571,11 @@
         <v>762739</v>
       </c>
       <c r="F41" s="3">
-        <v>763701</v>
+        <v>763709</v>
       </c>
       <c r="G41" s="12">
         <f t="shared" si="0"/>
-        <v>0.87101133898571848</v>
+        <v>0.87102046309412207</v>
       </c>
       <c r="H41" s="10">
         <v>885438</v>
@@ -7585,14 +7585,14 @@
       </c>
       <c r="J41" s="11">
         <f t="shared" si="1"/>
-        <v>217417</v>
+        <v>217425</v>
       </c>
       <c r="K41" s="3">
-        <v>768951</v>
+        <v>768959</v>
       </c>
       <c r="L41" s="12">
         <f t="shared" si="2"/>
-        <v>0.86844138155353623</v>
+        <v>0.8684504166299617</v>
       </c>
       <c r="M41" s="10">
         <v>894344</v>
@@ -7602,14 +7602,14 @@
       </c>
       <c r="O41" s="11">
         <f t="shared" si="3"/>
-        <v>206473</v>
+        <v>206479</v>
       </c>
       <c r="P41" s="3">
-        <v>773417</v>
+        <v>773423</v>
       </c>
       <c r="Q41" s="12">
         <f t="shared" si="4"/>
-        <v>0.8647869276251644</v>
+        <v>0.86479363645308738</v>
       </c>
       <c r="R41" s="10">
         <v>899235</v>
@@ -7619,14 +7619,14 @@
       </c>
       <c r="T41" s="11">
         <f t="shared" si="5"/>
-        <v>170800</v>
+        <v>170806</v>
       </c>
       <c r="U41" s="3">
-        <v>780257</v>
+        <v>780263</v>
       </c>
       <c r="V41" s="12">
         <f t="shared" si="6"/>
-        <v>0.86768975851696162</v>
+        <v>0.86769643085511572</v>
       </c>
       <c r="W41" s="10">
         <v>900188</v>
@@ -7636,14 +7636,14 @@
       </c>
       <c r="Y41" s="11">
         <f t="shared" si="7"/>
-        <v>227456</v>
+        <v>227468</v>
       </c>
       <c r="Z41" s="3">
-        <v>786252</v>
+        <v>786264</v>
       </c>
       <c r="AA41" s="12">
         <f t="shared" si="8"/>
-        <v>0.87343088332659402</v>
+        <v>0.87344421387532378</v>
       </c>
       <c r="AB41" s="10">
         <v>900385</v>
@@ -7653,14 +7653,14 @@
       </c>
       <c r="AD41" s="11">
         <f t="shared" si="9"/>
-        <v>278300</v>
+        <v>278311</v>
       </c>
       <c r="AE41" s="3">
-        <v>790818</v>
+        <v>790829</v>
       </c>
       <c r="AF41" s="12">
         <f t="shared" si="10"/>
-        <v>0.87831094476251825</v>
+        <v>0.87832316175858105</v>
       </c>
       <c r="AG41" s="10">
         <v>896586</v>
@@ -7670,14 +7670,14 @@
       </c>
       <c r="AI41" s="11">
         <f t="shared" si="11"/>
-        <v>232852</v>
+        <v>232863</v>
       </c>
       <c r="AJ41" s="3">
-        <v>796662</v>
+        <v>796673</v>
       </c>
       <c r="AK41" s="12">
         <f t="shared" si="12"/>
-        <v>0.88855056848980463</v>
+        <v>0.88856283725152974</v>
       </c>
       <c r="AL41" s="10">
         <v>888836</v>
@@ -7687,14 +7687,14 @@
       </c>
       <c r="AN41" s="11">
         <f t="shared" si="13"/>
-        <v>136975</v>
+        <v>136985</v>
       </c>
       <c r="AO41" s="3">
-        <v>802500</v>
+        <v>802510</v>
       </c>
       <c r="AP41" s="12">
         <f t="shared" si="14"/>
-        <v>0.90286622054012211</v>
+        <v>0.90287747120953699</v>
       </c>
       <c r="AQ41" s="10">
         <v>877850</v>
@@ -7704,14 +7704,14 @@
       </c>
       <c r="AS41" s="11">
         <f t="shared" si="15"/>
-        <v>256439</v>
+        <v>256445</v>
       </c>
       <c r="AT41" s="3">
-        <v>809977</v>
+        <v>809983</v>
       </c>
       <c r="AU41" s="12">
         <f t="shared" si="16"/>
-        <v>0.92268269066469211</v>
+        <v>0.92268952554536654</v>
       </c>
       <c r="AV41" s="10">
         <v>870770</v>
@@ -7721,14 +7721,14 @@
       </c>
       <c r="AX41" s="11">
         <f t="shared" si="17"/>
-        <v>141878</v>
+        <v>141886</v>
       </c>
       <c r="AY41" s="3">
-        <v>814236</v>
+        <v>814244</v>
       </c>
       <c r="AZ41" s="12">
         <f t="shared" si="18"/>
-        <v>0.93507585240649083</v>
+        <v>0.93508503967752676</v>
       </c>
       <c r="BA41" s="10">
         <v>867846</v>
@@ -7738,14 +7738,14 @@
       </c>
       <c r="BC41" s="11">
         <f t="shared" si="19"/>
-        <v>163691</v>
+        <v>163695</v>
       </c>
       <c r="BD41" s="3">
-        <v>820747</v>
+        <v>820751</v>
       </c>
       <c r="BE41" s="12">
         <f t="shared" si="20"/>
-        <v>0.94572885051034405</v>
+        <v>0.94573345962302069</v>
       </c>
       <c r="BF41" s="10">
         <v>876639</v>
@@ -7755,14 +7755,14 @@
       </c>
       <c r="BH41" s="11">
         <f t="shared" si="21"/>
-        <v>773500</v>
+        <v>773508</v>
       </c>
       <c r="BI41" s="3">
-        <v>823823</v>
+        <v>823831</v>
       </c>
       <c r="BJ41" s="12">
         <f t="shared" si="22"/>
-        <v>0.93975171079543574</v>
+        <v>0.93976083655872034</v>
       </c>
     </row>
     <row r="42" spans="1:62" x14ac:dyDescent="0.3">
@@ -7782,11 +7782,11 @@
         <v>17282</v>
       </c>
       <c r="F42" s="3">
-        <v>17295</v>
+        <v>17297</v>
       </c>
       <c r="G42" s="12">
         <f t="shared" si="0"/>
-        <v>0.82727446666028892</v>
+        <v>0.82737013297617912</v>
       </c>
       <c r="H42" s="10">
         <v>20875</v>
@@ -7796,14 +7796,14 @@
       </c>
       <c r="J42" s="11">
         <f t="shared" si="1"/>
-        <v>5357</v>
+        <v>5359</v>
       </c>
       <c r="K42" s="3">
-        <v>17359</v>
+        <v>17361</v>
       </c>
       <c r="L42" s="12">
         <f t="shared" si="2"/>
-        <v>0.83156886227544913</v>
+        <v>0.83166467065868266</v>
       </c>
       <c r="M42" s="10">
         <v>20879</v>
@@ -7813,14 +7813,14 @@
       </c>
       <c r="O42" s="11">
         <f t="shared" si="3"/>
-        <v>5237</v>
+        <v>5239</v>
       </c>
       <c r="P42" s="3">
-        <v>17406</v>
+        <v>17408</v>
       </c>
       <c r="Q42" s="12">
         <f t="shared" si="4"/>
-        <v>0.83366061592988172</v>
+        <v>0.83375640595813971</v>
       </c>
       <c r="R42" s="10">
         <v>21076</v>
@@ -7830,14 +7830,14 @@
       </c>
       <c r="T42" s="11">
         <f t="shared" si="5"/>
-        <v>4508</v>
+        <v>4510</v>
       </c>
       <c r="U42" s="3">
-        <v>17521</v>
+        <v>17523</v>
       </c>
       <c r="V42" s="12">
         <f t="shared" si="6"/>
-        <v>0.83132472955019932</v>
+        <v>0.83141962421711901</v>
       </c>
       <c r="W42" s="10">
         <v>21069</v>
@@ -7847,14 +7847,14 @@
       </c>
       <c r="Y42" s="11">
         <f t="shared" si="7"/>
-        <v>5567</v>
+        <v>5569</v>
       </c>
       <c r="Z42" s="3">
-        <v>17588</v>
+        <v>17590</v>
       </c>
       <c r="AA42" s="12">
         <f t="shared" si="8"/>
-        <v>0.83478095780530637</v>
+        <v>0.83487588400018986</v>
       </c>
       <c r="AB42" s="10">
         <v>21025</v>
@@ -7864,14 +7864,14 @@
       </c>
       <c r="AD42" s="11">
         <f t="shared" si="9"/>
-        <v>6691</v>
+        <v>6693</v>
       </c>
       <c r="AE42" s="3">
-        <v>17734</v>
+        <v>17736</v>
       </c>
       <c r="AF42" s="12">
         <f t="shared" si="10"/>
-        <v>0.8434720570749108</v>
+        <v>0.84356718192627822</v>
       </c>
       <c r="AG42" s="10">
         <v>20898</v>
@@ -7881,14 +7881,14 @@
       </c>
       <c r="AI42" s="11">
         <f t="shared" si="11"/>
-        <v>5906</v>
+        <v>5907</v>
       </c>
       <c r="AJ42" s="3">
-        <v>17870</v>
+        <v>17871</v>
       </c>
       <c r="AK42" s="12">
         <f t="shared" si="12"/>
-        <v>0.85510575174657866</v>
+        <v>0.85515360321561873</v>
       </c>
       <c r="AL42" s="10">
         <v>20773</v>
@@ -7898,14 +7898,14 @@
       </c>
       <c r="AN42" s="11">
         <f t="shared" si="13"/>
-        <v>3444</v>
+        <v>3445</v>
       </c>
       <c r="AO42" s="3">
-        <v>17890</v>
+        <v>17891</v>
       </c>
       <c r="AP42" s="12">
         <f t="shared" si="14"/>
-        <v>0.86121407596399169</v>
+        <v>0.86126221537572811</v>
       </c>
       <c r="AQ42" s="10">
         <v>20391</v>
@@ -7915,14 +7915,14 @@
       </c>
       <c r="AS42" s="11">
         <f t="shared" si="15"/>
-        <v>6412</v>
+        <v>6413</v>
       </c>
       <c r="AT42" s="3">
-        <v>17964</v>
+        <v>17965</v>
       </c>
       <c r="AU42" s="12">
         <f t="shared" si="16"/>
-        <v>0.88097690157422393</v>
+        <v>0.88102594281790991</v>
       </c>
       <c r="AV42" s="10">
         <v>19656</v>
@@ -7932,14 +7932,14 @@
       </c>
       <c r="AX42" s="11">
         <f t="shared" si="17"/>
-        <v>3555</v>
+        <v>3556</v>
       </c>
       <c r="AY42" s="3">
-        <v>18003</v>
+        <v>18004</v>
       </c>
       <c r="AZ42" s="12">
         <f t="shared" si="18"/>
-        <v>0.91590354090354087</v>
+        <v>0.91595441595441596</v>
       </c>
       <c r="BA42" s="10">
         <v>19500</v>
@@ -9011,10 +9011,10 @@
       </c>
     </row>
     <row r="48" spans="1:62" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A48" s="24" t="s">
+      <c r="A48" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="B48" s="24"/>
+      <c r="B48" s="27"/>
       <c r="C48" s="6">
         <f>SUM(C10:C47)</f>
         <v>10233313</v>
@@ -9025,15 +9025,15 @@
       </c>
       <c r="E48" s="7">
         <f t="shared" ref="E48" si="23">F48-D48</f>
-        <v>2915108</v>
+        <v>2915130</v>
       </c>
       <c r="F48" s="8">
         <f>SUM(F10:F47)</f>
-        <v>8977086</v>
+        <v>8977108</v>
       </c>
       <c r="G48" s="5">
         <f>F48/C48</f>
-        <v>0.87724141732007999</v>
+        <v>0.87724356716148522</v>
       </c>
       <c r="H48" s="6">
         <f>SUM(H10:H47)</f>
@@ -9045,15 +9045,15 @@
       </c>
       <c r="J48" s="7">
         <f>K48-I48</f>
-        <v>2520054</v>
+        <v>2520074</v>
       </c>
       <c r="K48" s="8">
         <f>SUM(K10:K47)</f>
-        <v>9038462</v>
+        <v>9038482</v>
       </c>
       <c r="L48" s="5">
         <f>K48/H48</f>
-        <v>0.8787095704158141</v>
+        <v>0.87871151479433873</v>
       </c>
       <c r="M48" s="6">
         <f>SUM(M10:M47)</f>
@@ -9065,15 +9065,15 @@
       </c>
       <c r="O48" s="7">
         <f>P48-N48</f>
-        <v>2400860</v>
+        <v>2400879</v>
       </c>
       <c r="P48" s="8">
         <f>SUM(P10:P47)</f>
-        <v>9089524</v>
+        <v>9089543</v>
       </c>
       <c r="Q48" s="5">
         <f>P48/M48</f>
-        <v>0.87750278783429758</v>
+        <v>0.87750462209459201</v>
       </c>
       <c r="R48" s="6">
         <f>SUM(R10:R47)</f>
@@ -9085,15 +9085,15 @@
       </c>
       <c r="T48" s="7">
         <f>U48-S48</f>
-        <v>2087868</v>
+        <v>2087888</v>
       </c>
       <c r="U48" s="8">
         <f>SUM(U10:U47)</f>
-        <v>9168343</v>
+        <v>9168363</v>
       </c>
       <c r="V48" s="5">
         <f>U48/R48</f>
-        <v>0.87930874417196825</v>
+        <v>0.87931066231299804</v>
       </c>
       <c r="W48" s="6">
         <f>SUM(W10:W47)</f>
@@ -9105,15 +9105,15 @@
       </c>
       <c r="Y48" s="7">
         <f>Z48-X48</f>
-        <v>2662360</v>
+        <v>2662389</v>
       </c>
       <c r="Z48" s="8">
         <f>SUM(Z10:Z47)</f>
-        <v>9229579</v>
+        <v>9229608</v>
       </c>
       <c r="AA48" s="5">
         <f>Z48/W48</f>
-        <v>0.88271568630545216</v>
+        <v>0.88271845986152686</v>
       </c>
       <c r="AB48" s="6">
         <f>SUM(AB10:AB47)</f>
@@ -9125,15 +9125,15 @@
       </c>
       <c r="AD48" s="7">
         <f>AE48-AC48</f>
-        <v>3305578</v>
+        <v>3305606</v>
       </c>
       <c r="AE48" s="8">
         <f>SUM(AE10:AE47)</f>
-        <v>9295931</v>
+        <v>9295959</v>
       </c>
       <c r="AF48" s="5">
         <f>AE48/AB48</f>
-        <v>0.88754020264251399</v>
+        <v>0.88754287597622028</v>
       </c>
       <c r="AG48" s="6">
         <f>SUM(AG10:AG47)</f>
@@ -9145,15 +9145,15 @@
       </c>
       <c r="AI48" s="7">
         <f>AJ48-AH48</f>
-        <v>2880788</v>
+        <v>2880815</v>
       </c>
       <c r="AJ48" s="8">
         <f>SUM(AJ10:AJ47)</f>
-        <v>9363596</v>
+        <v>9363623</v>
       </c>
       <c r="AK48" s="5">
         <f>AJ48/AG48</f>
-        <v>0.89219046210675801</v>
+        <v>0.89219303474471423</v>
       </c>
       <c r="AL48" s="6">
         <f>SUM(AL10:AL47)</f>
@@ -9165,15 +9165,15 @@
       </c>
       <c r="AN48" s="7">
         <f>AO48-AM48</f>
-        <v>1785230</v>
+        <v>1785252</v>
       </c>
       <c r="AO48" s="8">
         <f>SUM(AO10:AO47)</f>
-        <v>9435019</v>
+        <v>9435041</v>
       </c>
       <c r="AP48" s="5">
         <f>AO48/AL48</f>
-        <v>0.90042210481712925</v>
+        <v>0.90042420436629877</v>
       </c>
       <c r="AQ48" s="6">
         <f>SUM(AQ10:AQ47)</f>
@@ -9185,15 +9185,15 @@
       </c>
       <c r="AS48" s="7">
         <f>AT48-AR48</f>
-        <v>2955224</v>
+        <v>2955244</v>
       </c>
       <c r="AT48" s="8">
         <f>SUM(AT10:AT47)</f>
-        <v>9520095</v>
+        <v>9520115</v>
       </c>
       <c r="AU48" s="5">
         <f>AT48/AQ48</f>
-        <v>0.91797591031541992</v>
+        <v>0.91797783881699546</v>
       </c>
       <c r="AV48" s="6">
         <f>SUM(AV10:AV47)</f>
@@ -9205,15 +9205,15 @@
       </c>
       <c r="AX48" s="7">
         <f>AY48-AW48</f>
-        <v>1784498</v>
+        <v>1784516</v>
       </c>
       <c r="AY48" s="8">
         <f>SUM(AY10:AY47)</f>
-        <v>9585344</v>
+        <v>9585362</v>
       </c>
       <c r="AZ48" s="5">
         <f>AY48/AV48</f>
-        <v>0.92542875936269064</v>
+        <v>0.92543049719470472</v>
       </c>
       <c r="BA48" s="6">
         <f>SUM(BA10:BA47)</f>
@@ -9225,15 +9225,15 @@
       </c>
       <c r="BC48" s="7">
         <f>BD48-BB48</f>
-        <v>2313736</v>
+        <v>2313753</v>
       </c>
       <c r="BD48" s="8">
         <f>SUM(BD10:BD47)</f>
-        <v>9653734</v>
+        <v>9653751</v>
       </c>
       <c r="BE48" s="5">
         <f>BD48/BA48</f>
-        <v>0.93073175039658906</v>
+        <v>0.93073338939345351</v>
       </c>
       <c r="BF48" s="6">
         <f>SUM(BF10:BF47)</f>
@@ -9245,35 +9245,29 @@
       </c>
       <c r="BH48" s="7">
         <f>BI48-BG48</f>
-        <v>9066652</v>
+        <v>9066674</v>
       </c>
       <c r="BI48" s="8">
         <f>SUM(BI10:BI47)</f>
-        <v>9676025</v>
+        <v>9676047</v>
       </c>
       <c r="BJ48" s="5">
         <f>BI48/BF48</f>
-        <v>0.92790754320905966</v>
+        <v>0.92790965295618721</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A59" s="21" t="s">
+      <c r="A59" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="B59" s="21"/>
-      <c r="C59" s="21"/>
-      <c r="D59" s="21"/>
-      <c r="E59" s="21"/>
+      <c r="B59" s="26"/>
+      <c r="C59" s="26"/>
+      <c r="D59" s="26"/>
+      <c r="E59" s="26"/>
       <c r="F59" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="C8:G8"/>
     <mergeCell ref="A59:E59"/>
     <mergeCell ref="AQ8:AU8"/>
     <mergeCell ref="AV8:AZ8"/>
@@ -9287,6 +9281,12 @@
     <mergeCell ref="AG8:AK8"/>
     <mergeCell ref="AL8:AP8"/>
     <mergeCell ref="H8:L8"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C8:G8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/gstdatabase/GSTR-3B-2019-2020.xlsx
+++ b/gstdatabase/GSTR-3B-2019-2020.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\Jun-26\GST Statistics Downloads 31st May 26\Downloads\GSTR 3B\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\Jul-26\GST Statistics Downloads 31st Jul 26\Downloads\GSTR 3B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91F9D3A5-31E1-4001-A701-6471A6043E81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C146DE02-F707-4A3B-9476-DE706191E4F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -185,10 +185,10 @@
     <t>STATE WISE RETURN PERIOD WISE GSTR-3B FILING SUMMARY</t>
   </si>
   <si>
-    <t>Data Considered upto 30th Jun 2026</t>
+    <t>Data Considered upto 31st Jul 2026</t>
   </si>
   <si>
-    <t>Filing %age as on 30th Jun 2026</t>
+    <t>Filing %age as on 31st Jul 2026</t>
   </si>
 </sst>
 </file>
@@ -367,6 +367,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="17" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -375,18 +387,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -671,7 +671,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BJ59"/>
+  <dimension ref="A1:BJ57"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="27.44140625" bestFit="1" customWidth="1"/>
@@ -679,12 +679,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:62" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
     </row>
     <row r="2" spans="1:62" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -701,10 +701,10 @@
       <c r="L2" s="1"/>
     </row>
     <row r="3" spans="1:62" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="22" t="s">
+      <c r="A3" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="22"/>
+      <c r="B3" s="26"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
@@ -731,107 +731,107 @@
       <c r="L4" s="1"/>
     </row>
     <row r="5" spans="1:62" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="22" t="s">
+      <c r="A5" s="26" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="22"/>
-      <c r="C5" s="22"/>
+      <c r="B5" s="26"/>
+      <c r="C5" s="26"/>
     </row>
     <row r="8" spans="1:62" s="17" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="23" t="s">
+      <c r="A8" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="24" t="s">
+      <c r="B8" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="C8" s="25">
+      <c r="C8" s="22">
         <v>43556</v>
       </c>
-      <c r="D8" s="24"/>
-      <c r="E8" s="24"/>
-      <c r="F8" s="24"/>
-      <c r="G8" s="24"/>
-      <c r="H8" s="25">
+      <c r="D8" s="23"/>
+      <c r="E8" s="23"/>
+      <c r="F8" s="23"/>
+      <c r="G8" s="23"/>
+      <c r="H8" s="22">
         <v>43586</v>
       </c>
-      <c r="I8" s="24"/>
-      <c r="J8" s="24"/>
-      <c r="K8" s="24"/>
-      <c r="L8" s="24"/>
-      <c r="M8" s="25">
+      <c r="I8" s="23"/>
+      <c r="J8" s="23"/>
+      <c r="K8" s="23"/>
+      <c r="L8" s="23"/>
+      <c r="M8" s="22">
         <v>43617</v>
       </c>
-      <c r="N8" s="24"/>
-      <c r="O8" s="24"/>
-      <c r="P8" s="24"/>
-      <c r="Q8" s="24"/>
-      <c r="R8" s="25">
+      <c r="N8" s="23"/>
+      <c r="O8" s="23"/>
+      <c r="P8" s="23"/>
+      <c r="Q8" s="23"/>
+      <c r="R8" s="22">
         <v>43647</v>
       </c>
-      <c r="S8" s="24"/>
-      <c r="T8" s="24"/>
-      <c r="U8" s="24"/>
-      <c r="V8" s="24"/>
-      <c r="W8" s="25">
+      <c r="S8" s="23"/>
+      <c r="T8" s="23"/>
+      <c r="U8" s="23"/>
+      <c r="V8" s="23"/>
+      <c r="W8" s="22">
         <v>43678</v>
       </c>
-      <c r="X8" s="24"/>
-      <c r="Y8" s="24"/>
-      <c r="Z8" s="24"/>
-      <c r="AA8" s="24"/>
-      <c r="AB8" s="25">
+      <c r="X8" s="23"/>
+      <c r="Y8" s="23"/>
+      <c r="Z8" s="23"/>
+      <c r="AA8" s="23"/>
+      <c r="AB8" s="22">
         <v>43709</v>
       </c>
-      <c r="AC8" s="24"/>
-      <c r="AD8" s="24"/>
-      <c r="AE8" s="24"/>
-      <c r="AF8" s="24"/>
-      <c r="AG8" s="25">
+      <c r="AC8" s="23"/>
+      <c r="AD8" s="23"/>
+      <c r="AE8" s="23"/>
+      <c r="AF8" s="23"/>
+      <c r="AG8" s="22">
         <v>43739</v>
       </c>
-      <c r="AH8" s="24"/>
-      <c r="AI8" s="24"/>
-      <c r="AJ8" s="24"/>
-      <c r="AK8" s="24"/>
-      <c r="AL8" s="25">
+      <c r="AH8" s="23"/>
+      <c r="AI8" s="23"/>
+      <c r="AJ8" s="23"/>
+      <c r="AK8" s="23"/>
+      <c r="AL8" s="22">
         <v>43770</v>
       </c>
-      <c r="AM8" s="24"/>
-      <c r="AN8" s="24"/>
-      <c r="AO8" s="24"/>
-      <c r="AP8" s="24"/>
-      <c r="AQ8" s="25">
+      <c r="AM8" s="23"/>
+      <c r="AN8" s="23"/>
+      <c r="AO8" s="23"/>
+      <c r="AP8" s="23"/>
+      <c r="AQ8" s="22">
         <v>43800</v>
       </c>
-      <c r="AR8" s="24"/>
-      <c r="AS8" s="24"/>
-      <c r="AT8" s="24"/>
-      <c r="AU8" s="24"/>
-      <c r="AV8" s="25">
+      <c r="AR8" s="23"/>
+      <c r="AS8" s="23"/>
+      <c r="AT8" s="23"/>
+      <c r="AU8" s="23"/>
+      <c r="AV8" s="22">
         <v>43831</v>
       </c>
-      <c r="AW8" s="24"/>
-      <c r="AX8" s="24"/>
-      <c r="AY8" s="24"/>
-      <c r="AZ8" s="24"/>
-      <c r="BA8" s="25">
+      <c r="AW8" s="23"/>
+      <c r="AX8" s="23"/>
+      <c r="AY8" s="23"/>
+      <c r="AZ8" s="23"/>
+      <c r="BA8" s="22">
         <v>43862</v>
       </c>
-      <c r="BB8" s="24"/>
-      <c r="BC8" s="24"/>
-      <c r="BD8" s="24"/>
-      <c r="BE8" s="24"/>
-      <c r="BF8" s="25">
+      <c r="BB8" s="23"/>
+      <c r="BC8" s="23"/>
+      <c r="BD8" s="23"/>
+      <c r="BE8" s="23"/>
+      <c r="BF8" s="22">
         <v>43891</v>
       </c>
-      <c r="BG8" s="24"/>
-      <c r="BH8" s="24"/>
-      <c r="BI8" s="24"/>
-      <c r="BJ8" s="24"/>
+      <c r="BG8" s="23"/>
+      <c r="BH8" s="23"/>
+      <c r="BI8" s="23"/>
+      <c r="BJ8" s="23"/>
     </row>
     <row r="9" spans="1:62" s="17" customFormat="1" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="A9" s="23"/>
-      <c r="B9" s="24"/>
+      <c r="A9" s="27"/>
+      <c r="B9" s="23"/>
       <c r="C9" s="18" t="s">
         <v>3</v>
       </c>
@@ -2507,11 +2507,11 @@
         <v>487170</v>
       </c>
       <c r="F17" s="3">
-        <v>487418</v>
+        <v>487420</v>
       </c>
       <c r="G17" s="12">
         <f t="shared" si="0"/>
-        <v>0.88027985869808634</v>
+        <v>0.88028347071019386</v>
       </c>
       <c r="H17" s="10">
         <v>557836</v>
@@ -2521,14 +2521,14 @@
       </c>
       <c r="J17" s="11">
         <f t="shared" si="1"/>
-        <v>119060</v>
+        <v>119062</v>
       </c>
       <c r="K17" s="3">
-        <v>491127</v>
+        <v>491129</v>
       </c>
       <c r="L17" s="12">
         <f t="shared" si="2"/>
-        <v>0.88041467384679373</v>
+        <v>0.88041825912992344</v>
       </c>
       <c r="M17" s="10">
         <v>560439</v>
@@ -2538,14 +2538,14 @@
       </c>
       <c r="O17" s="11">
         <f t="shared" si="3"/>
-        <v>114183</v>
+        <v>114185</v>
       </c>
       <c r="P17" s="3">
-        <v>494269</v>
+        <v>494271</v>
       </c>
       <c r="Q17" s="12">
         <f t="shared" si="4"/>
-        <v>0.88193184271615643</v>
+        <v>0.88193541134717601</v>
       </c>
       <c r="R17" s="10">
         <v>561513</v>
@@ -2555,14 +2555,14 @@
       </c>
       <c r="T17" s="11">
         <f t="shared" si="5"/>
-        <v>96204</v>
+        <v>96206</v>
       </c>
       <c r="U17" s="3">
-        <v>498345</v>
+        <v>498347</v>
       </c>
       <c r="V17" s="12">
         <f t="shared" si="6"/>
-        <v>0.88750394024715362</v>
+        <v>0.88750750205249029</v>
       </c>
       <c r="W17" s="10">
         <v>560642</v>
@@ -2572,14 +2572,14 @@
       </c>
       <c r="Y17" s="11">
         <f t="shared" si="7"/>
-        <v>126338</v>
+        <v>126340</v>
       </c>
       <c r="Z17" s="3">
-        <v>500736</v>
+        <v>500738</v>
       </c>
       <c r="AA17" s="12">
         <f t="shared" si="8"/>
-        <v>0.89314749876034971</v>
+        <v>0.89315106609922201</v>
       </c>
       <c r="AB17" s="10">
         <v>559918</v>
@@ -2589,14 +2589,14 @@
       </c>
       <c r="AD17" s="11">
         <f t="shared" si="9"/>
-        <v>167229</v>
+        <v>167231</v>
       </c>
       <c r="AE17" s="3">
-        <v>504383</v>
+        <v>504385</v>
       </c>
       <c r="AF17" s="12">
         <f t="shared" si="10"/>
-        <v>0.9008158337470844</v>
+        <v>0.90081940569869157</v>
       </c>
       <c r="AG17" s="10">
         <v>561583</v>
@@ -2606,14 +2606,14 @@
       </c>
       <c r="AI17" s="11">
         <f t="shared" si="11"/>
-        <v>143632</v>
+        <v>143633</v>
       </c>
       <c r="AJ17" s="3">
-        <v>508326</v>
+        <v>508327</v>
       </c>
       <c r="AK17" s="12">
         <f t="shared" si="12"/>
-        <v>0.9051662888655817</v>
+        <v>0.90516806954626472</v>
       </c>
       <c r="AL17" s="10">
         <v>559753</v>
@@ -2623,14 +2623,14 @@
       </c>
       <c r="AN17" s="11">
         <f t="shared" si="13"/>
-        <v>81141</v>
+        <v>81142</v>
       </c>
       <c r="AO17" s="3">
-        <v>511820</v>
+        <v>511821</v>
       </c>
       <c r="AP17" s="12">
         <f t="shared" si="14"/>
-        <v>0.91436758713218147</v>
+        <v>0.91436937363444237</v>
       </c>
       <c r="AQ17" s="10">
         <v>541872</v>
@@ -2640,14 +2640,14 @@
       </c>
       <c r="AS17" s="11">
         <f t="shared" si="15"/>
-        <v>151531</v>
+        <v>151532</v>
       </c>
       <c r="AT17" s="3">
-        <v>515484</v>
+        <v>515485</v>
       </c>
       <c r="AU17" s="12">
         <f t="shared" si="16"/>
-        <v>0.95130215253786876</v>
+        <v>0.95130399799214571</v>
       </c>
       <c r="AV17" s="10">
         <v>543495</v>
@@ -2657,14 +2657,14 @@
       </c>
       <c r="AX17" s="11">
         <f t="shared" si="17"/>
-        <v>80657</v>
+        <v>80658</v>
       </c>
       <c r="AY17" s="3">
-        <v>518293</v>
+        <v>518294</v>
       </c>
       <c r="AZ17" s="12">
         <f t="shared" si="18"/>
-        <v>0.95362974820375535</v>
+        <v>0.95363158814708504</v>
       </c>
       <c r="BA17" s="10">
         <v>547860</v>
@@ -2674,14 +2674,14 @@
       </c>
       <c r="BC17" s="11">
         <f t="shared" si="19"/>
-        <v>132522</v>
+        <v>132523</v>
       </c>
       <c r="BD17" s="3">
-        <v>522895</v>
+        <v>522896</v>
       </c>
       <c r="BE17" s="12">
         <f t="shared" si="20"/>
-        <v>0.95443178914321181</v>
+        <v>0.95443361442704344</v>
       </c>
       <c r="BF17" s="10">
         <v>552190</v>
@@ -2691,14 +2691,14 @@
       </c>
       <c r="BH17" s="11">
         <f t="shared" si="21"/>
-        <v>503404</v>
+        <v>503406</v>
       </c>
       <c r="BI17" s="3">
-        <v>526188</v>
+        <v>526190</v>
       </c>
       <c r="BJ17" s="12">
         <f t="shared" si="22"/>
-        <v>0.95291113565982721</v>
+        <v>0.9529147576015502</v>
       </c>
     </row>
     <row r="18" spans="1:62" x14ac:dyDescent="0.3">
@@ -2718,11 +2718,11 @@
         <v>977646</v>
       </c>
       <c r="F18" s="3">
-        <v>978118</v>
+        <v>978119</v>
       </c>
       <c r="G18" s="12">
         <f t="shared" si="0"/>
-        <v>0.87817863661706785</v>
+        <v>0.87817953444190755</v>
       </c>
       <c r="H18" s="10">
         <v>1112907</v>
@@ -2732,14 +2732,14 @@
       </c>
       <c r="J18" s="11">
         <f t="shared" si="1"/>
-        <v>228451</v>
+        <v>228452</v>
       </c>
       <c r="K18" s="3">
-        <v>985776</v>
+        <v>985777</v>
       </c>
       <c r="L18" s="12">
         <f t="shared" si="2"/>
-        <v>0.88576673522585447</v>
+        <v>0.88576763377353185</v>
       </c>
       <c r="M18" s="10">
         <v>1118687</v>
@@ -2749,14 +2749,14 @@
       </c>
       <c r="O18" s="11">
         <f t="shared" si="3"/>
-        <v>221700</v>
+        <v>221701</v>
       </c>
       <c r="P18" s="3">
-        <v>991280</v>
+        <v>991281</v>
       </c>
       <c r="Q18" s="12">
         <f t="shared" si="4"/>
-        <v>0.88611023458751192</v>
+        <v>0.88611112849259888</v>
       </c>
       <c r="R18" s="10">
         <v>1127309</v>
@@ -2766,14 +2766,14 @@
       </c>
       <c r="T18" s="11">
         <f t="shared" si="5"/>
-        <v>178383</v>
+        <v>178384</v>
       </c>
       <c r="U18" s="3">
-        <v>1000097</v>
+        <v>1000098</v>
       </c>
       <c r="V18" s="12">
         <f t="shared" si="6"/>
-        <v>0.88715427624546594</v>
+        <v>0.88715516331369659</v>
       </c>
       <c r="W18" s="10">
         <v>1128388</v>
@@ -2783,14 +2783,14 @@
       </c>
       <c r="Y18" s="11">
         <f t="shared" si="7"/>
-        <v>244987</v>
+        <v>244988</v>
       </c>
       <c r="Z18" s="3">
-        <v>1007721</v>
+        <v>1007722</v>
       </c>
       <c r="AA18" s="12">
         <f t="shared" si="8"/>
-        <v>0.89306249268868509</v>
+        <v>0.89306337890867327</v>
       </c>
       <c r="AB18" s="10">
         <v>1126122</v>
@@ -3351,11 +3351,11 @@
         <v>8222</v>
       </c>
       <c r="F21" s="3">
-        <v>8290</v>
+        <v>8291</v>
       </c>
       <c r="G21" s="12">
         <f t="shared" si="0"/>
-        <v>0.76560768378278532</v>
+        <v>0.76570003694126343</v>
       </c>
       <c r="H21" s="10">
         <v>10989</v>
@@ -3365,14 +3365,14 @@
       </c>
       <c r="J21" s="11">
         <f t="shared" si="1"/>
-        <v>4995</v>
+        <v>4996</v>
       </c>
       <c r="K21" s="3">
-        <v>8340</v>
+        <v>8341</v>
       </c>
       <c r="L21" s="12">
         <f t="shared" si="2"/>
-        <v>0.75894075894075896</v>
+        <v>0.75903175903175901</v>
       </c>
       <c r="M21" s="10">
         <v>11143</v>
@@ -3382,14 +3382,14 @@
       </c>
       <c r="O21" s="11">
         <f t="shared" si="3"/>
-        <v>4765</v>
+        <v>4766</v>
       </c>
       <c r="P21" s="3">
-        <v>8397</v>
+        <v>8398</v>
       </c>
       <c r="Q21" s="12">
         <f t="shared" si="4"/>
-        <v>0.75356726195818002</v>
+        <v>0.75365700439737948</v>
       </c>
       <c r="R21" s="10">
         <v>11396</v>
@@ -3399,14 +3399,14 @@
       </c>
       <c r="T21" s="11">
         <f t="shared" si="5"/>
-        <v>4332</v>
+        <v>4333</v>
       </c>
       <c r="U21" s="3">
-        <v>8565</v>
+        <v>8566</v>
       </c>
       <c r="V21" s="12">
         <f t="shared" si="6"/>
-        <v>0.7515795015795016</v>
+        <v>0.75166725166725168</v>
       </c>
       <c r="W21" s="10">
         <v>11658</v>
@@ -3416,14 +3416,14 @@
       </c>
       <c r="Y21" s="11">
         <f t="shared" si="7"/>
-        <v>4718</v>
+        <v>4719</v>
       </c>
       <c r="Z21" s="3">
-        <v>8748</v>
+        <v>8749</v>
       </c>
       <c r="AA21" s="12">
         <f t="shared" si="8"/>
-        <v>0.75038600102933606</v>
+        <v>0.75047177903585516</v>
       </c>
       <c r="AB21" s="10">
         <v>11960</v>
@@ -3433,14 +3433,14 @@
       </c>
       <c r="AD21" s="11">
         <f t="shared" si="9"/>
-        <v>5133</v>
+        <v>5134</v>
       </c>
       <c r="AE21" s="3">
-        <v>8954</v>
+        <v>8955</v>
       </c>
       <c r="AF21" s="12">
         <f t="shared" si="10"/>
-        <v>0.74866220735785949</v>
+        <v>0.74874581939799334</v>
       </c>
       <c r="AG21" s="10">
         <v>12126</v>
@@ -3450,14 +3450,14 @@
       </c>
       <c r="AI21" s="11">
         <f t="shared" si="11"/>
-        <v>4719</v>
+        <v>4720</v>
       </c>
       <c r="AJ21" s="3">
-        <v>9062</v>
+        <v>9063</v>
       </c>
       <c r="AK21" s="12">
         <f t="shared" si="12"/>
-        <v>0.74731980867557313</v>
+        <v>0.74740227610094012</v>
       </c>
       <c r="AL21" s="10">
         <v>12318</v>
@@ -3467,14 +3467,14 @@
       </c>
       <c r="AN21" s="11">
         <f t="shared" si="13"/>
-        <v>4266</v>
+        <v>4267</v>
       </c>
       <c r="AO21" s="3">
-        <v>9186</v>
+        <v>9187</v>
       </c>
       <c r="AP21" s="12">
         <f t="shared" si="14"/>
-        <v>0.7457379444715051</v>
+        <v>0.74581912648157167</v>
       </c>
       <c r="AQ21" s="10">
         <v>12515</v>
@@ -3484,14 +3484,14 @@
       </c>
       <c r="AS21" s="11">
         <f t="shared" si="15"/>
-        <v>4857</v>
+        <v>4858</v>
       </c>
       <c r="AT21" s="3">
-        <v>9291</v>
+        <v>9292</v>
       </c>
       <c r="AU21" s="12">
         <f t="shared" si="16"/>
-        <v>0.74238913304035159</v>
+        <v>0.74246903715541346</v>
       </c>
       <c r="AV21" s="10">
         <v>12661</v>
@@ -3501,14 +3501,14 @@
       </c>
       <c r="AX21" s="11">
         <f t="shared" si="17"/>
-        <v>3813</v>
+        <v>3814</v>
       </c>
       <c r="AY21" s="3">
-        <v>9426</v>
+        <v>9427</v>
       </c>
       <c r="AZ21" s="12">
         <f t="shared" si="18"/>
-        <v>0.74449095648053076</v>
+        <v>0.74456993918331882</v>
       </c>
       <c r="BA21" s="10">
         <v>12621</v>
@@ -3518,14 +3518,14 @@
       </c>
       <c r="BC21" s="11">
         <f t="shared" si="19"/>
-        <v>4213</v>
+        <v>4214</v>
       </c>
       <c r="BD21" s="3">
-        <v>9593</v>
+        <v>9594</v>
       </c>
       <c r="BE21" s="12">
         <f t="shared" si="20"/>
-        <v>0.76008240234529756</v>
+        <v>0.76016163536962211</v>
       </c>
       <c r="BF21" s="10">
         <v>12538</v>
@@ -3535,14 +3535,14 @@
       </c>
       <c r="BH21" s="11">
         <f t="shared" si="21"/>
-        <v>8965</v>
+        <v>8966</v>
       </c>
       <c r="BI21" s="3">
-        <v>9669</v>
+        <v>9670</v>
       </c>
       <c r="BJ21" s="12">
         <f t="shared" si="22"/>
-        <v>0.77117562609666612</v>
+        <v>0.77125538363375334</v>
       </c>
     </row>
     <row r="22" spans="1:62" x14ac:dyDescent="0.3">
@@ -3984,11 +3984,11 @@
         <v>4208</v>
       </c>
       <c r="F24" s="3">
-        <v>4215</v>
+        <v>4216</v>
       </c>
       <c r="G24" s="12">
         <f t="shared" si="0"/>
-        <v>0.79483311333207618</v>
+        <v>0.79502168583820476</v>
       </c>
       <c r="H24" s="10">
         <v>5386</v>
@@ -4066,14 +4066,14 @@
       </c>
       <c r="AD24" s="11">
         <f t="shared" si="9"/>
-        <v>1957</v>
+        <v>1958</v>
       </c>
       <c r="AE24" s="3">
-        <v>4548</v>
+        <v>4549</v>
       </c>
       <c r="AF24" s="12">
         <f t="shared" si="10"/>
-        <v>0.7841379310344827</v>
+        <v>0.78431034482758621</v>
       </c>
       <c r="AG24" s="10">
         <v>5880</v>
@@ -4083,14 +4083,14 @@
       </c>
       <c r="AI24" s="11">
         <f t="shared" si="11"/>
-        <v>1917</v>
+        <v>1918</v>
       </c>
       <c r="AJ24" s="3">
-        <v>4610</v>
+        <v>4611</v>
       </c>
       <c r="AK24" s="12">
         <f t="shared" si="12"/>
-        <v>0.78401360544217691</v>
+        <v>0.78418367346938778</v>
       </c>
       <c r="AL24" s="10">
         <v>5984</v>
@@ -4100,14 +4100,14 @@
       </c>
       <c r="AN24" s="11">
         <f t="shared" si="13"/>
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="AO24" s="3">
-        <v>4665</v>
+        <v>4666</v>
       </c>
       <c r="AP24" s="12">
         <f t="shared" si="14"/>
-        <v>0.77957887700534756</v>
+        <v>0.77974598930481287</v>
       </c>
       <c r="AQ24" s="10">
         <v>6083</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="AS24" s="11">
         <f t="shared" si="15"/>
-        <v>2043</v>
+        <v>2044</v>
       </c>
       <c r="AT24" s="3">
-        <v>4734</v>
+        <v>4735</v>
       </c>
       <c r="AU24" s="12">
         <f t="shared" si="16"/>
-        <v>0.77823442380404406</v>
+        <v>0.77839881637349995</v>
       </c>
       <c r="AV24" s="10">
         <v>6170</v>
@@ -4134,14 +4134,14 @@
       </c>
       <c r="AX24" s="11">
         <f t="shared" si="17"/>
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="AY24" s="3">
-        <v>4764</v>
+        <v>4765</v>
       </c>
       <c r="AZ24" s="12">
         <f t="shared" si="18"/>
-        <v>0.77212317666126418</v>
+        <v>0.77228525121555913</v>
       </c>
       <c r="BA24" s="10">
         <v>6245</v>
@@ -4151,14 +4151,14 @@
       </c>
       <c r="BC24" s="11">
         <f t="shared" si="19"/>
-        <v>1604</v>
+        <v>1606</v>
       </c>
       <c r="BD24" s="3">
-        <v>4821</v>
+        <v>4823</v>
       </c>
       <c r="BE24" s="12">
         <f t="shared" si="20"/>
-        <v>0.77197758206565248</v>
+        <v>0.77229783827061649</v>
       </c>
       <c r="BF24" s="10">
         <v>6256</v>
@@ -4168,14 +4168,14 @@
       </c>
       <c r="BH24" s="11">
         <f t="shared" si="21"/>
-        <v>3499</v>
+        <v>3500</v>
       </c>
       <c r="BI24" s="3">
-        <v>4864</v>
+        <v>4865</v>
       </c>
       <c r="BJ24" s="12">
         <f t="shared" si="22"/>
-        <v>0.77749360613810736</v>
+        <v>0.77765345268542196</v>
       </c>
     </row>
     <row r="25" spans="1:62" x14ac:dyDescent="0.3">
@@ -4454,14 +4454,14 @@
       </c>
       <c r="T26" s="11">
         <f t="shared" si="5"/>
-        <v>5650</v>
+        <v>5651</v>
       </c>
       <c r="U26" s="3">
-        <v>20652</v>
+        <v>20653</v>
       </c>
       <c r="V26" s="12">
         <f t="shared" si="6"/>
-        <v>0.80546021840873638</v>
+        <v>0.8054992199687987</v>
       </c>
       <c r="W26" s="10">
         <v>25884</v>
@@ -4471,14 +4471,14 @@
       </c>
       <c r="Y26" s="11">
         <f t="shared" si="7"/>
-        <v>6419</v>
+        <v>6420</v>
       </c>
       <c r="Z26" s="3">
-        <v>20817</v>
+        <v>20818</v>
       </c>
       <c r="AA26" s="12">
         <f t="shared" si="8"/>
-        <v>0.80424200278164115</v>
+        <v>0.80428063668675631</v>
       </c>
       <c r="AB26" s="10">
         <v>26140</v>
@@ -4488,14 +4488,14 @@
       </c>
       <c r="AD26" s="11">
         <f t="shared" si="9"/>
-        <v>7478</v>
+        <v>7479</v>
       </c>
       <c r="AE26" s="3">
-        <v>20977</v>
+        <v>20978</v>
       </c>
       <c r="AF26" s="12">
         <f t="shared" si="10"/>
-        <v>0.80248661055853099</v>
+        <v>0.80252486610558527</v>
       </c>
       <c r="AG26" s="10">
         <v>26255</v>
@@ -4505,14 +4505,14 @@
       </c>
       <c r="AI26" s="11">
         <f t="shared" si="11"/>
-        <v>6656</v>
+        <v>6657</v>
       </c>
       <c r="AJ26" s="3">
-        <v>21058</v>
+        <v>21059</v>
       </c>
       <c r="AK26" s="12">
         <f t="shared" si="12"/>
-        <v>0.8020567510950295</v>
+        <v>0.80209483907827084</v>
       </c>
       <c r="AL26" s="10">
         <v>26357</v>
@@ -4522,14 +4522,14 @@
       </c>
       <c r="AN26" s="11">
         <f t="shared" si="13"/>
-        <v>6662</v>
+        <v>6663</v>
       </c>
       <c r="AO26" s="3">
-        <v>21054</v>
+        <v>21055</v>
       </c>
       <c r="AP26" s="12">
         <f t="shared" si="14"/>
-        <v>0.7988010775126152</v>
+        <v>0.79883901809765911</v>
       </c>
       <c r="AQ26" s="10">
         <v>26428</v>
@@ -4539,14 +4539,14 @@
       </c>
       <c r="AS26" s="11">
         <f t="shared" si="15"/>
-        <v>8147</v>
+        <v>8148</v>
       </c>
       <c r="AT26" s="3">
-        <v>21060</v>
+        <v>21061</v>
       </c>
       <c r="AU26" s="12">
         <f t="shared" si="16"/>
-        <v>0.79688209474799454</v>
+        <v>0.7969199334039655</v>
       </c>
       <c r="AV26" s="10">
         <v>26536</v>
@@ -4617,11 +4617,11 @@
         <v>119095</v>
       </c>
       <c r="F27" s="3">
-        <v>119353</v>
+        <v>119355</v>
       </c>
       <c r="G27" s="12">
         <f t="shared" si="0"/>
-        <v>0.75605430024768316</v>
+        <v>0.7560669694608616</v>
       </c>
       <c r="H27" s="10">
         <v>159240</v>
@@ -4631,14 +4631,14 @@
       </c>
       <c r="J27" s="11">
         <f t="shared" si="1"/>
-        <v>52400</v>
+        <v>52402</v>
       </c>
       <c r="K27" s="3">
-        <v>120251</v>
+        <v>120253</v>
       </c>
       <c r="L27" s="12">
         <f t="shared" si="2"/>
-        <v>0.7551557397638784</v>
+        <v>0.75516829942225572</v>
       </c>
       <c r="M27" s="10">
         <v>161175</v>
@@ -4648,14 +4648,14 @@
       </c>
       <c r="O27" s="11">
         <f t="shared" si="3"/>
-        <v>51224</v>
+        <v>51226</v>
       </c>
       <c r="P27" s="3">
-        <v>121472</v>
+        <v>121474</v>
       </c>
       <c r="Q27" s="12">
         <f t="shared" si="4"/>
-        <v>0.75366527066852795</v>
+        <v>0.75367767954087173</v>
       </c>
       <c r="R27" s="10">
         <v>163738</v>
@@ -4665,14 +4665,14 @@
       </c>
       <c r="T27" s="11">
         <f t="shared" si="5"/>
-        <v>45704</v>
+        <v>45706</v>
       </c>
       <c r="U27" s="3">
-        <v>123211</v>
+        <v>123213</v>
       </c>
       <c r="V27" s="12">
         <f t="shared" si="6"/>
-        <v>0.75248873199868083</v>
+        <v>0.75250094663425715</v>
       </c>
       <c r="W27" s="10">
         <v>165285</v>
@@ -4682,14 +4682,14 @@
       </c>
       <c r="Y27" s="11">
         <f t="shared" si="7"/>
-        <v>54510</v>
+        <v>54512</v>
       </c>
       <c r="Z27" s="3">
-        <v>124681</v>
+        <v>124683</v>
       </c>
       <c r="AA27" s="12">
         <f t="shared" si="8"/>
-        <v>0.75433947424146175</v>
+        <v>0.75435157455304469</v>
       </c>
       <c r="AB27" s="10">
         <v>167059</v>
@@ -4699,14 +4699,14 @@
       </c>
       <c r="AD27" s="11">
         <f t="shared" si="9"/>
-        <v>63480</v>
+        <v>63482</v>
       </c>
       <c r="AE27" s="3">
-        <v>126163</v>
+        <v>126165</v>
       </c>
       <c r="AF27" s="12">
         <f t="shared" si="10"/>
-        <v>0.75520025859127615</v>
+        <v>0.75521223040961571</v>
       </c>
       <c r="AG27" s="10">
         <v>167755</v>
@@ -4716,14 +4716,14 @@
       </c>
       <c r="AI27" s="11">
         <f t="shared" si="11"/>
-        <v>54796</v>
+        <v>54798</v>
       </c>
       <c r="AJ27" s="3">
-        <v>127105</v>
+        <v>127107</v>
       </c>
       <c r="AK27" s="12">
         <f t="shared" si="12"/>
-        <v>0.75768233435665111</v>
+        <v>0.7576942565050222</v>
       </c>
       <c r="AL27" s="10">
         <v>166641</v>
@@ -4733,14 +4733,14 @@
       </c>
       <c r="AN27" s="11">
         <f t="shared" si="13"/>
-        <v>50762</v>
+        <v>50764</v>
       </c>
       <c r="AO27" s="3">
-        <v>128425</v>
+        <v>128427</v>
       </c>
       <c r="AP27" s="12">
         <f t="shared" si="14"/>
-        <v>0.7706686829771785</v>
+        <v>0.77068068482546315</v>
       </c>
       <c r="AQ27" s="10">
         <v>146205</v>
@@ -4750,14 +4750,14 @@
       </c>
       <c r="AS27" s="11">
         <f t="shared" si="15"/>
-        <v>56459</v>
+        <v>56461</v>
       </c>
       <c r="AT27" s="3">
-        <v>128846</v>
+        <v>128848</v>
       </c>
       <c r="AU27" s="12">
         <f t="shared" si="16"/>
-        <v>0.88126945042919191</v>
+        <v>0.88128312985192025</v>
       </c>
       <c r="AV27" s="10">
         <v>144136</v>
@@ -4767,14 +4767,14 @@
       </c>
       <c r="AX27" s="11">
         <f t="shared" si="17"/>
-        <v>38973</v>
+        <v>38975</v>
       </c>
       <c r="AY27" s="3">
-        <v>129613</v>
+        <v>129615</v>
       </c>
       <c r="AZ27" s="12">
         <f t="shared" si="18"/>
-        <v>0.89924099461619578</v>
+        <v>0.8992548704001776</v>
       </c>
       <c r="BA27" s="10">
         <v>144942</v>
@@ -4784,14 +4784,14 @@
       </c>
       <c r="BC27" s="11">
         <f t="shared" si="19"/>
-        <v>48737</v>
+        <v>48739</v>
       </c>
       <c r="BD27" s="3">
-        <v>130840</v>
+        <v>130842</v>
       </c>
       <c r="BE27" s="12">
         <f t="shared" si="20"/>
-        <v>0.90270590995018696</v>
+        <v>0.90271970857308437</v>
       </c>
       <c r="BF27" s="10">
         <v>145908</v>
@@ -4801,14 +4801,14 @@
       </c>
       <c r="BH27" s="11">
         <f t="shared" si="21"/>
-        <v>123827</v>
+        <v>123829</v>
       </c>
       <c r="BI27" s="3">
-        <v>131303</v>
+        <v>131305</v>
       </c>
       <c r="BJ27" s="12">
         <f t="shared" si="22"/>
-        <v>0.89990267840008775</v>
+        <v>0.89991638566768095</v>
       </c>
     </row>
     <row r="28" spans="1:62" x14ac:dyDescent="0.3">
@@ -4927,14 +4927,14 @@
       </c>
       <c r="AI28" s="11">
         <f t="shared" si="11"/>
-        <v>145989</v>
+        <v>145990</v>
       </c>
       <c r="AJ28" s="3">
-        <v>535620</v>
+        <v>535621</v>
       </c>
       <c r="AK28" s="12">
         <f t="shared" si="12"/>
-        <v>0.87709070901522568</v>
+        <v>0.87709234653942014</v>
       </c>
       <c r="AL28" s="10">
         <v>612549</v>
@@ -4944,14 +4944,14 @@
       </c>
       <c r="AN28" s="11">
         <f t="shared" si="13"/>
-        <v>100038</v>
+        <v>100039</v>
       </c>
       <c r="AO28" s="3">
-        <v>539206</v>
+        <v>539207</v>
       </c>
       <c r="AP28" s="12">
         <f t="shared" si="14"/>
-        <v>0.88026590525819159</v>
+        <v>0.88026753778065103</v>
       </c>
       <c r="AQ28" s="10">
         <v>611342</v>
@@ -4961,14 +4961,14 @@
       </c>
       <c r="AS28" s="11">
         <f t="shared" si="15"/>
-        <v>156270</v>
+        <v>156271</v>
       </c>
       <c r="AT28" s="3">
-        <v>543847</v>
+        <v>543848</v>
       </c>
       <c r="AU28" s="12">
         <f t="shared" si="16"/>
-        <v>0.88959534924804773</v>
+        <v>0.88959698499366968</v>
       </c>
       <c r="AV28" s="10">
         <v>612426</v>
@@ -4978,14 +4978,14 @@
       </c>
       <c r="AX28" s="11">
         <f t="shared" si="17"/>
-        <v>93830</v>
+        <v>93831</v>
       </c>
       <c r="AY28" s="3">
-        <v>546420</v>
+        <v>546421</v>
       </c>
       <c r="AZ28" s="12">
         <f t="shared" si="18"/>
-        <v>0.89222208070852638</v>
+        <v>0.89222371355886265</v>
       </c>
       <c r="BA28" s="10">
         <v>611319</v>
@@ -4995,14 +4995,14 @@
       </c>
       <c r="BC28" s="11">
         <f t="shared" si="19"/>
-        <v>134677</v>
+        <v>134679</v>
       </c>
       <c r="BD28" s="3">
-        <v>549767</v>
+        <v>549769</v>
       </c>
       <c r="BE28" s="12">
         <f t="shared" si="20"/>
-        <v>0.8993127974101901</v>
+        <v>0.8993160690245191</v>
       </c>
       <c r="BF28" s="10">
         <v>611625</v>
@@ -5012,14 +5012,14 @@
       </c>
       <c r="BH28" s="11">
         <f t="shared" si="21"/>
-        <v>507349</v>
+        <v>507350</v>
       </c>
       <c r="BI28" s="3">
-        <v>550974</v>
+        <v>550975</v>
       </c>
       <c r="BJ28" s="12">
         <f t="shared" si="22"/>
-        <v>0.90083629675045984</v>
+        <v>0.90083793173921933</v>
       </c>
     </row>
     <row r="29" spans="1:62" x14ac:dyDescent="0.3">
@@ -5070,14 +5070,14 @@
       </c>
       <c r="O29" s="11">
         <f t="shared" si="3"/>
-        <v>41910</v>
+        <v>41911</v>
       </c>
       <c r="P29" s="3">
-        <v>128930</v>
+        <v>128931</v>
       </c>
       <c r="Q29" s="12">
         <f t="shared" si="4"/>
-        <v>0.86068090787716955</v>
+        <v>0.86068758344459284</v>
       </c>
       <c r="R29" s="10">
         <v>151023</v>
@@ -5223,14 +5223,14 @@
       </c>
       <c r="BH29" s="11">
         <f t="shared" si="21"/>
-        <v>125296</v>
+        <v>125297</v>
       </c>
       <c r="BI29" s="3">
-        <v>137605</v>
+        <v>137606</v>
       </c>
       <c r="BJ29" s="12">
         <f t="shared" si="22"/>
-        <v>0.95851240935908777</v>
+        <v>0.95851937503918194</v>
       </c>
     </row>
     <row r="30" spans="1:62" x14ac:dyDescent="0.3">
@@ -5250,11 +5250,11 @@
         <v>192952</v>
       </c>
       <c r="F30" s="3">
-        <v>193169</v>
+        <v>193170</v>
       </c>
       <c r="G30" s="12">
         <f t="shared" si="0"/>
-        <v>0.88195357586383227</v>
+        <v>0.88195814157352614</v>
       </c>
       <c r="H30" s="10">
         <v>219645</v>
@@ -5264,14 +5264,14 @@
       </c>
       <c r="J30" s="11">
         <f t="shared" si="1"/>
-        <v>67235</v>
+        <v>67236</v>
       </c>
       <c r="K30" s="3">
-        <v>194746</v>
+        <v>194747</v>
       </c>
       <c r="L30" s="12">
         <f t="shared" si="2"/>
-        <v>0.88663980514011242</v>
+        <v>0.88664435794122332</v>
       </c>
       <c r="M30" s="10">
         <v>219769</v>
@@ -5281,14 +5281,14 @@
       </c>
       <c r="O30" s="11">
         <f t="shared" si="3"/>
-        <v>62227</v>
+        <v>62228</v>
       </c>
       <c r="P30" s="3">
-        <v>195701</v>
+        <v>195702</v>
       </c>
       <c r="Q30" s="12">
         <f t="shared" si="4"/>
-        <v>0.89048500925972274</v>
+        <v>0.89048955949201203</v>
       </c>
       <c r="R30" s="10">
         <v>219972</v>
@@ -5349,14 +5349,14 @@
       </c>
       <c r="AI30" s="11">
         <f t="shared" si="11"/>
-        <v>65145</v>
+        <v>65147</v>
       </c>
       <c r="AJ30" s="3">
-        <v>204332</v>
+        <v>204334</v>
       </c>
       <c r="AK30" s="12">
         <f t="shared" si="12"/>
-        <v>0.92214655456420391</v>
+        <v>0.922155580527387</v>
       </c>
       <c r="AL30" s="10">
         <v>221270</v>
@@ -5366,14 +5366,14 @@
       </c>
       <c r="AN30" s="11">
         <f t="shared" si="13"/>
-        <v>41877</v>
+        <v>41879</v>
       </c>
       <c r="AO30" s="3">
-        <v>207165</v>
+        <v>207167</v>
       </c>
       <c r="AP30" s="12">
         <f t="shared" si="14"/>
-        <v>0.93625434988927558</v>
+        <v>0.93626338862023772</v>
       </c>
       <c r="AQ30" s="10">
         <v>222288</v>
@@ -5383,14 +5383,14 @@
       </c>
       <c r="AS30" s="11">
         <f t="shared" si="15"/>
-        <v>71378</v>
+        <v>71380</v>
       </c>
       <c r="AT30" s="3">
-        <v>210206</v>
+        <v>210208</v>
       </c>
       <c r="AU30" s="12">
         <f t="shared" si="16"/>
-        <v>0.94564708846181533</v>
+        <v>0.94565608579860361</v>
       </c>
       <c r="AV30" s="10">
         <v>223595</v>
@@ -5400,14 +5400,14 @@
       </c>
       <c r="AX30" s="11">
         <f t="shared" si="17"/>
-        <v>44969</v>
+        <v>44971</v>
       </c>
       <c r="AY30" s="3">
-        <v>212267</v>
+        <v>212269</v>
       </c>
       <c r="AZ30" s="12">
         <f t="shared" si="18"/>
-        <v>0.94933697086249691</v>
+        <v>0.94934591560634185</v>
       </c>
       <c r="BA30" s="10">
         <v>223670</v>
@@ -5417,14 +5417,14 @@
       </c>
       <c r="BC30" s="11">
         <f t="shared" si="19"/>
-        <v>55526</v>
+        <v>55529</v>
       </c>
       <c r="BD30" s="3">
-        <v>214165</v>
+        <v>214168</v>
       </c>
       <c r="BE30" s="12">
         <f t="shared" si="20"/>
-        <v>0.9575043591004605</v>
+        <v>0.95751777171726205</v>
       </c>
       <c r="BF30" s="10">
         <v>223069</v>
@@ -5434,14 +5434,14 @@
       </c>
       <c r="BH30" s="11">
         <f t="shared" si="21"/>
-        <v>194011</v>
+        <v>194013</v>
       </c>
       <c r="BI30" s="3">
-        <v>214658</v>
+        <v>214660</v>
       </c>
       <c r="BJ30" s="12">
         <f t="shared" si="22"/>
-        <v>0.96229417803459916</v>
+        <v>0.96230314387028226</v>
       </c>
     </row>
     <row r="31" spans="1:62" x14ac:dyDescent="0.3">
@@ -5492,14 +5492,14 @@
       </c>
       <c r="O31" s="11">
         <f t="shared" si="3"/>
-        <v>37058</v>
+        <v>37059</v>
       </c>
       <c r="P31" s="3">
-        <v>96421</v>
+        <v>96422</v>
       </c>
       <c r="Q31" s="12">
         <f t="shared" si="4"/>
-        <v>0.92028480620007058</v>
+        <v>0.92029435064377274</v>
       </c>
       <c r="R31" s="10">
         <v>106003</v>
@@ -5509,14 +5509,14 @@
       </c>
       <c r="T31" s="11">
         <f t="shared" si="5"/>
-        <v>31796</v>
+        <v>31797</v>
       </c>
       <c r="U31" s="3">
-        <v>97295</v>
+        <v>97296</v>
       </c>
       <c r="V31" s="12">
         <f t="shared" si="6"/>
-        <v>0.91785138156467272</v>
+        <v>0.91786081525994545</v>
       </c>
       <c r="W31" s="10">
         <v>106926</v>
@@ -5526,14 +5526,14 @@
       </c>
       <c r="Y31" s="11">
         <f t="shared" si="7"/>
-        <v>38976</v>
+        <v>38978</v>
       </c>
       <c r="Z31" s="3">
-        <v>97991</v>
+        <v>97993</v>
       </c>
       <c r="AA31" s="12">
         <f t="shared" si="8"/>
-        <v>0.91643753624001645</v>
+        <v>0.91645624076464094</v>
       </c>
       <c r="AB31" s="10">
         <v>107458</v>
@@ -5543,14 +5543,14 @@
       </c>
       <c r="AD31" s="11">
         <f t="shared" si="9"/>
-        <v>45796</v>
+        <v>45798</v>
       </c>
       <c r="AE31" s="3">
-        <v>98716</v>
+        <v>98718</v>
       </c>
       <c r="AF31" s="12">
         <f t="shared" si="10"/>
-        <v>0.91864728545106</v>
+        <v>0.91866589737385773</v>
       </c>
       <c r="AG31" s="10">
         <v>107867</v>
@@ -5560,14 +5560,14 @@
       </c>
       <c r="AI31" s="11">
         <f t="shared" si="11"/>
-        <v>40920</v>
+        <v>40922</v>
       </c>
       <c r="AJ31" s="3">
-        <v>99572</v>
+        <v>99574</v>
       </c>
       <c r="AK31" s="12">
         <f t="shared" si="12"/>
-        <v>0.92309974320227683</v>
+        <v>0.92311828455412681</v>
       </c>
       <c r="AL31" s="10">
         <v>106953</v>
@@ -5577,14 +5577,14 @@
       </c>
       <c r="AN31" s="11">
         <f t="shared" si="13"/>
-        <v>26281</v>
+        <v>26282</v>
       </c>
       <c r="AO31" s="3">
-        <v>100301</v>
+        <v>100302</v>
       </c>
       <c r="AP31" s="12">
         <f t="shared" si="14"/>
-        <v>0.93780445616298747</v>
+        <v>0.93781380606434606</v>
       </c>
       <c r="AQ31" s="10">
         <v>105112</v>
@@ -5594,14 +5594,14 @@
       </c>
       <c r="AS31" s="11">
         <f t="shared" si="15"/>
-        <v>38479</v>
+        <v>38480</v>
       </c>
       <c r="AT31" s="3">
-        <v>101059</v>
+        <v>101060</v>
       </c>
       <c r="AU31" s="12">
         <f t="shared" si="16"/>
-        <v>0.9614411294619073</v>
+        <v>0.96145064312352535</v>
       </c>
       <c r="AV31" s="10">
         <v>104718</v>
@@ -5611,14 +5611,14 @@
       </c>
       <c r="AX31" s="11">
         <f t="shared" si="17"/>
-        <v>26651</v>
+        <v>26652</v>
       </c>
       <c r="AY31" s="3">
-        <v>101539</v>
+        <v>101540</v>
       </c>
       <c r="AZ31" s="12">
         <f t="shared" si="18"/>
-        <v>0.96964227735441855</v>
+        <v>0.96965182681105444</v>
       </c>
       <c r="BA31" s="10">
         <v>105608</v>
@@ -5628,14 +5628,14 @@
       </c>
       <c r="BC31" s="11">
         <f t="shared" si="19"/>
-        <v>34947</v>
+        <v>34948</v>
       </c>
       <c r="BD31" s="3">
-        <v>102145</v>
+        <v>102146</v>
       </c>
       <c r="BE31" s="12">
         <f t="shared" si="20"/>
-        <v>0.96720892356639654</v>
+        <v>0.96721839254601927</v>
       </c>
       <c r="BF31" s="10">
         <v>107069</v>
@@ -5645,14 +5645,14 @@
       </c>
       <c r="BH31" s="11">
         <f t="shared" si="21"/>
-        <v>97171</v>
+        <v>97172</v>
       </c>
       <c r="BI31" s="3">
-        <v>102795</v>
+        <v>102796</v>
       </c>
       <c r="BJ31" s="12">
         <f t="shared" si="22"/>
-        <v>0.96008181639877088</v>
+        <v>0.96009115617032004</v>
       </c>
     </row>
     <row r="32" spans="1:62" x14ac:dyDescent="0.3">
@@ -5805,14 +5805,14 @@
       </c>
       <c r="AS32" s="11">
         <f t="shared" si="15"/>
-        <v>107061</v>
+        <v>107062</v>
       </c>
       <c r="AT32" s="3">
-        <v>340058</v>
+        <v>340059</v>
       </c>
       <c r="AU32" s="12">
         <f t="shared" si="16"/>
-        <v>0.95857951470322933</v>
+        <v>0.95858233357387701</v>
       </c>
       <c r="AV32" s="10">
         <v>347413</v>
@@ -5883,11 +5883,11 @@
         <v>798628</v>
       </c>
       <c r="F33" s="3">
-        <v>798875</v>
+        <v>798878</v>
       </c>
       <c r="G33" s="12">
         <f t="shared" si="0"/>
-        <v>0.91929110299972838</v>
+        <v>0.91929455519601566</v>
       </c>
       <c r="H33" s="10">
         <v>871303</v>
@@ -5897,14 +5897,14 @@
       </c>
       <c r="J33" s="11">
         <f t="shared" si="1"/>
-        <v>172519</v>
+        <v>172522</v>
       </c>
       <c r="K33" s="3">
-        <v>805154</v>
+        <v>805157</v>
       </c>
       <c r="L33" s="12">
         <f t="shared" si="2"/>
-        <v>0.9240803715814131</v>
+        <v>0.92408381470051171</v>
       </c>
       <c r="M33" s="10">
         <v>877062</v>
@@ -5914,14 +5914,14 @@
       </c>
       <c r="O33" s="11">
         <f t="shared" si="3"/>
-        <v>162004</v>
+        <v>162007</v>
       </c>
       <c r="P33" s="3">
-        <v>810232</v>
+        <v>810235</v>
       </c>
       <c r="Q33" s="12">
         <f t="shared" si="4"/>
-        <v>0.92380242217767961</v>
+        <v>0.92380584268843025</v>
       </c>
       <c r="R33" s="10">
         <v>881026</v>
@@ -5931,14 +5931,14 @@
       </c>
       <c r="T33" s="11">
         <f t="shared" si="5"/>
-        <v>137069</v>
+        <v>137073</v>
       </c>
       <c r="U33" s="3">
-        <v>816380</v>
+        <v>816384</v>
       </c>
       <c r="V33" s="12">
         <f t="shared" si="6"/>
-        <v>0.92662418589235729</v>
+        <v>0.92662872605348767</v>
       </c>
       <c r="W33" s="10">
         <v>884173</v>
@@ -5948,14 +5948,14 @@
       </c>
       <c r="Y33" s="11">
         <f t="shared" si="7"/>
-        <v>177132</v>
+        <v>177138</v>
       </c>
       <c r="Z33" s="3">
-        <v>820950</v>
+        <v>820956</v>
       </c>
       <c r="AA33" s="12">
         <f t="shared" si="8"/>
-        <v>0.92849476290273514</v>
+        <v>0.92850154890502201</v>
       </c>
       <c r="AB33" s="10">
         <v>884817</v>
@@ -5965,14 +5965,14 @@
       </c>
       <c r="AD33" s="11">
         <f t="shared" si="9"/>
-        <v>222673</v>
+        <v>222677</v>
       </c>
       <c r="AE33" s="3">
-        <v>826028</v>
+        <v>826032</v>
       </c>
       <c r="AF33" s="12">
         <f t="shared" si="10"/>
-        <v>0.93355801256078941</v>
+        <v>0.93356253326959138</v>
       </c>
       <c r="AG33" s="10">
         <v>888089</v>
@@ -5982,14 +5982,14 @@
       </c>
       <c r="AI33" s="11">
         <f t="shared" si="11"/>
-        <v>209157</v>
+        <v>209160</v>
       </c>
       <c r="AJ33" s="3">
-        <v>829771</v>
+        <v>829774</v>
       </c>
       <c r="AK33" s="12">
         <f t="shared" si="12"/>
-        <v>0.9343331580506008</v>
+        <v>0.93433653609041434</v>
       </c>
       <c r="AL33" s="10">
         <v>887648</v>
@@ -5999,14 +5999,14 @@
       </c>
       <c r="AN33" s="11">
         <f t="shared" si="13"/>
-        <v>110955</v>
+        <v>110959</v>
       </c>
       <c r="AO33" s="3">
-        <v>833654</v>
+        <v>833658</v>
       </c>
       <c r="AP33" s="12">
         <f t="shared" si="14"/>
-        <v>0.93917183388009662</v>
+        <v>0.93917634017087859</v>
       </c>
       <c r="AQ33" s="10">
         <v>877839</v>
@@ -6016,14 +6016,14 @@
       </c>
       <c r="AS33" s="11">
         <f t="shared" si="15"/>
-        <v>210337</v>
+        <v>210340</v>
       </c>
       <c r="AT33" s="3">
-        <v>841914</v>
+        <v>841917</v>
       </c>
       <c r="AU33" s="12">
         <f t="shared" si="16"/>
-        <v>0.95907563915478811</v>
+        <v>0.95907905663794846</v>
       </c>
       <c r="AV33" s="10">
         <v>881788</v>
@@ -6033,14 +6033,14 @@
       </c>
       <c r="AX33" s="11">
         <f t="shared" si="17"/>
-        <v>121430</v>
+        <v>121433</v>
       </c>
       <c r="AY33" s="3">
-        <v>847606</v>
+        <v>847609</v>
       </c>
       <c r="AZ33" s="12">
         <f t="shared" si="18"/>
-        <v>0.96123558043429935</v>
+        <v>0.96123898261260077</v>
       </c>
       <c r="BA33" s="10">
         <v>886741</v>
@@ -6050,14 +6050,14 @@
       </c>
       <c r="BC33" s="11">
         <f t="shared" si="19"/>
-        <v>139172</v>
+        <v>139175</v>
       </c>
       <c r="BD33" s="3">
-        <v>853498</v>
+        <v>853501</v>
       </c>
       <c r="BE33" s="12">
         <f t="shared" si="20"/>
-        <v>0.96251103760850121</v>
+        <v>0.96251442078352079</v>
       </c>
       <c r="BF33" s="10">
         <v>893063</v>
@@ -6067,14 +6067,14 @@
       </c>
       <c r="BH33" s="11">
         <f t="shared" si="21"/>
-        <v>834008</v>
+        <v>834012</v>
       </c>
       <c r="BI33" s="3">
-        <v>857131</v>
+        <v>857135</v>
       </c>
       <c r="BJ33" s="12">
         <f t="shared" si="22"/>
-        <v>0.95976543648096491</v>
+        <v>0.95976991544829426</v>
       </c>
     </row>
     <row r="34" spans="1:62" x14ac:dyDescent="0.3">
@@ -6516,11 +6516,11 @@
         <v>1213488</v>
       </c>
       <c r="F36" s="3">
-        <v>1214467</v>
+        <v>1214468</v>
       </c>
       <c r="G36" s="12">
         <f t="shared" si="0"/>
-        <v>0.87391405402799338</v>
+        <v>0.87391477361449021</v>
       </c>
       <c r="H36" s="10">
         <v>1398033</v>
@@ -6530,14 +6530,14 @@
       </c>
       <c r="J36" s="11">
         <f t="shared" si="1"/>
-        <v>374679</v>
+        <v>374682</v>
       </c>
       <c r="K36" s="3">
-        <v>1219844</v>
+        <v>1219847</v>
       </c>
       <c r="L36" s="12">
         <f t="shared" si="2"/>
-        <v>0.87254306586468278</v>
+        <v>0.87254521173677591</v>
       </c>
       <c r="M36" s="10">
         <v>1405014</v>
@@ -6547,14 +6547,14 @@
       </c>
       <c r="O36" s="11">
         <f t="shared" si="3"/>
-        <v>355857</v>
+        <v>355861</v>
       </c>
       <c r="P36" s="3">
-        <v>1224769</v>
+        <v>1224773</v>
       </c>
       <c r="Q36" s="12">
         <f t="shared" si="4"/>
-        <v>0.87171302207664836</v>
+        <v>0.87171586902336917</v>
       </c>
       <c r="R36" s="10">
         <v>1409335</v>
@@ -6564,14 +6564,14 @@
       </c>
       <c r="T36" s="11">
         <f t="shared" si="5"/>
-        <v>320698</v>
+        <v>320701</v>
       </c>
       <c r="U36" s="3">
-        <v>1232421</v>
+        <v>1232424</v>
       </c>
       <c r="V36" s="12">
         <f t="shared" si="6"/>
-        <v>0.8744698740895529</v>
+        <v>0.87447200275307146</v>
       </c>
       <c r="W36" s="10">
         <v>1413902</v>
@@ -6581,14 +6581,14 @@
       </c>
       <c r="Y36" s="11">
         <f t="shared" si="7"/>
-        <v>384046</v>
+        <v>384051</v>
       </c>
       <c r="Z36" s="3">
-        <v>1237581</v>
+        <v>1237586</v>
       </c>
       <c r="AA36" s="12">
         <f t="shared" si="8"/>
-        <v>0.87529475168717497</v>
+        <v>0.87529828800015841</v>
       </c>
       <c r="AB36" s="10">
         <v>1416919</v>
@@ -6598,14 +6598,14 @@
       </c>
       <c r="AD36" s="11">
         <f t="shared" si="9"/>
-        <v>476495</v>
+        <v>476498</v>
       </c>
       <c r="AE36" s="3">
-        <v>1244828</v>
+        <v>1244831</v>
       </c>
       <c r="AF36" s="12">
         <f t="shared" si="10"/>
-        <v>0.8785456331660455</v>
+        <v>0.87854775043598121</v>
       </c>
       <c r="AG36" s="10">
         <v>1419473</v>
@@ -6615,14 +6615,14 @@
       </c>
       <c r="AI36" s="11">
         <f t="shared" si="11"/>
-        <v>414506</v>
+        <v>414510</v>
       </c>
       <c r="AJ36" s="3">
-        <v>1251115</v>
+        <v>1251119</v>
       </c>
       <c r="AK36" s="12">
         <f t="shared" si="12"/>
-        <v>0.88139401031227782</v>
+        <v>0.88139682825950194</v>
       </c>
       <c r="AL36" s="10">
         <v>1415447</v>
@@ -6632,14 +6632,14 @@
       </c>
       <c r="AN36" s="11">
         <f t="shared" si="13"/>
-        <v>261120</v>
+        <v>261122</v>
       </c>
       <c r="AO36" s="3">
-        <v>1259385</v>
+        <v>1259387</v>
       </c>
       <c r="AP36" s="12">
         <f t="shared" si="14"/>
-        <v>0.88974366401567839</v>
+        <v>0.88974507699687799</v>
       </c>
       <c r="AQ36" s="10">
         <v>1379433</v>
@@ -6649,14 +6649,14 @@
       </c>
       <c r="AS36" s="11">
         <f t="shared" si="15"/>
-        <v>413104</v>
+        <v>413106</v>
       </c>
       <c r="AT36" s="3">
-        <v>1269277</v>
+        <v>1269279</v>
       </c>
       <c r="AU36" s="12">
         <f t="shared" si="16"/>
-        <v>0.92014400119469375</v>
+        <v>0.92014545106576395</v>
       </c>
       <c r="AV36" s="10">
         <v>1370415</v>
@@ -6666,14 +6666,14 @@
       </c>
       <c r="AX36" s="11">
         <f t="shared" si="17"/>
-        <v>275212</v>
+        <v>275214</v>
       </c>
       <c r="AY36" s="3">
-        <v>1275422</v>
+        <v>1275424</v>
       </c>
       <c r="AZ36" s="12">
         <f t="shared" si="18"/>
-        <v>0.93068304126852086</v>
+        <v>0.93068450068045083</v>
       </c>
       <c r="BA36" s="10">
         <v>1375391</v>
@@ -6683,14 +6683,14 @@
       </c>
       <c r="BC36" s="11">
         <f t="shared" si="19"/>
-        <v>338579</v>
+        <v>338581</v>
       </c>
       <c r="BD36" s="3">
-        <v>1281945</v>
+        <v>1281947</v>
       </c>
       <c r="BE36" s="12">
         <f t="shared" si="20"/>
-        <v>0.93205859279288583</v>
+        <v>0.93206004692483813</v>
       </c>
       <c r="BF36" s="10">
         <v>1380633</v>
@@ -6700,14 +6700,14 @@
       </c>
       <c r="BH36" s="11">
         <f t="shared" si="21"/>
-        <v>1217309</v>
+        <v>1217311</v>
       </c>
       <c r="BI36" s="3">
-        <v>1281464</v>
+        <v>1281466</v>
       </c>
       <c r="BJ36" s="12">
         <f t="shared" si="22"/>
-        <v>0.92817135328505118</v>
+        <v>0.92817280189594198</v>
       </c>
     </row>
     <row r="37" spans="1:62" x14ac:dyDescent="0.3">
@@ -6727,11 +6727,11 @@
         <v>627302</v>
       </c>
       <c r="F37" s="3">
-        <v>627970</v>
+        <v>627971</v>
       </c>
       <c r="G37" s="12">
         <f t="shared" si="0"/>
-        <v>0.88628229157257699</v>
+        <v>0.88628370291753233</v>
       </c>
       <c r="H37" s="10">
         <v>707340</v>
@@ -6741,14 +6741,14 @@
       </c>
       <c r="J37" s="11">
         <f t="shared" si="1"/>
-        <v>167234</v>
+        <v>167235</v>
       </c>
       <c r="K37" s="3">
-        <v>632197</v>
+        <v>632198</v>
       </c>
       <c r="L37" s="12">
         <f t="shared" si="2"/>
-        <v>0.89376678824893263</v>
+        <v>0.89376820199621121</v>
       </c>
       <c r="M37" s="10">
         <v>710827</v>
@@ -6758,14 +6758,14 @@
       </c>
       <c r="O37" s="11">
         <f t="shared" si="3"/>
-        <v>160113</v>
+        <v>160114</v>
       </c>
       <c r="P37" s="3">
-        <v>636970</v>
+        <v>636971</v>
       </c>
       <c r="Q37" s="12">
         <f t="shared" si="4"/>
-        <v>0.89609708128700793</v>
+        <v>0.89609848809907333</v>
       </c>
       <c r="R37" s="10">
         <v>713357</v>
@@ -6775,14 +6775,14 @@
       </c>
       <c r="T37" s="11">
         <f t="shared" si="5"/>
-        <v>137614</v>
+        <v>137615</v>
       </c>
       <c r="U37" s="3">
-        <v>644568</v>
+        <v>644569</v>
       </c>
       <c r="V37" s="12">
         <f t="shared" si="6"/>
-        <v>0.9035700217422693</v>
+        <v>0.90357142356491915</v>
       </c>
       <c r="W37" s="10">
         <v>709504</v>
@@ -6792,14 +6792,14 @@
       </c>
       <c r="Y37" s="11">
         <f t="shared" si="7"/>
-        <v>170679</v>
+        <v>170680</v>
       </c>
       <c r="Z37" s="3">
-        <v>650134</v>
+        <v>650135</v>
       </c>
       <c r="AA37" s="12">
         <f t="shared" si="8"/>
-        <v>0.91632182482410252</v>
+        <v>0.9163232342594263</v>
       </c>
       <c r="AB37" s="10">
         <v>709880</v>
@@ -6809,14 +6809,14 @@
       </c>
       <c r="AD37" s="11">
         <f t="shared" si="9"/>
-        <v>220785</v>
+        <v>220786</v>
       </c>
       <c r="AE37" s="3">
-        <v>655099</v>
+        <v>655100</v>
       </c>
       <c r="AF37" s="12">
         <f t="shared" si="10"/>
-        <v>0.9228306192595932</v>
+        <v>0.92283202794838559</v>
       </c>
       <c r="AG37" s="10">
         <v>716349</v>
@@ -6826,14 +6826,14 @@
       </c>
       <c r="AI37" s="11">
         <f t="shared" si="11"/>
-        <v>195311</v>
+        <v>195312</v>
       </c>
       <c r="AJ37" s="3">
-        <v>661857</v>
+        <v>661858</v>
       </c>
       <c r="AK37" s="12">
         <f t="shared" si="12"/>
-        <v>0.92393093310662822</v>
+        <v>0.92393232907423617</v>
       </c>
       <c r="AL37" s="10">
         <v>718037</v>
@@ -6843,14 +6843,14 @@
       </c>
       <c r="AN37" s="11">
         <f t="shared" si="13"/>
-        <v>115177</v>
+        <v>115179</v>
       </c>
       <c r="AO37" s="3">
-        <v>668147</v>
+        <v>668149</v>
       </c>
       <c r="AP37" s="12">
         <f t="shared" si="14"/>
-        <v>0.93051890083658639</v>
+        <v>0.93052168620837084</v>
       </c>
       <c r="AQ37" s="10">
         <v>723207</v>
@@ -6860,14 +6860,14 @@
       </c>
       <c r="AS37" s="11">
         <f t="shared" si="15"/>
-        <v>201325</v>
+        <v>201326</v>
       </c>
       <c r="AT37" s="3">
-        <v>675768</v>
+        <v>675769</v>
       </c>
       <c r="AU37" s="12">
         <f t="shared" si="16"/>
-        <v>0.93440467252114545</v>
+        <v>0.93440605525112452</v>
       </c>
       <c r="AV37" s="10">
         <v>726054</v>
@@ -6877,14 +6877,14 @@
       </c>
       <c r="AX37" s="11">
         <f t="shared" si="17"/>
-        <v>124580</v>
+        <v>124582</v>
       </c>
       <c r="AY37" s="3">
-        <v>681066</v>
+        <v>681068</v>
       </c>
       <c r="AZ37" s="12">
         <f t="shared" si="18"/>
-        <v>0.93803766661983823</v>
+        <v>0.93804042123588605</v>
       </c>
       <c r="BA37" s="10">
         <v>731853</v>
@@ -6894,14 +6894,14 @@
       </c>
       <c r="BC37" s="11">
         <f t="shared" si="19"/>
-        <v>136742</v>
+        <v>136744</v>
       </c>
       <c r="BD37" s="3">
-        <v>686377</v>
+        <v>686379</v>
       </c>
       <c r="BE37" s="12">
         <f t="shared" si="20"/>
-        <v>0.93786183837464632</v>
+        <v>0.93786457116388122</v>
       </c>
       <c r="BF37" s="10">
         <v>734800</v>
@@ -6911,14 +6911,14 @@
       </c>
       <c r="BH37" s="11">
         <f t="shared" si="21"/>
-        <v>630834</v>
+        <v>630835</v>
       </c>
       <c r="BI37" s="3">
-        <v>686240</v>
+        <v>686241</v>
       </c>
       <c r="BJ37" s="12">
         <f t="shared" si="22"/>
-        <v>0.9339139902014153</v>
+        <v>0.93391535111594992</v>
       </c>
     </row>
     <row r="38" spans="1:62" x14ac:dyDescent="0.3">
@@ -7476,14 +7476,14 @@
       </c>
       <c r="AN40" s="11">
         <f t="shared" si="13"/>
-        <v>62708</v>
+        <v>62709</v>
       </c>
       <c r="AO40" s="3">
-        <v>277521</v>
+        <v>277522</v>
       </c>
       <c r="AP40" s="12">
         <f t="shared" si="14"/>
-        <v>0.91334869178871159</v>
+        <v>0.9133519828862926</v>
       </c>
       <c r="AQ40" s="10">
         <v>302709</v>
@@ -7493,14 +7493,14 @@
       </c>
       <c r="AS40" s="11">
         <f t="shared" si="15"/>
-        <v>107028</v>
+        <v>107029</v>
       </c>
       <c r="AT40" s="3">
-        <v>279348</v>
+        <v>279349</v>
       </c>
       <c r="AU40" s="12">
         <f t="shared" si="16"/>
-        <v>0.92282687333379587</v>
+        <v>0.9228301768364997</v>
       </c>
       <c r="AV40" s="10">
         <v>301724</v>
@@ -7510,14 +7510,14 @@
       </c>
       <c r="AX40" s="11">
         <f t="shared" si="17"/>
-        <v>70559</v>
+        <v>70560</v>
       </c>
       <c r="AY40" s="3">
-        <v>280799</v>
+        <v>280800</v>
       </c>
       <c r="AZ40" s="12">
         <f t="shared" si="18"/>
-        <v>0.93064853972504669</v>
+        <v>0.93065185401227613</v>
       </c>
       <c r="BA40" s="10">
         <v>302553</v>
@@ -7527,14 +7527,14 @@
       </c>
       <c r="BC40" s="11">
         <f t="shared" si="19"/>
-        <v>83698</v>
+        <v>83699</v>
       </c>
       <c r="BD40" s="3">
-        <v>282393</v>
+        <v>282394</v>
       </c>
       <c r="BE40" s="12">
         <f t="shared" si="20"/>
-        <v>0.93336704643483948</v>
+        <v>0.93337035164086957</v>
       </c>
       <c r="BF40" s="10">
         <v>304085</v>
@@ -7544,14 +7544,14 @@
       </c>
       <c r="BH40" s="11">
         <f t="shared" si="21"/>
-        <v>272365</v>
+        <v>272367</v>
       </c>
       <c r="BI40" s="3">
-        <v>283650</v>
+        <v>283652</v>
       </c>
       <c r="BJ40" s="12">
         <f t="shared" si="22"/>
-        <v>0.93279839518555663</v>
+        <v>0.932804972293931</v>
       </c>
     </row>
     <row r="41" spans="1:62" x14ac:dyDescent="0.3">
@@ -7571,11 +7571,11 @@
         <v>762739</v>
       </c>
       <c r="F41" s="3">
-        <v>763709</v>
+        <v>763716</v>
       </c>
       <c r="G41" s="12">
         <f t="shared" si="0"/>
-        <v>0.87102046309412207</v>
+        <v>0.87102844668897517</v>
       </c>
       <c r="H41" s="10">
         <v>885438</v>
@@ -7585,14 +7585,14 @@
       </c>
       <c r="J41" s="11">
         <f t="shared" si="1"/>
-        <v>217425</v>
+        <v>217437</v>
       </c>
       <c r="K41" s="3">
-        <v>768959</v>
+        <v>768971</v>
       </c>
       <c r="L41" s="12">
         <f t="shared" si="2"/>
-        <v>0.8684504166299617</v>
+        <v>0.8684639692445999</v>
       </c>
       <c r="M41" s="10">
         <v>894344</v>
@@ -7602,14 +7602,14 @@
       </c>
       <c r="O41" s="11">
         <f t="shared" si="3"/>
-        <v>206479</v>
+        <v>206491</v>
       </c>
       <c r="P41" s="3">
-        <v>773423</v>
+        <v>773435</v>
       </c>
       <c r="Q41" s="12">
         <f t="shared" si="4"/>
-        <v>0.86479363645308738</v>
+        <v>0.86480705410893344</v>
       </c>
       <c r="R41" s="10">
         <v>899235</v>
@@ -7619,14 +7619,14 @@
       </c>
       <c r="T41" s="11">
         <f t="shared" si="5"/>
-        <v>170806</v>
+        <v>170818</v>
       </c>
       <c r="U41" s="3">
-        <v>780263</v>
+        <v>780275</v>
       </c>
       <c r="V41" s="12">
         <f t="shared" si="6"/>
-        <v>0.86769643085511572</v>
+        <v>0.86770977553142392</v>
       </c>
       <c r="W41" s="10">
         <v>900188</v>
@@ -7636,14 +7636,14 @@
       </c>
       <c r="Y41" s="11">
         <f t="shared" si="7"/>
-        <v>227468</v>
+        <v>227482</v>
       </c>
       <c r="Z41" s="3">
-        <v>786264</v>
+        <v>786278</v>
       </c>
       <c r="AA41" s="12">
         <f t="shared" si="8"/>
-        <v>0.87344421387532378</v>
+        <v>0.87345976618217525</v>
       </c>
       <c r="AB41" s="10">
         <v>900385</v>
@@ -7653,14 +7653,14 @@
       </c>
       <c r="AD41" s="11">
         <f t="shared" si="9"/>
-        <v>278311</v>
+        <v>278325</v>
       </c>
       <c r="AE41" s="3">
-        <v>790829</v>
+        <v>790843</v>
       </c>
       <c r="AF41" s="12">
         <f t="shared" si="10"/>
-        <v>0.87832316175858105</v>
+        <v>0.878338710662661</v>
       </c>
       <c r="AG41" s="10">
         <v>896586</v>
@@ -7670,14 +7670,14 @@
       </c>
       <c r="AI41" s="11">
         <f t="shared" si="11"/>
-        <v>232863</v>
+        <v>232877</v>
       </c>
       <c r="AJ41" s="3">
-        <v>796673</v>
+        <v>796687</v>
       </c>
       <c r="AK41" s="12">
         <f t="shared" si="12"/>
-        <v>0.88856283725152974</v>
+        <v>0.88857845203917973</v>
       </c>
       <c r="AL41" s="10">
         <v>888836</v>
@@ -7687,14 +7687,14 @@
       </c>
       <c r="AN41" s="11">
         <f t="shared" si="13"/>
-        <v>136985</v>
+        <v>137000</v>
       </c>
       <c r="AO41" s="3">
-        <v>802510</v>
+        <v>802525</v>
       </c>
       <c r="AP41" s="12">
         <f t="shared" si="14"/>
-        <v>0.90287747120953699</v>
+        <v>0.90289434721365924</v>
       </c>
       <c r="AQ41" s="10">
         <v>877850</v>
@@ -7704,14 +7704,14 @@
       </c>
       <c r="AS41" s="11">
         <f t="shared" si="15"/>
-        <v>256445</v>
+        <v>256456</v>
       </c>
       <c r="AT41" s="3">
-        <v>809983</v>
+        <v>809994</v>
       </c>
       <c r="AU41" s="12">
         <f t="shared" si="16"/>
-        <v>0.92268952554536654</v>
+        <v>0.92270205615993617</v>
       </c>
       <c r="AV41" s="10">
         <v>870770</v>
@@ -7721,14 +7721,14 @@
       </c>
       <c r="AX41" s="11">
         <f t="shared" si="17"/>
-        <v>141886</v>
+        <v>141894</v>
       </c>
       <c r="AY41" s="3">
-        <v>814244</v>
+        <v>814252</v>
       </c>
       <c r="AZ41" s="12">
         <f t="shared" si="18"/>
-        <v>0.93508503967752676</v>
+        <v>0.93509422694856281</v>
       </c>
       <c r="BA41" s="10">
         <v>867846</v>
@@ -7738,14 +7738,14 @@
       </c>
       <c r="BC41" s="11">
         <f t="shared" si="19"/>
-        <v>163695</v>
+        <v>163704</v>
       </c>
       <c r="BD41" s="3">
-        <v>820751</v>
+        <v>820760</v>
       </c>
       <c r="BE41" s="12">
         <f t="shared" si="20"/>
-        <v>0.94573345962302069</v>
+        <v>0.94574383012654317</v>
       </c>
       <c r="BF41" s="10">
         <v>876639</v>
@@ -7755,14 +7755,14 @@
       </c>
       <c r="BH41" s="11">
         <f t="shared" si="21"/>
-        <v>773508</v>
+        <v>773524</v>
       </c>
       <c r="BI41" s="3">
-        <v>823831</v>
+        <v>823847</v>
       </c>
       <c r="BJ41" s="12">
         <f t="shared" si="22"/>
-        <v>0.93976083655872034</v>
+        <v>0.93977908808528943</v>
       </c>
     </row>
     <row r="42" spans="1:62" x14ac:dyDescent="0.3">
@@ -8354,14 +8354,14 @@
       </c>
       <c r="AX44" s="11">
         <f t="shared" si="17"/>
-        <v>77768</v>
+        <v>77769</v>
       </c>
       <c r="AY44" s="3">
-        <v>303221</v>
+        <v>303222</v>
       </c>
       <c r="AZ44" s="12">
         <f t="shared" si="18"/>
-        <v>0.86154077828794839</v>
+        <v>0.86154361958448877</v>
       </c>
       <c r="BA44" s="10">
         <v>353580</v>
@@ -8371,14 +8371,14 @@
       </c>
       <c r="BC44" s="11">
         <f t="shared" si="19"/>
-        <v>84508</v>
+        <v>84509</v>
       </c>
       <c r="BD44" s="3">
-        <v>306114</v>
+        <v>306115</v>
       </c>
       <c r="BE44" s="12">
         <f t="shared" si="20"/>
-        <v>0.86575598167317158</v>
+        <v>0.86575880988743703</v>
       </c>
       <c r="BF44" s="10">
         <v>357819</v>
@@ -8388,14 +8388,14 @@
       </c>
       <c r="BH44" s="11">
         <f t="shared" si="21"/>
-        <v>278262</v>
+        <v>278264</v>
       </c>
       <c r="BI44" s="3">
-        <v>306789</v>
+        <v>306791</v>
       </c>
       <c r="BJ44" s="12">
         <f t="shared" si="22"/>
-        <v>0.85738599683079997</v>
+        <v>0.85739158624891354</v>
       </c>
     </row>
     <row r="45" spans="1:62" x14ac:dyDescent="0.3">
@@ -9011,10 +9011,10 @@
       </c>
     </row>
     <row r="48" spans="1:62" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A48" s="27" t="s">
+      <c r="A48" s="24" t="s">
         <v>44</v>
       </c>
-      <c r="B48" s="27"/>
+      <c r="B48" s="24"/>
       <c r="C48" s="6">
         <f>SUM(C10:C47)</f>
         <v>10233313</v>
@@ -9025,15 +9025,15 @@
       </c>
       <c r="E48" s="7">
         <f t="shared" ref="E48" si="23">F48-D48</f>
-        <v>2915130</v>
+        <v>2915150</v>
       </c>
       <c r="F48" s="8">
         <f>SUM(F10:F47)</f>
-        <v>8977108</v>
+        <v>8977128</v>
       </c>
       <c r="G48" s="5">
         <f>F48/C48</f>
-        <v>0.87724356716148522</v>
+        <v>0.8772455215627627</v>
       </c>
       <c r="H48" s="6">
         <f>SUM(H10:H47)</f>
@@ -9045,15 +9045,15 @@
       </c>
       <c r="J48" s="7">
         <f>K48-I48</f>
-        <v>2520074</v>
+        <v>2520100</v>
       </c>
       <c r="K48" s="8">
         <f>SUM(K10:K47)</f>
-        <v>9038482</v>
+        <v>9038508</v>
       </c>
       <c r="L48" s="5">
         <f>K48/H48</f>
-        <v>0.87871151479433873</v>
+        <v>0.87871404248642071</v>
       </c>
       <c r="M48" s="6">
         <f>SUM(M10:M47)</f>
@@ -9065,15 +9065,15 @@
       </c>
       <c r="O48" s="7">
         <f>P48-N48</f>
-        <v>2400879</v>
+        <v>2400908</v>
       </c>
       <c r="P48" s="8">
         <f>SUM(P10:P47)</f>
-        <v>9089543</v>
+        <v>9089572</v>
       </c>
       <c r="Q48" s="5">
         <f>P48/M48</f>
-        <v>0.87750462209459201</v>
+        <v>0.87750742175504148</v>
       </c>
       <c r="R48" s="6">
         <f>SUM(R10:R47)</f>
@@ -9085,15 +9085,15 @@
       </c>
       <c r="T48" s="7">
         <f>U48-S48</f>
-        <v>2087888</v>
+        <v>2087916</v>
       </c>
       <c r="U48" s="8">
         <f>SUM(U10:U47)</f>
-        <v>9168363</v>
+        <v>9168391</v>
       </c>
       <c r="V48" s="5">
         <f>U48/R48</f>
-        <v>0.87931066231299804</v>
+        <v>0.87931334771043979</v>
       </c>
       <c r="W48" s="6">
         <f>SUM(W10:W47)</f>
@@ -9105,15 +9105,15 @@
       </c>
       <c r="Y48" s="7">
         <f>Z48-X48</f>
-        <v>2662389</v>
+        <v>2662424</v>
       </c>
       <c r="Z48" s="8">
         <f>SUM(Z10:Z47)</f>
-        <v>9229608</v>
+        <v>9229643</v>
       </c>
       <c r="AA48" s="5">
         <f>Z48/W48</f>
-        <v>0.88271845986152686</v>
+        <v>0.8827218072567895</v>
       </c>
       <c r="AB48" s="6">
         <f>SUM(AB10:AB47)</f>
@@ -9125,15 +9125,15 @@
       </c>
       <c r="AD48" s="7">
         <f>AE48-AC48</f>
-        <v>3305606</v>
+        <v>3305637</v>
       </c>
       <c r="AE48" s="8">
         <f>SUM(AE10:AE47)</f>
-        <v>9295959</v>
+        <v>9295990</v>
       </c>
       <c r="AF48" s="5">
         <f>AE48/AB48</f>
-        <v>0.88754287597622028</v>
+        <v>0.88754583573853807</v>
       </c>
       <c r="AG48" s="6">
         <f>SUM(AG10:AG47)</f>
@@ -9145,15 +9145,15 @@
       </c>
       <c r="AI48" s="7">
         <f>AJ48-AH48</f>
-        <v>2880815</v>
+        <v>2880848</v>
       </c>
       <c r="AJ48" s="8">
         <f>SUM(AJ10:AJ47)</f>
-        <v>9363623</v>
+        <v>9363656</v>
       </c>
       <c r="AK48" s="5">
         <f>AJ48/AG48</f>
-        <v>0.89219303474471423</v>
+        <v>0.89219617907999416</v>
       </c>
       <c r="AL48" s="6">
         <f>SUM(AL10:AL47)</f>
@@ -9165,15 +9165,15 @@
       </c>
       <c r="AN48" s="7">
         <f>AO48-AM48</f>
-        <v>1785252</v>
+        <v>1785286</v>
       </c>
       <c r="AO48" s="8">
         <f>SUM(AO10:AO47)</f>
-        <v>9435041</v>
+        <v>9435075</v>
       </c>
       <c r="AP48" s="5">
         <f>AO48/AL48</f>
-        <v>0.90042420436629877</v>
+        <v>0.90042744912410622</v>
       </c>
       <c r="AQ48" s="6">
         <f>SUM(AQ10:AQ47)</f>
@@ -9185,15 +9185,15 @@
       </c>
       <c r="AS48" s="7">
         <f>AT48-AR48</f>
-        <v>2955244</v>
+        <v>2955273</v>
       </c>
       <c r="AT48" s="8">
         <f>SUM(AT10:AT47)</f>
-        <v>9520115</v>
+        <v>9520144</v>
       </c>
       <c r="AU48" s="5">
         <f>AT48/AQ48</f>
-        <v>0.91797783881699546</v>
+        <v>0.91798063514427986</v>
       </c>
       <c r="AV48" s="6">
         <f>SUM(AV10:AV47)</f>
@@ -9205,15 +9205,15 @@
       </c>
       <c r="AX48" s="7">
         <f>AY48-AW48</f>
-        <v>1784516</v>
+        <v>1784542</v>
       </c>
       <c r="AY48" s="8">
         <f>SUM(AY10:AY47)</f>
-        <v>9585362</v>
+        <v>9585388</v>
       </c>
       <c r="AZ48" s="5">
         <f>AY48/AV48</f>
-        <v>0.92543049719470472</v>
+        <v>0.92543300739650269</v>
       </c>
       <c r="BA48" s="6">
         <f>SUM(BA10:BA47)</f>
@@ -9225,15 +9225,15 @@
       </c>
       <c r="BC48" s="7">
         <f>BD48-BB48</f>
-        <v>2313753</v>
+        <v>2313783</v>
       </c>
       <c r="BD48" s="8">
         <f>SUM(BD10:BD47)</f>
-        <v>9653751</v>
+        <v>9653781</v>
       </c>
       <c r="BE48" s="5">
         <f>BD48/BA48</f>
-        <v>0.93073338939345351</v>
+        <v>0.93073628174086154</v>
       </c>
       <c r="BF48" s="6">
         <f>SUM(BF10:BF47)</f>
@@ -9245,30 +9245,36 @@
       </c>
       <c r="BH48" s="7">
         <f>BI48-BG48</f>
-        <v>9066674</v>
+        <v>9066712</v>
       </c>
       <c r="BI48" s="8">
         <f>SUM(BI10:BI47)</f>
-        <v>9676047</v>
+        <v>9676085</v>
       </c>
       <c r="BJ48" s="5">
         <f>BI48/BF48</f>
-        <v>0.92790965295618721</v>
+        <v>0.92791329706486225</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A59" s="26" t="s">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A57" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="B59" s="26"/>
-      <c r="C59" s="26"/>
-      <c r="D59" s="26"/>
-      <c r="E59" s="26"/>
-      <c r="F59" s="2"/>
+      <c r="B57" s="21"/>
+      <c r="C57" s="21"/>
+      <c r="D57" s="21"/>
+      <c r="E57" s="21"/>
+      <c r="F57" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="A59:E59"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="A57:E57"/>
     <mergeCell ref="AQ8:AU8"/>
     <mergeCell ref="AV8:AZ8"/>
     <mergeCell ref="BA8:BE8"/>
@@ -9281,12 +9287,6 @@
     <mergeCell ref="AG8:AK8"/>
     <mergeCell ref="AL8:AP8"/>
     <mergeCell ref="H8:L8"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="C8:G8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
